--- a/Financial Analysis/AXP.xlsx
+++ b/Financial Analysis/AXP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A31F86-7A22-49EC-A532-A26ADC230F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B60690-99FC-42FC-ADD6-FA4A59EAD13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7753066E-724B-42EB-9AF0-1E4829C95CCE}"/>
   </bookViews>
@@ -256,10 +256,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
-  </si>
-  <si>
     <t>Total service revenue</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -813,14 +813,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="8">
-        <v>245.15</v>
+        <v>291.27999999999997</v>
       </c>
       <c r="F3" s="11">
-        <v>45769</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45782</v>
+        <v>45804</v>
       </c>
       <c r="H3" s="11">
         <v>45856</v>
@@ -841,7 +841,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>171752.09</v>
+        <v>204070.76799999998</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -880,7 +880,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>172039.09</v>
+        <v>204357.76799999998</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="AN45" s="8">
         <f>Main!D3</f>
-        <v>245.15</v>
+        <v>291.27999999999997</v>
       </c>
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.3">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="AN46" s="9">
         <f>AN44/AN45-1</f>
-        <v>0.20252062275431082</v>
+        <v>1.2077487874963433E-2</v>
       </c>
     </row>
     <row r="47" spans="2:40" x14ac:dyDescent="0.3">
@@ -6106,7 +6106,7 @@
         <v>62</v>
       </c>
       <c r="AN47" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AXP.xlsx
+++ b/Financial Analysis/AXP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B60690-99FC-42FC-ADD6-FA4A59EAD13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4BF8C7-2404-4C96-AD24-FEEE237E559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7753066E-724B-42EB-9AF0-1E4829C95CCE}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="78">
   <si>
     <t>AXP</t>
   </si>
@@ -259,7 +259,7 @@
     <t>Total service revenue</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -388,14 +388,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -412,8 +412,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9547860" y="0"/>
-          <a:ext cx="0" cy="9052560"/>
+          <a:off x="10759440" y="0"/>
+          <a:ext cx="0" cy="9235440"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -789,19 +789,21 @@
   <dimension ref="B2:K9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="8" width="13.88671875" style="1" customWidth="1"/>
+    <col min="1" max="4" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="11.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -813,17 +815,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="8">
-        <v>291.27999999999997</v>
+        <v>337.65</v>
+      </c>
+      <c r="E3" s="11">
+        <v>45918</v>
       </c>
       <c r="F3" s="11">
-        <v>45804</v>
+        <f ca="1">TODAY()</f>
+        <v>45918</v>
       </c>
       <c r="G3" s="11">
-        <f ca="1">TODAY()</f>
-        <v>45804</v>
-      </c>
-      <c r="H3" s="11">
-        <v>45856</v>
+        <v>45947</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -831,8 +833,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>700.6</f>
-        <v>700.6</v>
+        <f>695.9</f>
+        <v>695.9</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -841,7 +846,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>204070.76799999998</v>
+        <v>234970.63499999998</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -849,8 +854,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>52508</f>
-        <v>52508</v>
+        <f>57937</f>
+        <v>57937</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>63</v>
@@ -861,8 +869,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>1559+51236</f>
-        <v>52795</v>
+        <f>1493+58202</f>
+        <v>59695</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -871,7 +882,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-287</v>
+        <v>-1758</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -880,7 +891,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>204357.76799999998</v>
+        <v>236728.63499999998</v>
       </c>
     </row>
   </sheetData>
@@ -1046,11 +1057,10 @@
         <v>8743</v>
       </c>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:Q3" si="0">L3*1.06</f>
-        <v>9386.3000000000011</v>
+        <v>9361</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Q3" si="0">M3*1.06</f>
         <v>9306.8000000000011</v>
       </c>
       <c r="R3" s="3">
@@ -1074,47 +1084,47 @@
       </c>
       <c r="Z3" s="3">
         <f>SUM(O3:R3)</f>
-        <v>36980.180000000008</v>
+        <v>36954.880000000005</v>
       </c>
       <c r="AA3" s="3">
         <f>Z3*1.02</f>
-        <v>37719.78360000001</v>
+        <v>37693.977600000006</v>
       </c>
       <c r="AB3" s="3">
         <f>AA3*1.01</f>
-        <v>38096.981436000009</v>
+        <v>38070.917376000005</v>
       </c>
       <c r="AC3" s="3">
         <f t="shared" ref="AC3:AJ3" si="1">AB3*1.01</f>
-        <v>38477.951250360013</v>
+        <v>38451.626549760003</v>
       </c>
       <c r="AD3" s="3">
         <f t="shared" si="1"/>
-        <v>38862.730762863612</v>
+        <v>38836.142815257605</v>
       </c>
       <c r="AE3" s="3">
         <f t="shared" si="1"/>
-        <v>39251.35807049225</v>
+        <v>39224.504243410178</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" si="1"/>
-        <v>39643.871651197172</v>
+        <v>39616.749285844278</v>
       </c>
       <c r="AG3" s="3">
         <f t="shared" si="1"/>
-        <v>40040.310367709142</v>
+        <v>40012.916778702718</v>
       </c>
       <c r="AH3" s="3">
         <f t="shared" si="1"/>
-        <v>40440.713471386232</v>
+        <v>40413.045946489743</v>
       </c>
       <c r="AI3" s="3">
         <f t="shared" si="1"/>
-        <v>40845.120606100092</v>
+        <v>40817.17640595464</v>
       </c>
       <c r="AJ3" s="3">
         <f t="shared" si="1"/>
-        <v>41253.571812161092</v>
+        <v>41225.348170014186</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1161,16 +1171,15 @@
         <v>2333</v>
       </c>
       <c r="P4" s="3">
-        <f>L4*1.16</f>
-        <v>2389.6</v>
+        <v>2480</v>
       </c>
       <c r="Q4" s="3">
-        <f>M4*1.15</f>
-        <v>2495.5</v>
+        <f>M4*1.17</f>
+        <v>2538.8999999999996</v>
       </c>
       <c r="R4" s="3">
-        <f>N4*1.13</f>
-        <v>2536.85</v>
+        <f>N4*1.15</f>
+        <v>2581.75</v>
       </c>
       <c r="V4" s="3">
         <v>3851</v>
@@ -1189,47 +1198,47 @@
       </c>
       <c r="Z4" s="3">
         <f>SUM(O4:R4)</f>
-        <v>9754.9500000000007</v>
+        <v>9933.65</v>
       </c>
       <c r="AA4" s="3">
         <f>Z4*1.09</f>
-        <v>10632.895500000002</v>
+        <v>10827.6785</v>
       </c>
       <c r="AB4" s="3">
         <f>AA4*1.07</f>
-        <v>11377.198185000003</v>
+        <v>11585.615995</v>
       </c>
       <c r="AC4" s="3">
         <f>AB4*1.05</f>
-        <v>11946.058094250004</v>
+        <v>12164.89679475</v>
       </c>
       <c r="AD4" s="3">
         <f>AC4*1.04</f>
-        <v>12423.900418020005</v>
+        <v>12651.492666540002</v>
       </c>
       <c r="AE4" s="3">
         <f>AD4*1.03</f>
-        <v>12796.617430560605</v>
+        <v>13031.037446536202</v>
       </c>
       <c r="AF4" s="3">
         <f t="shared" ref="AF4:AJ4" si="2">AE4*1.02</f>
-        <v>13052.549779171817</v>
+        <v>13291.658195466925</v>
       </c>
       <c r="AG4" s="3">
         <f t="shared" si="2"/>
-        <v>13313.600774755254</v>
+        <v>13557.491359376265</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="2"/>
-        <v>13579.87279025036</v>
+        <v>13828.641186563791</v>
       </c>
       <c r="AI4" s="3">
         <f t="shared" si="2"/>
-        <v>13851.470246055367</v>
+        <v>14105.214010295067</v>
       </c>
       <c r="AJ4" s="3">
         <f t="shared" si="2"/>
-        <v>14128.499650976475</v>
+        <v>14387.318290500969</v>
       </c>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.3">
@@ -1273,17 +1282,14 @@
         <v>1290</v>
       </c>
       <c r="O5" s="3"/>
-      <c r="P5" s="3">
-        <f>L5*1.02</f>
-        <v>1305.5999999999999</v>
-      </c>
+      <c r="P5" s="3"/>
       <c r="Q5" s="3">
-        <f>M5*1.02</f>
-        <v>1292.3399999999999</v>
+        <f>M5*1.03</f>
+        <v>1305.01</v>
       </c>
       <c r="R5" s="3">
-        <f>N5*1.02</f>
-        <v>1315.8</v>
+        <f>N5*1.04</f>
+        <v>1341.6000000000001</v>
       </c>
       <c r="V5" s="3">
         <v>2182</v>
@@ -1353,17 +1359,14 @@
         <v>429</v>
       </c>
       <c r="O6" s="3"/>
-      <c r="P6" s="3">
-        <f>L6*1.04</f>
-        <v>424.32</v>
-      </c>
+      <c r="P6" s="3"/>
       <c r="Q6" s="3">
-        <f>M6*1.04</f>
-        <v>429.52000000000004</v>
+        <f>M6*1.05</f>
+        <v>433.65000000000003</v>
       </c>
       <c r="R6" s="3">
-        <f>N6*1.02</f>
-        <v>437.58</v>
+        <f>N6*1.03</f>
+        <v>441.87</v>
       </c>
       <c r="V6" s="3">
         <v>1146</v>
@@ -1408,23 +1411,25 @@
         <f>K5+K6</f>
         <v>1678</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <f>L5+L6</f>
+        <v>1688</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3">
         <v>1722</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" ref="P7:R7" si="3">P5+P6</f>
-        <v>1729.9199999999998</v>
+        <v>1828</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" si="3"/>
-        <v>1721.86</v>
+        <f t="shared" ref="Q7:R7" si="3">Q5+Q6</f>
+        <v>1738.66</v>
       </c>
       <c r="R7" s="3">
         <f t="shared" si="3"/>
-        <v>1753.3799999999999</v>
+        <v>1783.4700000000003</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1435,47 +1440,47 @@
       </c>
       <c r="Z7" s="3">
         <f>SUM(O7:R7)</f>
-        <v>6927.16</v>
+        <v>7072.13</v>
       </c>
       <c r="AA7" s="3">
-        <f>Z7*1.02</f>
-        <v>7065.7031999999999</v>
+        <f>Z7*1.03</f>
+        <v>7284.2939000000006</v>
       </c>
       <c r="AB7" s="3">
-        <f>AA7*1.01</f>
-        <v>7136.360232</v>
+        <f>AA7*1.02</f>
+        <v>7429.9797780000008</v>
       </c>
       <c r="AC7" s="3">
-        <f t="shared" ref="AC7:AJ7" si="4">AB7*1.01</f>
-        <v>7207.7238343199997</v>
+        <f>AB7*1.02</f>
+        <v>7578.5793735600009</v>
       </c>
       <c r="AD7" s="3">
-        <f t="shared" si="4"/>
-        <v>7279.8010726632001</v>
+        <f t="shared" ref="AD7:AE7" si="4">AC7*1.02</f>
+        <v>7730.1509610312014</v>
       </c>
       <c r="AE7" s="3">
         <f t="shared" si="4"/>
-        <v>7352.5990833898322</v>
+        <v>7884.7539802518259</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" si="4"/>
-        <v>7426.1250742237307</v>
+        <f t="shared" ref="AF7:AJ7" si="5">AE7*1.01</f>
+        <v>7963.6015200543443</v>
       </c>
       <c r="AG7" s="3">
-        <f t="shared" si="4"/>
-        <v>7500.386324965968</v>
+        <f t="shared" si="5"/>
+        <v>8043.2375352548879</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" si="4"/>
-        <v>7575.3901882156279</v>
+        <f t="shared" si="5"/>
+        <v>8123.6699106074366</v>
       </c>
       <c r="AI7" s="3">
-        <f t="shared" si="4"/>
-        <v>7651.1440900977841</v>
+        <f t="shared" si="5"/>
+        <v>8204.906609713511</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="4"/>
-        <v>7727.6555309987616</v>
+        <f t="shared" si="5"/>
+        <v>8286.9556758106464</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
@@ -1483,51 +1488,51 @@
         <v>16</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" ref="C8:N8" si="5">SUM(C3:C6)</f>
+        <f t="shared" ref="C8:N8" si="6">SUM(C3:C6)</f>
         <v>9536</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11035</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10978</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11418</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11298</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11949</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11939</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12195</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12032</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12603</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12630</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13141</v>
       </c>
       <c r="O8" s="3">
@@ -1535,16 +1540,16 @@
         <v>12798</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" ref="P8:R8" si="6">P3+P4+P7</f>
-        <v>13505.820000000002</v>
+        <f t="shared" ref="P8:R8" si="7">P3+P4+P7</f>
+        <v>13669</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="6"/>
-        <v>13524.160000000002</v>
+        <f t="shared" si="7"/>
+        <v>13584.36</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="6"/>
-        <v>13834.31</v>
+        <f t="shared" si="7"/>
+        <v>13909.3</v>
       </c>
       <c r="V8" s="3">
         <f>SUM(V3:V6)</f>
@@ -1563,48 +1568,48 @@
         <v>57171</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" ref="Z8:AJ8" si="7">SUM(Z3:Z7)</f>
-        <v>53662.290000000008</v>
+        <f t="shared" ref="Z8:AJ8" si="8">SUM(Z3:Z7)</f>
+        <v>53960.66</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" si="7"/>
-        <v>55418.382300000012</v>
+        <f t="shared" si="8"/>
+        <v>55805.950000000012</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="7"/>
-        <v>56610.539853000009</v>
+        <f t="shared" si="8"/>
+        <v>57086.513149000006</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="7"/>
-        <v>57631.733178930015</v>
+        <f t="shared" si="8"/>
+        <v>58195.102718070004</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="7"/>
-        <v>58566.432253546816</v>
+        <f t="shared" si="8"/>
+        <v>59217.786442828809</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="7"/>
-        <v>59400.574584442686</v>
+        <f t="shared" si="8"/>
+        <v>60140.295670198204</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="7"/>
-        <v>60122.546504592719</v>
+        <f t="shared" si="8"/>
+        <v>60872.009001365543</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="7"/>
-        <v>60854.297467430362</v>
+        <f t="shared" si="8"/>
+        <v>61613.645673333871</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="7"/>
-        <v>61595.97644985222</v>
+        <f t="shared" si="8"/>
+        <v>62365.357043660973</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="7"/>
-        <v>62347.734942253242</v>
+        <f t="shared" si="8"/>
+        <v>63127.297025963213</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="7"/>
-        <v>63109.726994136327</v>
+        <f t="shared" si="8"/>
+        <v>63899.622136325801</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.3">
@@ -1651,8 +1656,7 @@
         <v>6135</v>
       </c>
       <c r="P9" s="3">
-        <f>L9*1.06</f>
-        <v>6141.64</v>
+        <v>6264</v>
       </c>
       <c r="Q9" s="3">
         <f>M9*1.02</f>
@@ -1679,47 +1683,47 @@
       </c>
       <c r="Z9" s="3">
         <f>SUM(O9:R9)</f>
-        <v>24868.699999999997</v>
+        <v>24991.059999999998</v>
       </c>
       <c r="AA9" s="3">
-        <f>Z9*1.05</f>
-        <v>26112.134999999998</v>
+        <f>Z9*1.04</f>
+        <v>25990.702399999998</v>
       </c>
       <c r="AB9" s="3">
         <f>AA9*1.03</f>
-        <v>26895.499049999999</v>
+        <v>26770.423471999999</v>
       </c>
       <c r="AC9" s="3">
         <f>AB9*1.02</f>
-        <v>27433.409030999999</v>
+        <v>27305.831941439999</v>
       </c>
       <c r="AD9" s="3">
         <f>AC9*1.01</f>
-        <v>27707.743121309999</v>
+        <v>27578.890260854401</v>
       </c>
       <c r="AE9" s="3">
-        <f t="shared" ref="AE9:AJ9" si="8">AD9*1.01</f>
-        <v>27984.820552523099</v>
+        <f t="shared" ref="AE9:AJ9" si="9">AD9*1.01</f>
+        <v>27854.679163462944</v>
       </c>
       <c r="AF9" s="3">
-        <f t="shared" si="8"/>
-        <v>28264.66875804833</v>
+        <f t="shared" si="9"/>
+        <v>28133.225955097572</v>
       </c>
       <c r="AG9" s="3">
-        <f t="shared" si="8"/>
-        <v>28547.315445628814</v>
+        <f t="shared" si="9"/>
+        <v>28414.558214648547</v>
       </c>
       <c r="AH9" s="3">
-        <f t="shared" si="8"/>
-        <v>28832.788600085103</v>
+        <f t="shared" si="9"/>
+        <v>28698.703796795031</v>
       </c>
       <c r="AI9" s="3">
-        <f t="shared" si="8"/>
-        <v>29121.116486085954</v>
+        <f t="shared" si="9"/>
+        <v>28985.690834762983</v>
       </c>
       <c r="AJ9" s="3">
-        <f t="shared" si="8"/>
-        <v>29412.327650946812</v>
+        <f t="shared" si="9"/>
+        <v>29275.547743110612</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1766,15 +1770,14 @@
         <v>1966</v>
       </c>
       <c r="P10" s="3">
-        <f>L10*0.99</f>
-        <v>2043.36</v>
+        <v>2077</v>
       </c>
       <c r="Q10" s="3">
         <f>M10*0.98</f>
         <v>2100.14</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" ref="R10" si="9">N10*0.99</f>
+        <f t="shared" ref="R10" si="10">N10*0.99</f>
         <v>2018.61</v>
       </c>
       <c r="V10" s="3">
@@ -1789,52 +1792,52 @@
         <v>6849</v>
       </c>
       <c r="Y10" s="3">
-        <f t="shared" ref="Y10" si="10">SUM(K10:N10)</f>
+        <f t="shared" ref="Y10" si="11">SUM(K10:N10)</f>
         <v>8252</v>
       </c>
       <c r="Z10" s="3">
         <f>SUM(O10:R10)</f>
-        <v>8128.11</v>
+        <v>8161.7499999999991</v>
       </c>
       <c r="AA10" s="3">
         <f>Z10*1.05</f>
-        <v>8534.5154999999995</v>
+        <v>8569.8374999999996</v>
       </c>
       <c r="AB10" s="3">
         <f>AA10*1.03</f>
-        <v>8790.5509650000004</v>
+        <v>8826.9326249999995</v>
       </c>
       <c r="AC10" s="3">
         <f>AB10*1.02</f>
-        <v>8966.3619842999997</v>
+        <v>9003.4712774999989</v>
       </c>
       <c r="AD10" s="3">
         <f>AC10*1.01</f>
-        <v>9056.0256041430002</v>
+        <v>9093.5059902749981</v>
       </c>
       <c r="AE10" s="3">
-        <f t="shared" ref="AE10:AJ10" si="11">AD10*1.01</f>
-        <v>9146.5858601844302</v>
+        <f t="shared" ref="AE10:AJ10" si="12">AD10*1.01</f>
+        <v>9184.4410501777475</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" si="11"/>
-        <v>9238.0517187862752</v>
+        <f t="shared" si="12"/>
+        <v>9276.2854606795245</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" si="11"/>
-        <v>9330.4322359741382</v>
+        <f t="shared" si="12"/>
+        <v>9369.0483152863198</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="11"/>
-        <v>9423.7365583338797</v>
+        <f t="shared" si="12"/>
+        <v>9462.7387984391826</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="11"/>
-        <v>9517.9739239172177</v>
+        <f t="shared" si="12"/>
+        <v>9557.3661864235746</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="11"/>
-        <v>9613.1536631563904</v>
+        <f t="shared" si="12"/>
+        <v>9652.9398482878096</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1842,67 +1845,67 @@
         <v>18</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:R11" si="12">C9-C10</f>
+        <f t="shared" ref="C11:R11" si="13">C9-C10</f>
         <v>2199</v>
       </c>
       <c r="D11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2360</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2578</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2758</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2983</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3105</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3442</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3604</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3769</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3730</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4006</v>
       </c>
       <c r="N11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4038</v>
       </c>
       <c r="O11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4169</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="12"/>
-        <v>4098.2800000000007</v>
+        <f t="shared" si="13"/>
+        <v>4187</v>
       </c>
       <c r="Q11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4171.84</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4301.47</v>
       </c>
       <c r="V11" s="3">
@@ -1918,52 +1921,52 @@
         <v>13134</v>
       </c>
       <c r="Y11" s="3">
-        <f t="shared" ref="Y11:AJ11" si="13">Y9-Y10</f>
+        <f t="shared" ref="Y11:AJ11" si="14">Y9-Y10</f>
         <v>15543</v>
       </c>
       <c r="Z11" s="3">
-        <f t="shared" si="13"/>
-        <v>16740.589999999997</v>
+        <f t="shared" si="14"/>
+        <v>16829.309999999998</v>
       </c>
       <c r="AA11" s="3">
-        <f t="shared" si="13"/>
-        <v>17577.619500000001</v>
+        <f t="shared" si="14"/>
+        <v>17420.8649</v>
       </c>
       <c r="AB11" s="3">
-        <f t="shared" si="13"/>
-        <v>18104.948084999996</v>
+        <f t="shared" si="14"/>
+        <v>17943.490847000001</v>
       </c>
       <c r="AC11" s="3">
-        <f t="shared" si="13"/>
-        <v>18467.047046699998</v>
+        <f t="shared" si="14"/>
+        <v>18302.360663940002</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="13"/>
-        <v>18651.717517166999</v>
+        <f t="shared" si="14"/>
+        <v>18485.384270579401</v>
       </c>
       <c r="AE11" s="3">
-        <f t="shared" si="13"/>
-        <v>18838.234692338669</v>
+        <f t="shared" si="14"/>
+        <v>18670.238113285195</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="13"/>
-        <v>19026.617039262055</v>
+        <f t="shared" si="14"/>
+        <v>18856.94049441805</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="13"/>
-        <v>19216.883209654676</v>
+        <f t="shared" si="14"/>
+        <v>19045.509899362227</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="13"/>
-        <v>19409.052041751223</v>
+        <f t="shared" si="14"/>
+        <v>19235.964998355848</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="13"/>
-        <v>19603.142562168738</v>
+        <f t="shared" si="14"/>
+        <v>19428.32464833941</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="13"/>
-        <v>19799.173987790422</v>
+        <f t="shared" si="14"/>
+        <v>19622.607894822802</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
@@ -2009,7 +2012,9 @@
       <c r="O12" s="3">
         <v>146</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <v>226</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="V12" s="3">
@@ -2082,7 +2087,9 @@
       <c r="O13" s="3">
         <v>901</v>
       </c>
-      <c r="P13" s="3"/>
+      <c r="P13" s="3">
+        <v>1094</v>
+      </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="V13" s="3">
@@ -2155,7 +2162,9 @@
       <c r="O14" s="3">
         <v>103</v>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3">
+        <v>85</v>
+      </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="V14" s="3">
@@ -2190,58 +2199,61 @@
         <v>22</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:O15" si="14">SUM(C12:C14)</f>
+        <f t="shared" ref="C15:P15" si="15">SUM(C12:C14)</f>
         <v>-33</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>410</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>778</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1027</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1055</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1198</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1233</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1437</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1269</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1268</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1356</v>
       </c>
       <c r="N15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1292</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1150</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="15"/>
+        <v>1405</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="V15" s="3">
@@ -2277,68 +2289,68 @@
         <v>23</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:R16" si="15">C8+C9</f>
+        <f t="shared" ref="C16:R16" si="16">C8+C9</f>
         <v>12056</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13834</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14352</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15383</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15714</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>16724</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>17179</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>17747</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>17807</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18397</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18779</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>19218</v>
       </c>
       <c r="O16" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>18933</v>
       </c>
       <c r="P16" s="5">
-        <f t="shared" si="15"/>
-        <v>19647.460000000003</v>
+        <f t="shared" si="16"/>
+        <v>19933</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="15"/>
-        <v>19796.140000000003</v>
+        <f t="shared" si="16"/>
+        <v>19856.34</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="15"/>
-        <v>20154.39</v>
+        <f t="shared" si="16"/>
+        <v>20229.379999999997</v>
       </c>
       <c r="V16" s="5">
         <f>V8+V9</f>
@@ -2358,47 +2370,47 @@
       </c>
       <c r="Z16" s="5">
         <f>Z8+Z9</f>
-        <v>78530.990000000005</v>
+        <v>78951.72</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AJ16" si="16">AA8+AA9</f>
-        <v>81530.517300000007</v>
+        <f t="shared" ref="AA16:AJ16" si="17">AA8+AA9</f>
+        <v>81796.652400000006</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" si="16"/>
-        <v>83506.038903000008</v>
+        <f t="shared" si="17"/>
+        <v>83856.936621000001</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="16"/>
-        <v>85065.142209930011</v>
+        <f t="shared" si="17"/>
+        <v>85500.934659510007</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="16"/>
-        <v>86274.175374856815</v>
+        <f t="shared" si="17"/>
+        <v>86796.676703683217</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="16"/>
-        <v>87385.395136965788</v>
+        <f t="shared" si="17"/>
+        <v>87994.974833661152</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="16"/>
-        <v>88387.215262641053</v>
+        <f t="shared" si="17"/>
+        <v>89005.234956463115</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="16"/>
-        <v>89401.612913059173</v>
+        <f t="shared" si="17"/>
+        <v>90028.20388798241</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="16"/>
-        <v>90428.765049937327</v>
+        <f t="shared" si="17"/>
+        <v>91064.060840456004</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="16"/>
-        <v>91468.8514283392</v>
+        <f t="shared" si="17"/>
+        <v>92112.987860726193</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="16"/>
-        <v>92522.054645083146</v>
+        <f t="shared" si="17"/>
+        <v>93175.169879436406</v>
       </c>
     </row>
     <row r="17" spans="2:153" x14ac:dyDescent="0.3">
@@ -2444,7 +2456,9 @@
       <c r="O17" s="3">
         <v>4378</v>
       </c>
-      <c r="P17" s="3"/>
+      <c r="P17" s="3">
+        <v>4618</v>
+      </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="V17" s="3">
@@ -2459,7 +2473,7 @@
         <v>15367</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" ref="Y17:Y19" si="17">SUM(K17:N17)</f>
+        <f t="shared" ref="Y17:Y19" si="18">SUM(K17:N17)</f>
         <v>16599</v>
       </c>
       <c r="Z17" s="3"/>
@@ -2517,7 +2531,9 @@
       <c r="O18" s="3">
         <v>1529</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <v>1589</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="V18" s="3">
@@ -2532,7 +2548,7 @@
         <v>5657</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5886</v>
       </c>
       <c r="Z18" s="3"/>
@@ -2590,7 +2606,9 @@
       <c r="O19" s="3">
         <v>1328</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <v>1301</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="V19" s="3">
@@ -2605,7 +2623,7 @@
         <v>3968</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>4782</v>
       </c>
       <c r="Z19" s="3"/>
@@ -2625,68 +2643,68 @@
         <v>27</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:O20" si="18">SUM(C17:C19)+C15+C10</f>
+        <f t="shared" ref="C20:P20" si="19">SUM(C17:C19)+C15+C10</f>
         <v>5068</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>6522</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7113</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8146</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8630</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9161</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9191</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9782</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>9612</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10140</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10276</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10676</v>
       </c>
       <c r="O20" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10351</v>
       </c>
       <c r="P20" s="3">
-        <f>P16*0.55</f>
-        <v>10806.103000000003</v>
+        <f t="shared" si="19"/>
+        <v>10990</v>
       </c>
       <c r="Q20" s="3">
         <f>Q16*0.55</f>
-        <v>10887.877000000002</v>
+        <v>10920.987000000001</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" ref="R20" si="19">R16*0.56</f>
-        <v>11286.458400000001</v>
+        <f t="shared" ref="R20" si="20">R16*0.56</f>
+        <v>11328.452799999999</v>
       </c>
       <c r="V20" s="3">
         <f>SUM(V17:V19)+V15+V10</f>
@@ -2706,47 +2724,47 @@
       </c>
       <c r="Z20" s="3">
         <f>SUM(O20:R20)</f>
-        <v>43331.438400000006</v>
+        <v>43590.4398</v>
       </c>
       <c r="AA20" s="3">
-        <f t="shared" ref="AA20:AJ20" si="20">AA16-AA21</f>
-        <v>44841.784514999999</v>
+        <f t="shared" ref="AA20:AJ20" si="21">AA16-AA21</f>
+        <v>44988.158820000004</v>
       </c>
       <c r="AB20" s="3">
-        <f t="shared" si="20"/>
-        <v>45928.321396650004</v>
+        <f t="shared" si="21"/>
+        <v>46121.315141549996</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" si="20"/>
-        <v>46785.828215461508</v>
+        <f t="shared" si="21"/>
+        <v>47025.514062730501</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="20"/>
-        <v>47450.796456171251</v>
+        <f t="shared" si="21"/>
+        <v>47738.172187025768</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="20"/>
-        <v>48061.967325331185</v>
+        <f t="shared" si="21"/>
+        <v>48397.236158513631</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="20"/>
-        <v>48612.968394452575</v>
+        <f t="shared" si="21"/>
+        <v>48952.879226054712</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="20"/>
-        <v>49170.887102182547</v>
+        <f t="shared" si="21"/>
+        <v>49515.512138390324</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="20"/>
-        <v>49735.820777465531</v>
+        <f t="shared" si="21"/>
+        <v>50085.233462250799</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="20"/>
-        <v>50307.868285586555</v>
+        <f t="shared" si="21"/>
+        <v>50662.143323399403</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="20"/>
-        <v>50887.130054795729</v>
+        <f t="shared" si="21"/>
+        <v>51246.343433690025</v>
       </c>
     </row>
     <row r="21" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2754,68 +2772,68 @@
         <v>28</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" ref="C21:R21" si="21">C16-C20</f>
+        <f t="shared" ref="C21:R21" si="22">C16-C20</f>
         <v>6988</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7312</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7239</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7237</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7084</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7563</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7988</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7965</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8195</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8257</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8503</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8542</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8582</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="21"/>
-        <v>8841.357</v>
+        <f t="shared" si="22"/>
+        <v>8943</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="21"/>
-        <v>8908.2630000000008</v>
+        <f t="shared" si="22"/>
+        <v>8935.3529999999992</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="21"/>
-        <v>8867.9315999999981</v>
+        <f t="shared" si="22"/>
+        <v>8900.9271999999983</v>
       </c>
       <c r="V21" s="5">
         <f>V16-V20</f>
@@ -2835,47 +2853,47 @@
       </c>
       <c r="Z21" s="5">
         <f>Z16-Z20</f>
-        <v>35199.551599999999</v>
+        <v>35361.280200000001</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" ref="AA21:AJ21" si="22">AA16*0.45</f>
-        <v>36688.732785000007</v>
+        <f t="shared" ref="AA21:AJ21" si="23">AA16*0.45</f>
+        <v>36808.493580000002</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="22"/>
-        <v>37577.717506350004</v>
+        <f t="shared" si="23"/>
+        <v>37735.621479450005</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="22"/>
-        <v>38279.313994468503</v>
+        <f t="shared" si="23"/>
+        <v>38475.420596779506</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="22"/>
-        <v>38823.378918685565</v>
+        <f t="shared" si="23"/>
+        <v>39058.504516657449</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="22"/>
-        <v>39323.427811634603</v>
+        <f t="shared" si="23"/>
+        <v>39597.738675147521</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="22"/>
-        <v>39774.246868188478</v>
+        <f t="shared" si="23"/>
+        <v>40052.355730408402</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="22"/>
-        <v>40230.725810876625</v>
+        <f t="shared" si="23"/>
+        <v>40512.691749592086</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="22"/>
-        <v>40692.944272471796</v>
+        <f t="shared" si="23"/>
+        <v>40978.827378205206</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="22"/>
-        <v>41160.983142752644</v>
+        <f t="shared" si="23"/>
+        <v>41450.84453732679</v>
       </c>
       <c r="AJ21" s="5">
-        <f t="shared" si="22"/>
-        <v>41634.924590287417</v>
+        <f t="shared" si="23"/>
+        <v>41928.826445746381</v>
       </c>
     </row>
     <row r="22" spans="2:153" x14ac:dyDescent="0.3">
@@ -2922,16 +2940,15 @@
         <v>1486</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" ref="P22:R22" si="23">P16*0.08</f>
-        <v>1571.7968000000003</v>
+        <v>1555</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" si="23"/>
-        <v>1583.6912000000002</v>
+        <f t="shared" ref="Q22:R22" si="24">Q16*0.08</f>
+        <v>1588.5072</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="23"/>
-        <v>1612.3512000000001</v>
+        <f t="shared" si="24"/>
+        <v>1618.3503999999998</v>
       </c>
       <c r="V22" s="3">
         <v>3706</v>
@@ -2950,47 +2967,47 @@
       </c>
       <c r="Z22" s="3">
         <f>SUM(O22:R22)</f>
-        <v>6253.8392000000003</v>
+        <v>6247.8575999999994</v>
       </c>
       <c r="AA22" s="3">
-        <f t="shared" ref="AA22:AJ22" si="24">AA16*0.08</f>
-        <v>6522.4413840000007</v>
+        <f t="shared" ref="AA22:AJ22" si="25">AA16*0.08</f>
+        <v>6543.7321920000004</v>
       </c>
       <c r="AB22" s="3">
-        <f t="shared" si="24"/>
-        <v>6680.483112240001</v>
+        <f t="shared" si="25"/>
+        <v>6708.55492968</v>
       </c>
       <c r="AC22" s="3">
-        <f t="shared" si="24"/>
-        <v>6805.2113767944011</v>
+        <f t="shared" si="25"/>
+        <v>6840.0747727608004</v>
       </c>
       <c r="AD22" s="3">
-        <f t="shared" si="24"/>
-        <v>6901.9340299885453</v>
+        <f t="shared" si="25"/>
+        <v>6943.7341362946572</v>
       </c>
       <c r="AE22" s="3">
-        <f t="shared" si="24"/>
-        <v>6990.8316109572634</v>
+        <f t="shared" si="25"/>
+        <v>7039.5979866928919</v>
       </c>
       <c r="AF22" s="3">
-        <f t="shared" si="24"/>
-        <v>7070.9772210112842</v>
+        <f t="shared" si="25"/>
+        <v>7120.4187965170495</v>
       </c>
       <c r="AG22" s="3">
-        <f t="shared" si="24"/>
-        <v>7152.1290330447337</v>
+        <f t="shared" si="25"/>
+        <v>7202.2563110385927</v>
       </c>
       <c r="AH22" s="3">
-        <f t="shared" si="24"/>
-        <v>7234.3012039949863</v>
+        <f t="shared" si="25"/>
+        <v>7285.1248672364809</v>
       </c>
       <c r="AI22" s="3">
-        <f t="shared" si="24"/>
-        <v>7317.5081142671361</v>
+        <f t="shared" si="25"/>
+        <v>7369.0390288580957</v>
       </c>
       <c r="AJ22" s="3">
-        <f t="shared" si="24"/>
-        <v>7401.7643716066523</v>
+        <f t="shared" si="25"/>
+        <v>7454.0135903549126</v>
       </c>
     </row>
     <row r="23" spans="2:153" x14ac:dyDescent="0.3">
@@ -3037,16 +3054,15 @@
         <v>2120</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" ref="P23" si="25">L23*0.99</f>
-        <v>1929.51</v>
+        <v>2152</v>
       </c>
       <c r="Q23" s="3">
-        <f>M23*1.01</f>
-        <v>2069.4900000000002</v>
+        <f>M23*1.07</f>
+        <v>2192.4300000000003</v>
       </c>
       <c r="R23" s="3">
-        <f>N23*1.01</f>
-        <v>2123.02</v>
+        <f>N23*1.05</f>
+        <v>2207.1</v>
       </c>
       <c r="V23" s="3">
         <v>4586</v>
@@ -3065,47 +3081,47 @@
       </c>
       <c r="Z23" s="3">
         <f>SUM(O23:R23)</f>
-        <v>8242.02</v>
+        <v>8671.5300000000007</v>
       </c>
       <c r="AA23" s="3">
-        <f>Z23*1.02</f>
-        <v>8406.8604000000014</v>
+        <f>Z23*1.04</f>
+        <v>9018.3912000000018</v>
       </c>
       <c r="AB23" s="3">
-        <f>AA23*1.01</f>
-        <v>8490.9290040000014</v>
+        <f>AA23*1.03</f>
+        <v>9288.9429360000013</v>
       </c>
       <c r="AC23" s="3">
-        <f t="shared" ref="AC23:AJ23" si="26">AB23*1.01</f>
-        <v>8575.8382940400024</v>
+        <f>AB23*1.02</f>
+        <v>9474.7217947200006</v>
       </c>
       <c r="AD23" s="3">
-        <f t="shared" si="26"/>
-        <v>8661.5966769804018</v>
+        <f t="shared" ref="AD23:AJ23" si="26">AC23*1.01</f>
+        <v>9569.4690126672012</v>
       </c>
       <c r="AE23" s="3">
         <f t="shared" si="26"/>
-        <v>8748.2126437502066</v>
+        <v>9665.1637027938741</v>
       </c>
       <c r="AF23" s="3">
         <f t="shared" si="26"/>
-        <v>8835.6947701877089</v>
+        <v>9761.8153398218128</v>
       </c>
       <c r="AG23" s="3">
         <f t="shared" si="26"/>
-        <v>8924.0517178895861</v>
+        <v>9859.4334932200309</v>
       </c>
       <c r="AH23" s="3">
         <f t="shared" si="26"/>
-        <v>9013.2922350684821</v>
+        <v>9958.0278281522315</v>
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="26"/>
-        <v>9103.4251574191676</v>
+        <v>10057.608106433754</v>
       </c>
       <c r="AJ23" s="3">
         <f t="shared" si="26"/>
-        <v>9194.4594089933598</v>
+        <v>10158.184187498091</v>
       </c>
     </row>
     <row r="24" spans="2:153" x14ac:dyDescent="0.3">
@@ -3159,16 +3175,15 @@
         <v>1646</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" ref="P24:Q24" si="27">P16*0.08</f>
-        <v>1571.7968000000003</v>
+        <v>1686</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="27"/>
-        <v>1583.6912000000002</v>
+        <f t="shared" ref="Q24" si="27">Q16*0.08</f>
+        <v>1588.5072</v>
       </c>
       <c r="R24" s="3">
         <f>R16*0.11</f>
-        <v>2216.9829</v>
+        <v>2225.2317999999996</v>
       </c>
       <c r="V24" s="3">
         <f>1351+1772-28</f>
@@ -3188,47 +3203,47 @@
       </c>
       <c r="Z24" s="3">
         <f>SUM(O24:R24)</f>
-        <v>7018.4709000000003</v>
+        <v>7145.7389999999996</v>
       </c>
       <c r="AA24" s="3">
         <f t="shared" ref="AA24:AJ24" si="28">AA16*0.08</f>
-        <v>6522.4413840000007</v>
+        <v>6543.7321920000004</v>
       </c>
       <c r="AB24" s="3">
         <f t="shared" si="28"/>
-        <v>6680.483112240001</v>
+        <v>6708.55492968</v>
       </c>
       <c r="AC24" s="3">
         <f t="shared" si="28"/>
-        <v>6805.2113767944011</v>
+        <v>6840.0747727608004</v>
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="28"/>
-        <v>6901.9340299885453</v>
+        <v>6943.7341362946572</v>
       </c>
       <c r="AE24" s="3">
         <f t="shared" si="28"/>
-        <v>6990.8316109572634</v>
+        <v>7039.5979866928919</v>
       </c>
       <c r="AF24" s="3">
         <f t="shared" si="28"/>
-        <v>7070.9772210112842</v>
+        <v>7120.4187965170495</v>
       </c>
       <c r="AG24" s="3">
         <f t="shared" si="28"/>
-        <v>7152.1290330447337</v>
+        <v>7202.2563110385927</v>
       </c>
       <c r="AH24" s="3">
         <f t="shared" si="28"/>
-        <v>7234.3012039949863</v>
+        <v>7285.1248672364809</v>
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="28"/>
-        <v>7317.5081142671361</v>
+        <v>7369.0390288580957</v>
       </c>
       <c r="AJ24" s="3">
         <f t="shared" si="28"/>
-        <v>7401.7643716066523</v>
+        <v>7454.0135903549126</v>
       </c>
     </row>
     <row r="25" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3289,15 +3304,15 @@
       </c>
       <c r="P25" s="5">
         <f t="shared" si="30"/>
-        <v>3768.2533999999996</v>
+        <v>3550</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="30"/>
-        <v>3671.3906000000006</v>
+        <v>3565.9085999999988</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" si="30"/>
-        <v>2915.5774999999976</v>
+        <v>2850.244999999999</v>
       </c>
       <c r="V25" s="5">
         <f>V21-SUM(V22:V24)</f>
@@ -3317,47 +3332,47 @@
       </c>
       <c r="Z25" s="5">
         <f t="shared" ref="Z25:AJ25" si="31">Z21-SUM(Z22:Z24)</f>
-        <v>13685.2215</v>
+        <v>13296.153600000001</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="31"/>
-        <v>15236.989617000003</v>
+        <v>14702.637996000001</v>
       </c>
       <c r="AB25" s="5">
         <f t="shared" si="31"/>
-        <v>15725.82227787</v>
+        <v>15029.568684090002</v>
       </c>
       <c r="AC25" s="5">
         <f t="shared" si="31"/>
-        <v>16093.0529468397</v>
+        <v>15320.549256537906</v>
       </c>
       <c r="AD25" s="5">
         <f t="shared" si="31"/>
-        <v>16357.914181728072</v>
+        <v>15601.567231400932</v>
       </c>
       <c r="AE25" s="5">
         <f t="shared" si="31"/>
-        <v>16593.55194596987</v>
+        <v>15853.378998967863</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="31"/>
-        <v>16796.597655978199</v>
+        <v>16049.702797552491</v>
       </c>
       <c r="AG25" s="5">
         <f t="shared" si="31"/>
-        <v>17002.416026897572</v>
+        <v>16248.745634294868</v>
       </c>
       <c r="AH25" s="5">
         <f t="shared" si="31"/>
-        <v>17211.049629413341</v>
+        <v>16450.549815580012</v>
       </c>
       <c r="AI25" s="5">
         <f t="shared" si="31"/>
-        <v>17422.541756799204</v>
+        <v>16655.158373176844</v>
       </c>
       <c r="AJ25" s="5">
         <f t="shared" si="31"/>
-        <v>17636.936438080753</v>
+        <v>16862.615077538463</v>
       </c>
     </row>
     <row r="26" spans="2:153" x14ac:dyDescent="0.3">
@@ -3404,16 +3419,15 @@
         <v>746</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" ref="P26:R26" si="32">P25*0.21</f>
-        <v>791.33321399999988</v>
+        <v>665</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" si="32"/>
-        <v>770.99202600000012</v>
+        <f t="shared" ref="Q26:R26" si="32">Q25*0.21</f>
+        <v>748.8408059999997</v>
       </c>
       <c r="R26" s="3">
         <f t="shared" si="32"/>
-        <v>612.27127499999949</v>
+        <v>598.55144999999982</v>
       </c>
       <c r="V26" s="3">
         <v>2042</v>
@@ -3432,47 +3446,47 @@
       </c>
       <c r="Z26" s="3">
         <f>SUM(O26:R26)</f>
-        <v>2920.5965149999997</v>
+        <v>2758.3922559999996</v>
       </c>
       <c r="AA26" s="3">
         <f t="shared" ref="AA26:AJ26" si="33">AA25*0.2</f>
-        <v>3047.3979234000008</v>
+        <v>2940.5275992000006</v>
       </c>
       <c r="AB26" s="3">
         <f t="shared" si="33"/>
-        <v>3145.1644555740004</v>
+        <v>3005.9137368180004</v>
       </c>
       <c r="AC26" s="3">
         <f t="shared" si="33"/>
-        <v>3218.6105893679401</v>
+        <v>3064.1098513075813</v>
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="33"/>
-        <v>3271.5828363456149</v>
+        <v>3120.3134462801863</v>
       </c>
       <c r="AE26" s="3">
         <f t="shared" si="33"/>
-        <v>3318.7103891939742</v>
+        <v>3170.6757997935729</v>
       </c>
       <c r="AF26" s="3">
         <f t="shared" si="33"/>
-        <v>3359.3195311956401</v>
+        <v>3209.9405595104981</v>
       </c>
       <c r="AG26" s="3">
         <f t="shared" si="33"/>
-        <v>3400.4832053795144</v>
+        <v>3249.7491268589738</v>
       </c>
       <c r="AH26" s="3">
         <f t="shared" si="33"/>
-        <v>3442.2099258826684</v>
+        <v>3290.1099631160027</v>
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="33"/>
-        <v>3484.5083513598411</v>
+        <v>3331.0316746353692</v>
       </c>
       <c r="AJ26" s="3">
         <f t="shared" si="33"/>
-        <v>3527.3872876161508</v>
+        <v>3372.5230155076929</v>
       </c>
     </row>
     <row r="27" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3533,15 +3547,15 @@
       </c>
       <c r="P27" s="5">
         <f t="shared" si="36"/>
-        <v>2976.9201859999998</v>
+        <v>2885</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="36"/>
-        <v>2900.3985740000007</v>
+        <v>2817.0677939999991</v>
       </c>
       <c r="R27" s="5">
         <f t="shared" si="36"/>
-        <v>2303.306224999998</v>
+        <v>2251.693549999999</v>
       </c>
       <c r="V27" s="5">
         <f>V25-V26</f>
@@ -3561,515 +3575,515 @@
       </c>
       <c r="Z27" s="5">
         <f>Z25-Z26</f>
-        <v>10764.624985</v>
+        <v>10537.761344000002</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" ref="AA27:AJ27" si="37">AA25-AA26</f>
-        <v>12189.591693600003</v>
+        <v>11762.110396800001</v>
       </c>
       <c r="AB27" s="5">
         <f t="shared" si="37"/>
-        <v>12580.657822296</v>
+        <v>12023.654947272002</v>
       </c>
       <c r="AC27" s="5">
         <f t="shared" si="37"/>
-        <v>12874.44235747176</v>
+        <v>12256.439405230325</v>
       </c>
       <c r="AD27" s="5">
         <f t="shared" si="37"/>
-        <v>13086.331345382458</v>
+        <v>12481.253785120745</v>
       </c>
       <c r="AE27" s="5">
         <f t="shared" si="37"/>
-        <v>13274.841556775897</v>
+        <v>12682.70319917429</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="37"/>
-        <v>13437.278124782559</v>
+        <v>12839.762238041993</v>
       </c>
       <c r="AG27" s="5">
         <f t="shared" si="37"/>
-        <v>13601.932821518058</v>
+        <v>12998.996507435895</v>
       </c>
       <c r="AH27" s="5">
         <f t="shared" si="37"/>
-        <v>13768.839703530673</v>
+        <v>13160.439852464009</v>
       </c>
       <c r="AI27" s="5">
         <f t="shared" si="37"/>
-        <v>13938.033405439364</v>
+        <v>13324.126698541475</v>
       </c>
       <c r="AJ27" s="5">
         <f t="shared" si="37"/>
-        <v>14109.549150464602</v>
+        <v>13490.09206203077</v>
       </c>
       <c r="AK27" s="4">
         <f>AJ27*(1+$AN$39)</f>
-        <v>13968.453658959956</v>
+        <v>13355.191141410462</v>
       </c>
       <c r="AL27" s="4">
         <f t="shared" ref="AL27:CW27" si="38">AK27*(1+$AN$39)</f>
-        <v>13828.769122370357</v>
+        <v>13221.639229996357</v>
       </c>
       <c r="AM27" s="4">
         <f t="shared" si="38"/>
-        <v>13690.481431146653</v>
+        <v>13089.422837696393</v>
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="38"/>
-        <v>13553.576616835186</v>
+        <v>12958.528609319428</v>
       </c>
       <c r="AO27" s="4">
         <f t="shared" si="38"/>
-        <v>13418.040850666834</v>
+        <v>12828.943323226234</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="38"/>
-        <v>13283.860442160165</v>
+        <v>12700.653889993971</v>
       </c>
       <c r="AQ27" s="4">
         <f t="shared" si="38"/>
-        <v>13151.021837738563</v>
+        <v>12573.647351094032</v>
       </c>
       <c r="AR27" s="4">
         <f t="shared" si="38"/>
-        <v>13019.511619361178</v>
+        <v>12447.910877583092</v>
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="38"/>
-        <v>12889.316503167565</v>
+        <v>12323.431768807261</v>
       </c>
       <c r="AT27" s="4">
         <f t="shared" si="38"/>
-        <v>12760.42333813589</v>
+        <v>12200.197451119187</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="38"/>
-        <v>12632.819104754532</v>
+        <v>12078.195476607996</v>
       </c>
       <c r="AV27" s="4">
         <f t="shared" si="38"/>
-        <v>12506.490913706986</v>
+        <v>11957.413521841916</v>
       </c>
       <c r="AW27" s="4">
         <f t="shared" si="38"/>
-        <v>12381.426004569916</v>
+        <v>11837.839386623496</v>
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="38"/>
-        <v>12257.611744524216</v>
+        <v>11719.460992757262</v>
       </c>
       <c r="AY27" s="4">
         <f t="shared" si="38"/>
-        <v>12135.035627078974</v>
+        <v>11602.26638282969</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="38"/>
-        <v>12013.685270808184</v>
+        <v>11486.243719001393</v>
       </c>
       <c r="BA27" s="4">
         <f t="shared" si="38"/>
-        <v>11893.548418100103</v>
+        <v>11371.38128181138</v>
       </c>
       <c r="BB27" s="4">
         <f t="shared" si="38"/>
-        <v>11774.612933919101</v>
+        <v>11257.667468993266</v>
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="38"/>
-        <v>11656.86680457991</v>
+        <v>11145.090794303333</v>
       </c>
       <c r="BD27" s="4">
         <f t="shared" si="38"/>
-        <v>11540.298136534111</v>
+        <v>11033.639886360299</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="38"/>
-        <v>11424.89515516877</v>
+        <v>10923.303487496696</v>
       </c>
       <c r="BF27" s="4">
         <f t="shared" si="38"/>
-        <v>11310.646203617081</v>
+        <v>10814.070452621729</v>
       </c>
       <c r="BG27" s="4">
         <f t="shared" si="38"/>
-        <v>11197.539741580911</v>
+        <v>10705.929748095512</v>
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="38"/>
-        <v>11085.564344165103</v>
+        <v>10598.870450614557</v>
       </c>
       <c r="BI27" s="4">
         <f t="shared" si="38"/>
-        <v>10974.708700723451</v>
+        <v>10492.881746108411</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="38"/>
-        <v>10864.961613716217</v>
+        <v>10387.952928647326</v>
       </c>
       <c r="BK27" s="4">
         <f t="shared" si="38"/>
-        <v>10756.311997579056</v>
+        <v>10284.073399360854</v>
       </c>
       <c r="BL27" s="4">
         <f t="shared" si="38"/>
-        <v>10648.748877603266</v>
+        <v>10181.232665367244</v>
       </c>
       <c r="BM27" s="4">
         <f t="shared" si="38"/>
-        <v>10542.261388827234</v>
+        <v>10079.420338713571</v>
       </c>
       <c r="BN27" s="4">
         <f t="shared" si="38"/>
-        <v>10436.83877493896</v>
+        <v>9978.6261353264363</v>
       </c>
       <c r="BO27" s="4">
         <f t="shared" si="38"/>
-        <v>10332.470387189571</v>
+        <v>9878.8398739731711</v>
       </c>
       <c r="BP27" s="4">
         <f t="shared" si="38"/>
-        <v>10229.145683317674</v>
+        <v>9780.0514752334384</v>
       </c>
       <c r="BQ27" s="4">
         <f t="shared" si="38"/>
-        <v>10126.854226484498</v>
+        <v>9682.2509604811039</v>
       </c>
       <c r="BR27" s="4">
         <f t="shared" si="38"/>
-        <v>10025.585684219654</v>
+        <v>9585.4284508762921</v>
       </c>
       <c r="BS27" s="4">
         <f t="shared" si="38"/>
-        <v>9925.3298273774562</v>
+        <v>9489.574166367529</v>
       </c>
       <c r="BT27" s="4">
         <f t="shared" si="38"/>
-        <v>9826.0765291036823</v>
+        <v>9394.678424703854</v>
       </c>
       <c r="BU27" s="4">
         <f t="shared" si="38"/>
-        <v>9727.8157638126449</v>
+        <v>9300.7316404568155</v>
       </c>
       <c r="BV27" s="4">
         <f t="shared" si="38"/>
-        <v>9630.5376061745192</v>
+        <v>9207.7243240522475</v>
       </c>
       <c r="BW27" s="4">
         <f t="shared" si="38"/>
-        <v>9534.2322301127733</v>
+        <v>9115.6470808117247</v>
       </c>
       <c r="BX27" s="4">
         <f t="shared" si="38"/>
-        <v>9438.8899078116447</v>
+        <v>9024.4906100036078</v>
       </c>
       <c r="BY27" s="4">
         <f t="shared" si="38"/>
-        <v>9344.5010087335286</v>
+        <v>8934.2457039035708</v>
       </c>
       <c r="BZ27" s="4">
         <f t="shared" si="38"/>
-        <v>9251.055998646194</v>
+        <v>8844.9032468645346</v>
       </c>
       <c r="CA27" s="4">
         <f t="shared" si="38"/>
-        <v>9158.5454386597321</v>
+        <v>8756.4542143958897</v>
       </c>
       <c r="CB27" s="4">
         <f t="shared" si="38"/>
-        <v>9066.959984273135</v>
+        <v>8668.8896722519312</v>
       </c>
       <c r="CC27" s="4">
         <f t="shared" si="38"/>
-        <v>8976.2903844304037</v>
+        <v>8582.2007755294126</v>
       </c>
       <c r="CD27" s="4">
         <f t="shared" si="38"/>
-        <v>8886.527480586099</v>
+        <v>8496.3787677741184</v>
       </c>
       <c r="CE27" s="4">
         <f t="shared" si="38"/>
-        <v>8797.6622057802379</v>
+        <v>8411.4149800963769</v>
       </c>
       <c r="CF27" s="4">
         <f t="shared" si="38"/>
-        <v>8709.6855837224357</v>
+        <v>8327.3008302954131</v>
       </c>
       <c r="CG27" s="4">
         <f t="shared" si="38"/>
-        <v>8622.5887278852115</v>
+        <v>8244.0278219924585</v>
       </c>
       <c r="CH27" s="4">
         <f t="shared" si="38"/>
-        <v>8536.3628406063599</v>
+        <v>8161.5875437725335</v>
       </c>
       <c r="CI27" s="4">
         <f t="shared" si="38"/>
-        <v>8450.9992122002968</v>
+        <v>8079.9716683348079</v>
       </c>
       <c r="CJ27" s="4">
         <f t="shared" si="38"/>
-        <v>8366.4892200782942</v>
+        <v>7999.1719516514595</v>
       </c>
       <c r="CK27" s="4">
         <f t="shared" si="38"/>
-        <v>8282.8243278775117</v>
+        <v>7919.1802321349451</v>
       </c>
       <c r="CL27" s="4">
         <f t="shared" si="38"/>
-        <v>8199.9960845987371</v>
+        <v>7839.9884298135958</v>
       </c>
       <c r="CM27" s="4">
         <f t="shared" si="38"/>
-        <v>8117.9961237527496</v>
+        <v>7761.5885455154594</v>
       </c>
       <c r="CN27" s="4">
         <f t="shared" si="38"/>
-        <v>8036.8161625152215</v>
+        <v>7683.9726600603044</v>
       </c>
       <c r="CO27" s="4">
         <f t="shared" si="38"/>
-        <v>7956.4480008900691</v>
+        <v>7607.1329334597012</v>
       </c>
       <c r="CP27" s="4">
         <f t="shared" si="38"/>
-        <v>7876.8835208811688</v>
+        <v>7531.0616041251042</v>
       </c>
       <c r="CQ27" s="4">
         <f t="shared" si="38"/>
-        <v>7798.1146856723572</v>
+        <v>7455.7509880838534</v>
       </c>
       <c r="CR27" s="4">
         <f t="shared" si="38"/>
-        <v>7720.1335388156331</v>
+        <v>7381.1934782030148</v>
       </c>
       <c r="CS27" s="4">
         <f t="shared" si="38"/>
-        <v>7642.9322034274765</v>
+        <v>7307.3815434209846</v>
       </c>
       <c r="CT27" s="4">
         <f t="shared" si="38"/>
-        <v>7566.5028813932013</v>
+        <v>7234.3077279867748</v>
       </c>
       <c r="CU27" s="4">
         <f t="shared" si="38"/>
-        <v>7490.8378525792696</v>
+        <v>7161.9646507069074</v>
       </c>
       <c r="CV27" s="4">
         <f t="shared" si="38"/>
-        <v>7415.929474053477</v>
+        <v>7090.3450041998385</v>
       </c>
       <c r="CW27" s="4">
         <f t="shared" si="38"/>
-        <v>7341.7701793129418</v>
+        <v>7019.4415541578401</v>
       </c>
       <c r="CX27" s="4">
         <f t="shared" ref="CX27:EW27" si="39">CW27*(1+$AN$39)</f>
-        <v>7268.3524775198121</v>
+        <v>6949.2471386162615</v>
       </c>
       <c r="CY27" s="4">
         <f t="shared" si="39"/>
-        <v>7195.6689527446142</v>
+        <v>6879.7546672300987</v>
       </c>
       <c r="CZ27" s="4">
         <f t="shared" si="39"/>
-        <v>7123.7122632171677</v>
+        <v>6810.9571205577977</v>
       </c>
       <c r="DA27" s="4">
         <f t="shared" si="39"/>
-        <v>7052.4751405849956</v>
+        <v>6742.8475493522201</v>
       </c>
       <c r="DB27" s="4">
         <f t="shared" si="39"/>
-        <v>6981.9503891791455</v>
+        <v>6675.4190738586976</v>
       </c>
       <c r="DC27" s="4">
         <f t="shared" si="39"/>
-        <v>6912.1308852873544</v>
+        <v>6608.664883120111</v>
       </c>
       <c r="DD27" s="4">
         <f t="shared" si="39"/>
-        <v>6843.0095764344806</v>
+        <v>6542.5782342889097</v>
       </c>
       <c r="DE27" s="4">
         <f t="shared" si="39"/>
-        <v>6774.579480670136</v>
+        <v>6477.1524519460208</v>
       </c>
       <c r="DF27" s="4">
         <f t="shared" si="39"/>
-        <v>6706.8336858634348</v>
+        <v>6412.3809274265604</v>
       </c>
       <c r="DG27" s="4">
         <f t="shared" si="39"/>
-        <v>6639.7653490048006</v>
+        <v>6348.2571181522944</v>
       </c>
       <c r="DH27" s="4">
         <f t="shared" si="39"/>
-        <v>6573.3676955147521</v>
+        <v>6284.7745469707716</v>
       </c>
       <c r="DI27" s="4">
         <f t="shared" si="39"/>
-        <v>6507.6340185596046</v>
+        <v>6221.9268015010639</v>
       </c>
       <c r="DJ27" s="4">
         <f t="shared" si="39"/>
-        <v>6442.5576783740089</v>
+        <v>6159.7075334860529</v>
       </c>
       <c r="DK27" s="4">
         <f t="shared" si="39"/>
-        <v>6378.1321015902686</v>
+        <v>6098.1104581511927</v>
       </c>
       <c r="DL27" s="4">
         <f t="shared" si="39"/>
-        <v>6314.3507805743657</v>
+        <v>6037.1293535696805</v>
       </c>
       <c r="DM27" s="4">
         <f t="shared" si="39"/>
-        <v>6251.2072727686218</v>
+        <v>5976.7580600339834</v>
       </c>
       <c r="DN27" s="4">
         <f t="shared" si="39"/>
-        <v>6188.6952000409356</v>
+        <v>5916.9904794336435</v>
       </c>
       <c r="DO27" s="4">
         <f t="shared" si="39"/>
-        <v>6126.8082480405265</v>
+        <v>5857.8205746393069</v>
       </c>
       <c r="DP27" s="4">
         <f t="shared" si="39"/>
-        <v>6065.5401655601208</v>
+        <v>5799.2423688929139</v>
       </c>
       <c r="DQ27" s="4">
         <f t="shared" si="39"/>
-        <v>6004.8847639045198</v>
+        <v>5741.2499452039847</v>
       </c>
       <c r="DR27" s="4">
         <f t="shared" si="39"/>
-        <v>5944.8359162654742</v>
+        <v>5683.8374457519449</v>
       </c>
       <c r="DS27" s="4">
         <f t="shared" si="39"/>
-        <v>5885.3875571028193</v>
+        <v>5626.9990712944254</v>
       </c>
       <c r="DT27" s="4">
         <f t="shared" si="39"/>
-        <v>5826.5336815317914</v>
+        <v>5570.729080581481</v>
       </c>
       <c r="DU27" s="4">
         <f t="shared" si="39"/>
-        <v>5768.2683447164736</v>
+        <v>5515.0217897756665</v>
       </c>
       <c r="DV27" s="4">
         <f t="shared" si="39"/>
-        <v>5710.5856612693087</v>
+        <v>5459.8715718779094</v>
       </c>
       <c r="DW27" s="4">
         <f t="shared" si="39"/>
-        <v>5653.4798046566157</v>
+        <v>5405.2728561591302</v>
       </c>
       <c r="DX27" s="4">
         <f t="shared" si="39"/>
-        <v>5596.9450066100499</v>
+        <v>5351.2201275975385</v>
       </c>
       <c r="DY27" s="4">
         <f t="shared" si="39"/>
-        <v>5540.9755565439491</v>
+        <v>5297.7079263215628</v>
       </c>
       <c r="DZ27" s="4">
         <f t="shared" si="39"/>
-        <v>5485.5658009785093</v>
+        <v>5244.7308470583475</v>
       </c>
       <c r="EA27" s="4">
         <f t="shared" si="39"/>
-        <v>5430.7101429687245</v>
+        <v>5192.2835385877643</v>
       </c>
       <c r="EB27" s="4">
         <f t="shared" si="39"/>
-        <v>5376.4030415390371</v>
+        <v>5140.3607032018863</v>
       </c>
       <c r="EC27" s="4">
         <f t="shared" si="39"/>
-        <v>5322.6390111236469</v>
+        <v>5088.9570961698673</v>
       </c>
       <c r="ED27" s="4">
         <f t="shared" si="39"/>
-        <v>5269.4126210124105</v>
+        <v>5038.0675252081683</v>
       </c>
       <c r="EE27" s="4">
         <f t="shared" si="39"/>
-        <v>5216.7184948022859</v>
+        <v>4987.6868499560869</v>
       </c>
       <c r="EF27" s="4">
         <f t="shared" si="39"/>
-        <v>5164.5513098542633</v>
+        <v>4937.8099814565257</v>
       </c>
       <c r="EG27" s="4">
         <f t="shared" si="39"/>
-        <v>5112.905796755721</v>
+        <v>4888.4318816419609</v>
       </c>
       <c r="EH27" s="4">
         <f t="shared" si="39"/>
-        <v>5061.776738788164</v>
+        <v>4839.5475628255408</v>
       </c>
       <c r="EI27" s="4">
         <f t="shared" si="39"/>
-        <v>5011.1589714002821</v>
+        <v>4791.1520871972853</v>
       </c>
       <c r="EJ27" s="4">
         <f t="shared" si="39"/>
-        <v>4961.0473816862796</v>
+        <v>4743.2405663253121</v>
       </c>
       <c r="EK27" s="4">
         <f t="shared" si="39"/>
-        <v>4911.4369078694172</v>
+        <v>4695.808160662059</v>
       </c>
       <c r="EL27" s="4">
         <f t="shared" si="39"/>
-        <v>4862.3225387907232</v>
+        <v>4648.8500790554381</v>
       </c>
       <c r="EM27" s="4">
         <f t="shared" si="39"/>
-        <v>4813.6993134028162</v>
+        <v>4602.361578264884</v>
       </c>
       <c r="EN27" s="4">
         <f t="shared" si="39"/>
-        <v>4765.5623202687884</v>
+        <v>4556.3379624822355</v>
       </c>
       <c r="EO27" s="4">
         <f t="shared" si="39"/>
-        <v>4717.9066970661006</v>
+        <v>4510.7745828574134</v>
       </c>
       <c r="EP27" s="4">
         <f t="shared" si="39"/>
-        <v>4670.72763009544</v>
+        <v>4465.6668370288389</v>
       </c>
       <c r="EQ27" s="4">
         <f t="shared" si="39"/>
-        <v>4624.0203537944853</v>
+        <v>4421.0101686585504</v>
       </c>
       <c r="ER27" s="4">
         <f t="shared" si="39"/>
-        <v>4577.7801502565408</v>
+        <v>4376.800066971965</v>
       </c>
       <c r="ES27" s="4">
         <f t="shared" si="39"/>
-        <v>4532.0023487539756</v>
+        <v>4333.0320663022449</v>
       </c>
       <c r="ET27" s="4">
         <f t="shared" si="39"/>
-        <v>4486.6823252664362</v>
+        <v>4289.7017456392223</v>
       </c>
       <c r="EU27" s="4">
         <f t="shared" si="39"/>
-        <v>4441.8155020137719</v>
+        <v>4246.8047281828303</v>
       </c>
       <c r="EV27" s="4">
         <f t="shared" si="39"/>
-        <v>4397.3973469936345</v>
+        <v>4204.3366809010022</v>
       </c>
       <c r="EW27" s="4">
         <f t="shared" si="39"/>
-        <v>4353.4233735236985</v>
+        <v>4162.2933140919922</v>
       </c>
     </row>
     <row r="28" spans="2:153" x14ac:dyDescent="0.3">
@@ -4118,16 +4132,16 @@
         <v>700.6</v>
       </c>
       <c r="P28" s="3">
-        <f>700.6</f>
-        <v>700.6</v>
+        <f>695.9</f>
+        <v>695.9</v>
       </c>
       <c r="Q28" s="3">
-        <f>700.6</f>
-        <v>700.6</v>
+        <f>695.9</f>
+        <v>695.9</v>
       </c>
       <c r="R28" s="3">
-        <f>700.6</f>
-        <v>700.6</v>
+        <f>695.9</f>
+        <v>695.9</v>
       </c>
       <c r="V28" s="3">
         <v>710.9</v>
@@ -4143,48 +4157,48 @@
         <v>702.5</v>
       </c>
       <c r="Z28" s="3">
-        <f t="shared" ref="Z28:AJ28" si="41">700.6</f>
-        <v>700.6</v>
+        <f t="shared" ref="Z28:AJ28" si="41">695.9</f>
+        <v>695.9</v>
       </c>
       <c r="AA28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AB28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AC28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AE28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AF28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AG28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AH28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
       <c r="AJ28" s="3">
         <f t="shared" si="41"/>
-        <v>700.6</v>
+        <v>695.9</v>
       </c>
     </row>
     <row r="29" spans="2:153" x14ac:dyDescent="0.3">
@@ -4245,15 +4259,15 @@
       </c>
       <c r="P29" s="6">
         <f t="shared" si="44"/>
-        <v>4.2491010362546389</v>
+        <v>4.1457105906020981</v>
       </c>
       <c r="Q29" s="6">
         <f t="shared" si="44"/>
-        <v>4.1398780673708258</v>
+        <v>4.0480928208075859</v>
       </c>
       <c r="R29" s="6">
         <f t="shared" si="44"/>
-        <v>3.2876195047102454</v>
+        <v>3.2356567753987631</v>
       </c>
       <c r="V29" s="6">
         <f>V27/V28</f>
@@ -4273,47 +4287,47 @@
       </c>
       <c r="Z29" s="6">
         <f>Z27/Z28</f>
-        <v>15.36486580787896</v>
+        <v>15.142637367437853</v>
       </c>
       <c r="AA29" s="6">
         <f t="shared" ref="AA29:AJ29" si="45">AA27/AA28</f>
-        <v>17.39878917156723</v>
+        <v>16.902012353499067</v>
       </c>
       <c r="AB29" s="6">
         <f t="shared" si="45"/>
-        <v>17.956976623317157</v>
+        <v>17.277848753085216</v>
       </c>
       <c r="AC29" s="6">
         <f t="shared" si="45"/>
-        <v>18.376309388341078</v>
+        <v>17.612357242750864</v>
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="45"/>
-        <v>18.678748708795972</v>
+        <v>17.935412825292062</v>
       </c>
       <c r="AE29" s="6">
         <f t="shared" si="45"/>
-        <v>18.947818379640161</v>
+        <v>18.224893230599641</v>
       </c>
       <c r="AF29" s="6">
         <f t="shared" si="45"/>
-        <v>19.179671888071024</v>
+        <v>18.450585196209214</v>
       </c>
       <c r="AG29" s="6">
         <f t="shared" si="45"/>
-        <v>19.414691438078872</v>
+        <v>18.679402942140964</v>
       </c>
       <c r="AH29" s="6">
         <f t="shared" si="45"/>
-        <v>19.652925640209354</v>
+        <v>18.911395103411422</v>
       </c>
       <c r="AI29" s="6">
         <f t="shared" si="45"/>
-        <v>19.894423930116133</v>
+        <v>19.146611148931566</v>
       </c>
       <c r="AJ29" s="6">
         <f t="shared" si="45"/>
-        <v>20.139236583592066</v>
+        <v>19.385101396796625</v>
       </c>
     </row>
     <row r="31" spans="2:153" x14ac:dyDescent="0.3">
@@ -4358,7 +4372,7 @@
       </c>
       <c r="P31" s="7">
         <f t="shared" si="47"/>
-        <v>6.0000000000000053E-2</v>
+        <v>5.7142857142857162E-2</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="47"/>
@@ -4382,7 +4396,7 @@
       </c>
       <c r="Z31" s="7">
         <f t="shared" si="48"/>
-        <v>5.0812116390088979E-2</v>
+        <v>5.0093203000682207E-2</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="48"/>
@@ -4467,15 +4481,15 @@
       </c>
       <c r="P32" s="7">
         <f>P4/L4-1</f>
-        <v>0.15999999999999992</v>
+        <v>0.20388349514563098</v>
       </c>
       <c r="Q32" s="7">
         <f>Q4/M4-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.16999999999999993</v>
       </c>
       <c r="R32" s="7">
         <f>R4/N4-1</f>
-        <v>0.12999999999999989</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="W32" s="7">
         <f>W4/V4-1</f>
@@ -4491,7 +4505,7 @@
       </c>
       <c r="Z32" s="7">
         <f t="shared" si="50"/>
-        <v>0.15456858799857986</v>
+        <v>0.17571902000236705</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="50"/>
@@ -4575,16 +4589,16 @@
         <v>2.6221692491060766E-2</v>
       </c>
       <c r="P33" s="7">
-        <f t="shared" ref="P33:R34" si="52">P5/L5-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f>P7/L7-1</f>
+        <v>8.293838862559233E-2</v>
       </c>
       <c r="Q33" s="7">
-        <f t="shared" si="52"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="Q33:R34" si="52">Q5/M5-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="R33" s="7">
         <f t="shared" si="52"/>
-        <v>2.0000000000000018E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="W33" s="7">
         <f>W5/V5-1</f>
@@ -4600,27 +4614,27 @@
       </c>
       <c r="Z33" s="7">
         <f>Z7/Y7-1</f>
-        <v>2.3970436067997092E-2</v>
+        <v>4.5399852180340039E-2</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" ref="AA33:AJ33" si="53">AA7/Z7-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB33" s="7">
         <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC33" s="7">
         <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD33" s="7">
         <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE33" s="7">
         <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="53"/>
@@ -4680,17 +4694,14 @@
         <v>3.6231884057970953E-2</v>
       </c>
       <c r="O34" s="7"/>
-      <c r="P34" s="7">
-        <f t="shared" si="52"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
+      <c r="P34" s="7"/>
       <c r="Q34" s="7">
         <f t="shared" si="52"/>
-        <v>4.0000000000000036E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="R34" s="7">
         <f t="shared" si="52"/>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="W34" s="7">
         <f>W6/V6-1</f>
@@ -4758,7 +4769,7 @@
       </c>
       <c r="P35" s="7">
         <f t="shared" ref="P35:P37" si="64">P9/L9-1</f>
-        <v>6.0000000000000053E-2</v>
+        <v>8.1118398343113629E-2</v>
       </c>
       <c r="Q35" s="7">
         <f t="shared" ref="Q35:Q37" si="65">Q9/M9-1</f>
@@ -4782,11 +4793,11 @@
       </c>
       <c r="Z35" s="7">
         <f t="shared" si="67"/>
-        <v>4.5122924984240198E-2</v>
+        <v>5.0265181760874134E-2</v>
       </c>
       <c r="AA35" s="7">
         <f t="shared" si="67"/>
-        <v>5.0000000000000044E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB35" s="7">
         <f t="shared" si="67"/>
@@ -4867,7 +4878,7 @@
       </c>
       <c r="P36" s="7">
         <f t="shared" si="64"/>
-        <v>-1.0000000000000009E-2</v>
+        <v>6.2984496124030009E-3</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="65"/>
@@ -4891,7 +4902,7 @@
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="68"/>
-        <v>-1.5013330101793509E-2</v>
+        <v>-1.0936742607852712E-2</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="68"/>
@@ -4976,7 +4987,7 @@
       </c>
       <c r="P37" s="7">
         <f t="shared" si="64"/>
-        <v>9.8734584450402396E-2</v>
+        <v>0.12252010723860596</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="65"/>
@@ -5000,15 +5011,15 @@
       </c>
       <c r="Z37" s="7">
         <f t="shared" ref="Z37:AJ37" si="71">Z11/Y11-1</f>
-        <v>7.7050119024641095E-2</v>
+        <v>8.2758154796371164E-2</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="71"/>
-        <v>5.0000000000000266E-2</v>
+        <v>3.5150276511633827E-2</v>
       </c>
       <c r="AB37" s="7">
         <f t="shared" si="71"/>
-        <v>2.9999999999999805E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC37" s="7">
         <f t="shared" si="71"/>
@@ -5024,11 +5035,11 @@
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="71"/>
-        <v>1.0000000000000009E-2</v>
+        <v>1.0000000000000231E-2</v>
       </c>
       <c r="AG37" s="7">
         <f t="shared" si="71"/>
-        <v>1.0000000000000009E-2</v>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="AH37" s="7">
         <f t="shared" si="71"/>
@@ -5036,7 +5047,7 @@
       </c>
       <c r="AI37" s="7">
         <f t="shared" si="71"/>
-        <v>1.0000000000000009E-2</v>
+        <v>1.0000000000000231E-2</v>
       </c>
       <c r="AJ37" s="7">
         <f t="shared" si="71"/>
@@ -5089,15 +5100,15 @@
       </c>
       <c r="P38" s="7">
         <f t="shared" ref="P38" si="75">P16/L16-1</f>
-        <v>6.7970864814915544E-2</v>
+        <v>8.3491873675055617E-2</v>
       </c>
       <c r="Q38" s="7">
         <f t="shared" ref="Q38" si="76">Q16/M16-1</f>
-        <v>5.416369348740635E-2</v>
+        <v>5.7369401991586244E-2</v>
       </c>
       <c r="R38" s="7">
         <f t="shared" ref="R38" si="77">R16/N16-1</f>
-        <v>4.8724633156415731E-2</v>
+        <v>5.2626704131543134E-2</v>
       </c>
       <c r="V38" s="7"/>
       <c r="W38" s="7">
@@ -5114,47 +5125,47 @@
       </c>
       <c r="Z38" s="7">
         <f t="shared" si="78"/>
-        <v>5.8354873923532002E-2</v>
+        <v>6.4025013139984654E-2</v>
       </c>
       <c r="AA38" s="7">
         <f t="shared" si="78"/>
-        <v>3.8195460161650763E-2</v>
+        <v>3.60338242156093E-2</v>
       </c>
       <c r="AB38" s="7">
         <f t="shared" si="78"/>
-        <v>2.4230455888448077E-2</v>
+        <v>2.5187879461433749E-2</v>
       </c>
       <c r="AC38" s="7">
         <f t="shared" si="78"/>
-        <v>1.8670545596600974E-2</v>
+        <v>1.9604794841722173E-2</v>
       </c>
       <c r="AD38" s="7">
         <f t="shared" si="78"/>
-        <v>1.4213027022785152E-2</v>
+        <v>1.5154712043011331E-2</v>
       </c>
       <c r="AE38" s="7">
         <f t="shared" si="78"/>
-        <v>1.2880097170222538E-2</v>
+        <v>1.3805806575623025E-2</v>
       </c>
       <c r="AF38" s="7">
         <f t="shared" si="78"/>
-        <v>1.1464388575517015E-2</v>
+        <v>1.1480884274490455E-2</v>
       </c>
       <c r="AG38" s="7">
         <f t="shared" si="78"/>
-        <v>1.1476746353008771E-2</v>
+        <v>1.1493356902205543E-2</v>
       </c>
       <c r="AH38" s="7">
         <f t="shared" si="78"/>
-        <v>1.1489190221624312E-2</v>
+        <v>1.1505916010081219E-2</v>
       </c>
       <c r="AI38" s="7">
         <f t="shared" si="78"/>
-        <v>1.1501720473872545E-2</v>
+        <v>1.1518561884780176E-2</v>
       </c>
       <c r="AJ38" s="7">
         <f t="shared" si="78"/>
-        <v>1.1514337397896313E-2</v>
+        <v>1.1531294808460935E-2</v>
       </c>
     </row>
     <row r="39" spans="2:40" x14ac:dyDescent="0.3">
@@ -5215,7 +5226,7 @@
       </c>
       <c r="P39" s="7">
         <f t="shared" si="80"/>
-        <v>0.44999999999999996</v>
+        <v>0.4486529875081523</v>
       </c>
       <c r="Q39" s="7">
         <f t="shared" si="80"/>
@@ -5223,7 +5234,7 @@
       </c>
       <c r="R39" s="7">
         <f t="shared" si="80"/>
-        <v>0.43999999999999989</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="V39" s="7">
         <f t="shared" ref="V39:AJ39" si="81">V21/V16</f>
@@ -5243,23 +5254,23 @@
       </c>
       <c r="Z39" s="7">
         <f t="shared" si="81"/>
-        <v>0.4482249822649631</v>
+        <v>0.44788486178641834</v>
       </c>
       <c r="AA39" s="7">
         <f t="shared" si="81"/>
-        <v>0.45000000000000007</v>
+        <v>0.45</v>
       </c>
       <c r="AB39" s="7">
         <f t="shared" si="81"/>
-        <v>0.45</v>
+        <v>0.45000000000000007</v>
       </c>
       <c r="AC39" s="7">
         <f t="shared" si="81"/>
-        <v>0.44999999999999996</v>
+        <v>0.45</v>
       </c>
       <c r="AD39" s="7">
         <f t="shared" si="81"/>
-        <v>0.44999999999999996</v>
+        <v>0.45</v>
       </c>
       <c r="AE39" s="7">
         <f t="shared" si="81"/>
@@ -5267,19 +5278,19 @@
       </c>
       <c r="AF39" s="7">
         <f t="shared" si="81"/>
-        <v>0.45000000000000007</v>
+        <v>0.45</v>
       </c>
       <c r="AG39" s="7">
         <f t="shared" si="81"/>
-        <v>0.44999999999999996</v>
+        <v>0.45</v>
       </c>
       <c r="AH39" s="7">
         <f t="shared" si="81"/>
-        <v>0.45</v>
+        <v>0.45000000000000007</v>
       </c>
       <c r="AI39" s="7">
         <f t="shared" si="81"/>
-        <v>0.45000000000000007</v>
+        <v>0.45</v>
       </c>
       <c r="AJ39" s="7">
         <f t="shared" si="81"/>
@@ -5350,7 +5361,7 @@
       </c>
       <c r="P40" s="7">
         <f t="shared" si="84"/>
-        <v>0.08</v>
+        <v>7.8011337982240511E-2</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="84"/>
@@ -5378,7 +5389,7 @@
       </c>
       <c r="Z40" s="7">
         <f t="shared" si="85"/>
-        <v>7.9635303209599162E-2</v>
+        <v>7.913516766955804E-2</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="85"/>
@@ -5473,15 +5484,15 @@
       </c>
       <c r="P41" s="7">
         <f t="shared" ref="P41" si="89">P23/L23-1</f>
-        <v>-1.0000000000000009E-2</v>
+        <v>0.10415597742432015</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" ref="Q41" si="90">Q23/M23-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="R41" s="7">
         <f t="shared" ref="R41" si="91">R23/N23-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="V41" s="7"/>
       <c r="W41" s="7">
@@ -5498,19 +5509,19 @@
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="92"/>
-        <v>5.3696023420346517E-3</v>
+        <v>5.7761649182727526E-2</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="92"/>
-        <v>2.0000000000000018E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB41" s="7">
         <f t="shared" si="92"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC41" s="7">
         <f t="shared" si="92"/>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD41" s="7">
         <f t="shared" si="92"/>
@@ -5545,7 +5556,7 @@
       </c>
       <c r="AN41" s="3">
         <f>NPV(AN40,Z27:EW27)</f>
-        <v>206822.43022615445</v>
+        <v>197982.70311972545</v>
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.3">
@@ -5606,7 +5617,7 @@
       </c>
       <c r="P42" s="7">
         <f t="shared" si="95"/>
-        <v>0.08</v>
+        <v>8.4583354236692915E-2</v>
       </c>
       <c r="Q42" s="7">
         <f t="shared" si="95"/>
@@ -5614,7 +5625,7 @@
       </c>
       <c r="R42" s="7">
         <f t="shared" si="95"/>
-        <v>0.11</v>
+        <v>0.10999999999999999</v>
       </c>
       <c r="V42" s="7">
         <f t="shared" ref="V42:AJ42" si="96">V24/V16</f>
@@ -5634,7 +5645,7 @@
       </c>
       <c r="Z42" s="7">
         <f t="shared" si="96"/>
-        <v>8.9371990598870577E-2</v>
+        <v>9.0507705215288531E-2</v>
       </c>
       <c r="AA42" s="7">
         <f t="shared" si="96"/>
@@ -5681,7 +5692,7 @@
       </c>
       <c r="AN42" s="3">
         <f>Main!D8</f>
-        <v>-287</v>
+        <v>-1758</v>
       </c>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.3">
@@ -5742,15 +5753,15 @@
       </c>
       <c r="P43" s="7">
         <f t="shared" si="99"/>
-        <v>0.19179341248181694</v>
+        <v>0.17809662368935936</v>
       </c>
       <c r="Q43" s="7">
         <f t="shared" si="99"/>
-        <v>0.18545992299508895</v>
+        <v>0.17958539186980071</v>
       </c>
       <c r="R43" s="7">
         <f t="shared" si="99"/>
-        <v>0.1446621554906895</v>
+        <v>0.14089631021810847</v>
       </c>
       <c r="V43" s="7">
         <f t="shared" ref="V43:AJ43" si="100">V25/V16</f>
@@ -5770,54 +5781,54 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="100"/>
-        <v>0.17426523592788018</v>
+        <v>0.16840866291450016</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="100"/>
-        <v>0.18688694885786039</v>
+        <v>0.17974620677752823</v>
       </c>
       <c r="AB43" s="7">
         <f t="shared" si="100"/>
-        <v>0.18831958124773465</v>
+        <v>0.17922868744916923</v>
       </c>
       <c r="AC43" s="7">
         <f t="shared" si="100"/>
-        <v>0.18918504723267354</v>
+        <v>0.17918575179965998</v>
       </c>
       <c r="AD43" s="7">
         <f t="shared" si="100"/>
-        <v>0.18960383116562732</v>
+        <v>0.17974843996232034</v>
       </c>
       <c r="AE43" s="7">
         <f t="shared" si="100"/>
-        <v>0.18988930495721318</v>
+        <v>0.18016232209777724</v>
       </c>
       <c r="AF43" s="7">
         <f t="shared" si="100"/>
-        <v>0.19003424427466581</v>
+        <v>0.18032313273936301</v>
       </c>
       <c r="AG43" s="7">
         <f t="shared" si="100"/>
-        <v>0.19018019331968872</v>
+        <v>0.1804850583769545</v>
       </c>
       <c r="AH43" s="7">
         <f t="shared" si="100"/>
-        <v>0.19032715552301208</v>
+        <v>0.18064810270652581</v>
       </c>
       <c r="AI43" s="7">
         <f t="shared" si="100"/>
-        <v>0.19047513426413587</v>
+        <v>0.18081226936595801</v>
       </c>
       <c r="AJ43" s="7">
         <f t="shared" si="100"/>
-        <v>0.19062413287011915</v>
+        <v>0.18097756193369724</v>
       </c>
       <c r="AM43" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AN43" s="3">
         <f>AN41+AN42</f>
-        <v>206535.43022615445</v>
+        <v>196224.70311972545</v>
       </c>
     </row>
     <row r="44" spans="2:40" x14ac:dyDescent="0.3">
@@ -5878,7 +5889,7 @@
       </c>
       <c r="P44" s="7">
         <f t="shared" si="103"/>
-        <v>0.21</v>
+        <v>0.18732394366197183</v>
       </c>
       <c r="Q44" s="7">
         <f t="shared" si="103"/>
@@ -5886,7 +5897,7 @@
       </c>
       <c r="R44" s="7">
         <f t="shared" si="103"/>
-        <v>0.21</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" ref="V44:AJ44" si="104">V26/V25</f>
@@ -5906,7 +5917,7 @@
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="104"/>
-        <v>0.2134124402005477</v>
+        <v>0.20745791143688347</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="104"/>
@@ -5953,7 +5964,7 @@
       </c>
       <c r="AN44" s="8">
         <f>AN43/AJ28</f>
-        <v>294.79793066821929</v>
+        <v>281.972558010814</v>
       </c>
     </row>
     <row r="45" spans="2:40" x14ac:dyDescent="0.3">
@@ -6014,15 +6025,15 @@
       </c>
       <c r="P45" s="7">
         <f t="shared" si="107"/>
-        <v>0.15151679586063538</v>
+        <v>0.14473486178698641</v>
       </c>
       <c r="Q45" s="7">
         <f t="shared" si="107"/>
-        <v>0.14651333916612028</v>
+        <v>0.14187245957714256</v>
       </c>
       <c r="R45" s="7">
         <f t="shared" si="107"/>
-        <v>0.1142831028376447</v>
+        <v>0.11130808507230569</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" ref="V45:AJ45" si="108">V27/V16</f>
@@ -6042,54 +6053,54 @@
       </c>
       <c r="Z45" s="7">
         <f t="shared" si="108"/>
-        <v>0.1370748666863871</v>
+        <v>0.13347095343837984</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="108"/>
-        <v>0.14950955908628832</v>
+        <v>0.14379696542202258</v>
       </c>
       <c r="AB45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15065566499818772</v>
+        <v>0.14338294995933537</v>
       </c>
       <c r="AC45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15134803778613884</v>
+        <v>0.143348601439728</v>
       </c>
       <c r="AD45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15168306493250183</v>
+        <v>0.14379875196985628</v>
       </c>
       <c r="AE45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15191144396577055</v>
+        <v>0.14412985767822178</v>
       </c>
       <c r="AF45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15202739541973262</v>
+        <v>0.14425850619149042</v>
       </c>
       <c r="AG45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15214415465575096</v>
+        <v>0.1443880467015636</v>
       </c>
       <c r="AH45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15226172441840968</v>
+        <v>0.14451848216522065</v>
       </c>
       <c r="AI45" s="7">
         <f t="shared" si="108"/>
-        <v>0.1523801074113087</v>
+        <v>0.1446498154927664</v>
       </c>
       <c r="AJ45" s="7">
         <f t="shared" si="108"/>
-        <v>0.15249930629609529</v>
+        <v>0.14478204954695778</v>
       </c>
       <c r="AM45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AN45" s="8">
         <f>Main!D3</f>
-        <v>291.27999999999997</v>
+        <v>337.65</v>
       </c>
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.3">
@@ -6098,7 +6109,7 @@
       </c>
       <c r="AN46" s="9">
         <f>AN44/AN45-1</f>
-        <v>1.2077487874963433E-2</v>
+        <v>-0.16489691097049008</v>
       </c>
     </row>
     <row r="47" spans="2:40" x14ac:dyDescent="0.3">

--- a/Financial Analysis/AXP.xlsx
+++ b/Financial Analysis/AXP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4BF8C7-2404-4C96-AD24-FEEE237E559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A6B07B-E33E-446B-A0E5-E1368D30A0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7753066E-724B-42EB-9AF0-1E4829C95CCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7753066E-724B-42EB-9AF0-1E4829C95CCE}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
     <t>Total service revenue</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -388,14 +388,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -412,7 +412,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10759440" y="0"/>
+          <a:off x="11384280" y="0"/>
           <a:ext cx="0" cy="9235440"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -815,17 +815,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="8">
-        <v>337.65</v>
+        <v>357.56</v>
       </c>
       <c r="E3" s="11">
-        <v>45918</v>
+        <v>45956</v>
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>45918</v>
+        <v>45956</v>
       </c>
       <c r="G3" s="11">
-        <v>45947</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -833,11 +833,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>695.9</f>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -846,7 +846,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>234970.63499999998</v>
+        <v>246323.084</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -854,11 +854,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>57937</f>
-        <v>57937</v>
+        <f>54706+1374</f>
+        <v>56080</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>63</v>
@@ -869,11 +869,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>1493+58202</f>
-        <v>59695</v>
+        <f>1446+57787</f>
+        <v>59233</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -882,7 +882,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>-1758</v>
+        <v>-3153</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -891,7 +891,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>236728.63499999998</v>
+        <v>249476.084</v>
       </c>
     </row>
   </sheetData>
@@ -1060,12 +1060,11 @@
         <v>9361</v>
       </c>
       <c r="Q3" s="3">
-        <f t="shared" ref="Q3" si="0">M3*1.06</f>
-        <v>9306.8000000000011</v>
+        <v>9413</v>
       </c>
       <c r="R3" s="3">
-        <f>N3*1.04</f>
-        <v>9544.08</v>
+        <f>N3*1.05</f>
+        <v>9635.85</v>
       </c>
       <c r="V3" s="3">
         <v>17414</v>
@@ -1084,47 +1083,47 @@
       </c>
       <c r="Z3" s="3">
         <f>SUM(O3:R3)</f>
-        <v>36954.880000000005</v>
+        <v>37152.85</v>
       </c>
       <c r="AA3" s="3">
-        <f>Z3*1.02</f>
-        <v>37693.977600000006</v>
+        <f>Z3*1.04</f>
+        <v>38638.964</v>
       </c>
       <c r="AB3" s="3">
-        <f>AA3*1.01</f>
-        <v>38070.917376000005</v>
+        <f>AA3*1.03</f>
+        <v>39798.132920000004</v>
       </c>
       <c r="AC3" s="3">
-        <f t="shared" ref="AC3:AJ3" si="1">AB3*1.01</f>
-        <v>38451.626549760003</v>
+        <f>AB3*1.02</f>
+        <v>40594.095578400003</v>
       </c>
       <c r="AD3" s="3">
-        <f t="shared" si="1"/>
-        <v>38836.142815257605</v>
+        <f t="shared" ref="AC3:AJ3" si="0">AC3*1.01</f>
+        <v>41000.036534184001</v>
       </c>
       <c r="AE3" s="3">
-        <f t="shared" si="1"/>
-        <v>39224.504243410178</v>
+        <f t="shared" si="0"/>
+        <v>41410.03689952584</v>
       </c>
       <c r="AF3" s="3">
-        <f t="shared" si="1"/>
-        <v>39616.749285844278</v>
+        <f t="shared" si="0"/>
+        <v>41824.137268521095</v>
       </c>
       <c r="AG3" s="3">
-        <f t="shared" si="1"/>
-        <v>40012.916778702718</v>
+        <f t="shared" si="0"/>
+        <v>42242.378641206305</v>
       </c>
       <c r="AH3" s="3">
-        <f t="shared" si="1"/>
-        <v>40413.045946489743</v>
+        <f t="shared" si="0"/>
+        <v>42664.802427618371</v>
       </c>
       <c r="AI3" s="3">
-        <f t="shared" si="1"/>
-        <v>40817.17640595464</v>
+        <f t="shared" si="0"/>
+        <v>43091.450451894554</v>
       </c>
       <c r="AJ3" s="3">
-        <f t="shared" si="1"/>
-        <v>41225.348170014186</v>
+        <f t="shared" si="0"/>
+        <v>43522.364956413498</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -1174,8 +1173,7 @@
         <v>2480</v>
       </c>
       <c r="Q4" s="3">
-        <f>M4*1.17</f>
-        <v>2538.8999999999996</v>
+        <v>2551</v>
       </c>
       <c r="R4" s="3">
         <f>N4*1.15</f>
@@ -1198,47 +1196,47 @@
       </c>
       <c r="Z4" s="3">
         <f>SUM(O4:R4)</f>
-        <v>9933.65</v>
+        <v>9945.75</v>
       </c>
       <c r="AA4" s="3">
-        <f>Z4*1.09</f>
-        <v>10827.6785</v>
+        <f>Z4*1.13</f>
+        <v>11238.697499999998</v>
       </c>
       <c r="AB4" s="3">
-        <f>AA4*1.07</f>
-        <v>11585.615995</v>
+        <f>AA4*1.09</f>
+        <v>12250.180274999999</v>
       </c>
       <c r="AC4" s="3">
-        <f>AB4*1.05</f>
-        <v>12164.89679475</v>
+        <f>AB4*1.07</f>
+        <v>13107.69289425</v>
       </c>
       <c r="AD4" s="3">
-        <f>AC4*1.04</f>
-        <v>12651.492666540002</v>
+        <f>AC4*1.05</f>
+        <v>13763.0775389625</v>
       </c>
       <c r="AE4" s="3">
-        <f>AD4*1.03</f>
-        <v>13031.037446536202</v>
+        <f t="shared" ref="AE4:AJ4" si="1">AD4*1.05</f>
+        <v>14451.231415910624</v>
       </c>
       <c r="AF4" s="3">
-        <f t="shared" ref="AF4:AJ4" si="2">AE4*1.02</f>
-        <v>13291.658195466925</v>
+        <f t="shared" si="1"/>
+        <v>15173.792986706156</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" si="2"/>
-        <v>13557.491359376265</v>
+        <f t="shared" si="1"/>
+        <v>15932.482636041465</v>
       </c>
       <c r="AH4" s="3">
-        <f t="shared" si="2"/>
-        <v>13828.641186563791</v>
+        <f t="shared" si="1"/>
+        <v>16729.106767843539</v>
       </c>
       <c r="AI4" s="3">
-        <f t="shared" si="2"/>
-        <v>14105.214010295067</v>
+        <f t="shared" si="1"/>
+        <v>17565.562106235717</v>
       </c>
       <c r="AJ4" s="3">
-        <f t="shared" si="2"/>
-        <v>14387.318290500969</v>
+        <f t="shared" si="1"/>
+        <v>18443.840211547504</v>
       </c>
     </row>
     <row r="5" spans="2:36" x14ac:dyDescent="0.3">
@@ -1283,13 +1281,10 @@
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-      <c r="Q5" s="3">
-        <f>M5*1.03</f>
-        <v>1305.01</v>
-      </c>
+      <c r="Q5" s="3"/>
       <c r="R5" s="3">
-        <f>N5*1.04</f>
-        <v>1341.6000000000001</v>
+        <f>N5*1.23</f>
+        <v>1586.7</v>
       </c>
       <c r="V5" s="3">
         <v>2182</v>
@@ -1360,13 +1355,10 @@
       </c>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="3">
-        <f>M6*1.05</f>
-        <v>433.65000000000003</v>
-      </c>
+      <c r="Q6" s="3"/>
       <c r="R6" s="3">
-        <f>N6*1.03</f>
-        <v>441.87</v>
+        <f>N6*1.15</f>
+        <v>493.34999999999997</v>
       </c>
       <c r="V6" s="3">
         <v>1146</v>
@@ -1415,7 +1407,10 @@
         <f>L5+L6</f>
         <v>1688</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <f>M5+M6</f>
+        <v>1680</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3">
         <v>1722</v>
@@ -1424,12 +1419,11 @@
         <v>1828</v>
       </c>
       <c r="Q7" s="3">
-        <f t="shared" ref="Q7:R7" si="3">Q5+Q6</f>
-        <v>1738.66</v>
+        <v>1976</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="3"/>
-        <v>1783.4700000000003</v>
+        <f t="shared" ref="Q7:R7" si="2">R5+R6</f>
+        <v>2080.0500000000002</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1440,47 +1434,47 @@
       </c>
       <c r="Z7" s="3">
         <f>SUM(O7:R7)</f>
-        <v>7072.13</v>
+        <v>7606.05</v>
       </c>
       <c r="AA7" s="3">
-        <f>Z7*1.03</f>
-        <v>7284.2939000000006</v>
+        <f>Z7*1.07</f>
+        <v>8138.473500000001</v>
       </c>
       <c r="AB7" s="3">
-        <f>AA7*1.02</f>
-        <v>7429.9797780000008</v>
+        <f>AA7*1.06</f>
+        <v>8626.7819100000015</v>
       </c>
       <c r="AC7" s="3">
-        <f>AB7*1.02</f>
-        <v>7578.5793735600009</v>
+        <f>AB7*1.05</f>
+        <v>9058.1210055000029</v>
       </c>
       <c r="AD7" s="3">
-        <f t="shared" ref="AD7:AE7" si="4">AC7*1.02</f>
-        <v>7730.1509610312014</v>
+        <f>AC7*1.04</f>
+        <v>9420.4458457200035</v>
       </c>
       <c r="AE7" s="3">
-        <f t="shared" si="4"/>
-        <v>7884.7539802518259</v>
+        <f t="shared" ref="AE7:AJ7" si="3">AD7*1.04</f>
+        <v>9797.2636795488033</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" ref="AF7:AJ7" si="5">AE7*1.01</f>
-        <v>7963.6015200543443</v>
+        <f t="shared" si="3"/>
+        <v>10189.154226730756</v>
       </c>
       <c r="AG7" s="3">
-        <f t="shared" si="5"/>
-        <v>8043.2375352548879</v>
+        <f t="shared" si="3"/>
+        <v>10596.720395799986</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" si="5"/>
-        <v>8123.6699106074366</v>
+        <f t="shared" si="3"/>
+        <v>11020.589211631986</v>
       </c>
       <c r="AI7" s="3">
-        <f t="shared" si="5"/>
-        <v>8204.906609713511</v>
+        <f t="shared" si="3"/>
+        <v>11461.412780097266</v>
       </c>
       <c r="AJ7" s="3">
-        <f t="shared" si="5"/>
-        <v>8286.9556758106464</v>
+        <f t="shared" si="3"/>
+        <v>11919.869291301156</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
@@ -1488,51 +1482,51 @@
         <v>16</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" ref="C8:N8" si="6">SUM(C3:C6)</f>
+        <f t="shared" ref="C8:N8" si="4">SUM(C3:C6)</f>
         <v>9536</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11035</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10978</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11418</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11298</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11949</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>11939</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12195</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12032</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12603</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>12630</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13141</v>
       </c>
       <c r="O8" s="3">
@@ -1540,16 +1534,16 @@
         <v>12798</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" ref="P8:R8" si="7">P3+P4+P7</f>
+        <f t="shared" ref="P8:R8" si="5">P3+P4+P7</f>
         <v>13669</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" si="7"/>
-        <v>13584.36</v>
+        <f t="shared" si="5"/>
+        <v>13940</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="7"/>
-        <v>13909.3</v>
+        <f t="shared" si="5"/>
+        <v>14297.650000000001</v>
       </c>
       <c r="V8" s="3">
         <f>SUM(V3:V6)</f>
@@ -1568,48 +1562,48 @@
         <v>57171</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" ref="Z8:AJ8" si="8">SUM(Z3:Z7)</f>
-        <v>53960.66</v>
+        <f t="shared" ref="Z8:AJ8" si="6">SUM(Z3:Z7)</f>
+        <v>54704.65</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" si="8"/>
-        <v>55805.950000000012</v>
+        <f t="shared" si="6"/>
+        <v>58016.135000000002</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="8"/>
-        <v>57086.513149000006</v>
+        <f t="shared" si="6"/>
+        <v>60675.095105</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="8"/>
-        <v>58195.102718070004</v>
+        <f t="shared" si="6"/>
+        <v>62759.90947815001</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="8"/>
-        <v>59217.786442828809</v>
+        <f t="shared" si="6"/>
+        <v>64183.5599188665</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="8"/>
-        <v>60140.295670198204</v>
+        <f t="shared" si="6"/>
+        <v>65658.531994985271</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="8"/>
-        <v>60872.009001365543</v>
+        <f t="shared" si="6"/>
+        <v>67187.084481958009</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="8"/>
-        <v>61613.645673333871</v>
+        <f t="shared" si="6"/>
+        <v>68771.581673047753</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="8"/>
-        <v>62365.357043660973</v>
+        <f t="shared" si="6"/>
+        <v>70414.498407093895</v>
       </c>
       <c r="AI8" s="3">
-        <f t="shared" si="8"/>
-        <v>63127.297025963213</v>
+        <f t="shared" si="6"/>
+        <v>72118.425338227535</v>
       </c>
       <c r="AJ8" s="3">
-        <f t="shared" si="8"/>
-        <v>63899.622136325801</v>
+        <f t="shared" si="6"/>
+        <v>73886.074459262163</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.3">
@@ -1659,12 +1653,11 @@
         <v>6264</v>
       </c>
       <c r="Q9" s="3">
-        <f>M9*1.02</f>
-        <v>6271.9800000000005</v>
+        <v>6617</v>
       </c>
       <c r="R9" s="3">
-        <f>N9*1.04</f>
-        <v>6320.08</v>
+        <f>N9*1.09</f>
+        <v>6623.93</v>
       </c>
       <c r="V9" s="3">
         <v>6633</v>
@@ -1683,47 +1676,47 @@
       </c>
       <c r="Z9" s="3">
         <f>SUM(O9:R9)</f>
-        <v>24991.059999999998</v>
+        <v>25639.93</v>
       </c>
       <c r="AA9" s="3">
-        <f>Z9*1.04</f>
-        <v>25990.702399999998</v>
+        <f>Z9*1.06</f>
+        <v>27178.325800000002</v>
       </c>
       <c r="AB9" s="3">
-        <f>AA9*1.03</f>
-        <v>26770.423471999999</v>
+        <f>AA9*1.04</f>
+        <v>28265.458832000004</v>
       </c>
       <c r="AC9" s="3">
-        <f>AB9*1.02</f>
-        <v>27305.831941439999</v>
+        <f>AB9*1.03</f>
+        <v>29113.422596960005</v>
       </c>
       <c r="AD9" s="3">
         <f>AC9*1.01</f>
-        <v>27578.890260854401</v>
+        <v>29404.556822929604</v>
       </c>
       <c r="AE9" s="3">
-        <f t="shared" ref="AE9:AJ9" si="9">AD9*1.01</f>
-        <v>27854.679163462944</v>
+        <f t="shared" ref="AE9:AJ9" si="7">AD9*1.01</f>
+        <v>29698.6023911589</v>
       </c>
       <c r="AF9" s="3">
-        <f t="shared" si="9"/>
-        <v>28133.225955097572</v>
+        <f t="shared" si="7"/>
+        <v>29995.588415070488</v>
       </c>
       <c r="AG9" s="3">
-        <f t="shared" si="9"/>
-        <v>28414.558214648547</v>
+        <f t="shared" si="7"/>
+        <v>30295.544299221194</v>
       </c>
       <c r="AH9" s="3">
-        <f t="shared" si="9"/>
-        <v>28698.703796795031</v>
+        <f t="shared" si="7"/>
+        <v>30598.499742213407</v>
       </c>
       <c r="AI9" s="3">
-        <f t="shared" si="9"/>
-        <v>28985.690834762983</v>
+        <f t="shared" si="7"/>
+        <v>30904.484739635544</v>
       </c>
       <c r="AJ9" s="3">
-        <f t="shared" si="9"/>
-        <v>29275.547743110612</v>
+        <f t="shared" si="7"/>
+        <v>31213.529587031899</v>
       </c>
     </row>
     <row r="10" spans="2:36" x14ac:dyDescent="0.3">
@@ -1773,11 +1766,10 @@
         <v>2077</v>
       </c>
       <c r="Q10" s="3">
-        <f>M10*0.98</f>
-        <v>2100.14</v>
+        <v>2131</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" ref="R10" si="10">N10*0.99</f>
+        <f t="shared" ref="R10" si="8">N10*0.99</f>
         <v>2018.61</v>
       </c>
       <c r="V10" s="3">
@@ -1792,52 +1784,52 @@
         <v>6849</v>
       </c>
       <c r="Y10" s="3">
-        <f t="shared" ref="Y10" si="11">SUM(K10:N10)</f>
+        <f t="shared" ref="Y10" si="9">SUM(K10:N10)</f>
         <v>8252</v>
       </c>
       <c r="Z10" s="3">
         <f>SUM(O10:R10)</f>
-        <v>8161.7499999999991</v>
+        <v>8192.61</v>
       </c>
       <c r="AA10" s="3">
         <f>Z10*1.05</f>
-        <v>8569.8374999999996</v>
+        <v>8602.2405000000017</v>
       </c>
       <c r="AB10" s="3">
         <f>AA10*1.03</f>
-        <v>8826.9326249999995</v>
+        <v>8860.3077150000026</v>
       </c>
       <c r="AC10" s="3">
         <f>AB10*1.02</f>
-        <v>9003.4712774999989</v>
+        <v>9037.5138693000026</v>
       </c>
       <c r="AD10" s="3">
         <f>AC10*1.01</f>
-        <v>9093.5059902749981</v>
+        <v>9127.8890079930025</v>
       </c>
       <c r="AE10" s="3">
-        <f t="shared" ref="AE10:AJ10" si="12">AD10*1.01</f>
-        <v>9184.4410501777475</v>
+        <f t="shared" ref="AE10:AJ10" si="10">AD10*1.01</f>
+        <v>9219.1678980729321</v>
       </c>
       <c r="AF10" s="3">
-        <f t="shared" si="12"/>
-        <v>9276.2854606795245</v>
+        <f t="shared" si="10"/>
+        <v>9311.3595770536613</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" si="12"/>
-        <v>9369.0483152863198</v>
+        <f t="shared" si="10"/>
+        <v>9404.4731728241986</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="12"/>
-        <v>9462.7387984391826</v>
+        <f t="shared" si="10"/>
+        <v>9498.5179045524401</v>
       </c>
       <c r="AI10" s="3">
-        <f t="shared" si="12"/>
-        <v>9557.3661864235746</v>
+        <f t="shared" si="10"/>
+        <v>9593.5030835979651</v>
       </c>
       <c r="AJ10" s="3">
-        <f t="shared" si="12"/>
-        <v>9652.9398482878096</v>
+        <f t="shared" si="10"/>
+        <v>9689.4381144339441</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1845,68 +1837,68 @@
         <v>18</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" ref="C11:R11" si="13">C9-C10</f>
+        <f t="shared" ref="C11:R11" si="11">C9-C10</f>
         <v>2199</v>
       </c>
       <c r="D11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2360</v>
       </c>
       <c r="E11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2578</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2758</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>2983</v>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3105</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3442</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3604</v>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3769</v>
       </c>
       <c r="L11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>3730</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4006</v>
       </c>
       <c r="N11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4038</v>
       </c>
       <c r="O11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4169</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>4187</v>
       </c>
       <c r="Q11" s="3">
-        <f t="shared" si="13"/>
-        <v>4171.84</v>
+        <f t="shared" si="11"/>
+        <v>4486</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="13"/>
-        <v>4301.47</v>
+        <f t="shared" si="11"/>
+        <v>4605.3200000000006</v>
       </c>
       <c r="V11" s="3">
         <f>V9-V10</f>
@@ -1921,52 +1913,52 @@
         <v>13134</v>
       </c>
       <c r="Y11" s="3">
-        <f t="shared" ref="Y11:AJ11" si="14">Y9-Y10</f>
+        <f t="shared" ref="Y11:AJ11" si="12">Y9-Y10</f>
         <v>15543</v>
       </c>
       <c r="Z11" s="3">
-        <f t="shared" si="14"/>
-        <v>16829.309999999998</v>
+        <f t="shared" si="12"/>
+        <v>17447.32</v>
       </c>
       <c r="AA11" s="3">
-        <f t="shared" si="14"/>
-        <v>17420.8649</v>
+        <f t="shared" si="12"/>
+        <v>18576.085299999999</v>
       </c>
       <c r="AB11" s="3">
-        <f t="shared" si="14"/>
-        <v>17943.490847000001</v>
+        <f t="shared" si="12"/>
+        <v>19405.151117000001</v>
       </c>
       <c r="AC11" s="3">
-        <f t="shared" si="14"/>
-        <v>18302.360663940002</v>
+        <f t="shared" si="12"/>
+        <v>20075.908727660004</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="14"/>
-        <v>18485.384270579401</v>
+        <f t="shared" si="12"/>
+        <v>20276.667814936602</v>
       </c>
       <c r="AE11" s="3">
-        <f t="shared" si="14"/>
-        <v>18670.238113285195</v>
+        <f t="shared" si="12"/>
+        <v>20479.434493085966</v>
       </c>
       <c r="AF11" s="3">
-        <f t="shared" si="14"/>
-        <v>18856.94049441805</v>
+        <f t="shared" si="12"/>
+        <v>20684.228838016825</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" si="14"/>
-        <v>19045.509899362227</v>
+        <f t="shared" si="12"/>
+        <v>20891.071126396993</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="14"/>
-        <v>19235.964998355848</v>
+        <f t="shared" si="12"/>
+        <v>21099.981837660969</v>
       </c>
       <c r="AI11" s="3">
-        <f t="shared" si="14"/>
-        <v>19428.32464833941</v>
+        <f t="shared" si="12"/>
+        <v>21310.981656037577</v>
       </c>
       <c r="AJ11" s="3">
-        <f t="shared" si="14"/>
-        <v>19622.607894822802</v>
+        <f t="shared" si="12"/>
+        <v>21524.091472597953</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
@@ -2015,7 +2007,9 @@
       <c r="P12" s="3">
         <v>226</v>
       </c>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="3">
+        <v>190</v>
+      </c>
       <c r="R12" s="3"/>
       <c r="V12" s="3">
         <v>-147</v>
@@ -2090,7 +2084,9 @@
       <c r="P13" s="3">
         <v>1094</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="3">
+        <v>1030</v>
+      </c>
       <c r="R13" s="3"/>
       <c r="V13" s="3">
         <v>-1146</v>
@@ -2165,7 +2161,9 @@
       <c r="P14" s="3">
         <v>85</v>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="3">
+        <v>67</v>
+      </c>
       <c r="R14" s="3"/>
       <c r="V14" s="3">
         <v>-179</v>
@@ -2199,62 +2197,65 @@
         <v>22</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:P15" si="15">SUM(C12:C14)</f>
+        <f t="shared" ref="C15:Q15" si="13">SUM(C12:C14)</f>
         <v>-33</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>410</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>778</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1027</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1055</v>
       </c>
       <c r="H15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1198</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1233</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1437</v>
       </c>
       <c r="K15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1269</v>
       </c>
       <c r="L15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1268</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1356</v>
       </c>
       <c r="N15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1292</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1150</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>1405</v>
       </c>
-      <c r="Q15" s="3"/>
+      <c r="Q15" s="3">
+        <f t="shared" si="13"/>
+        <v>1287</v>
+      </c>
       <c r="R15" s="3"/>
       <c r="V15" s="3">
         <f>SUM(V12:V14)</f>
@@ -2289,68 +2290,68 @@
         <v>23</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:R16" si="16">C8+C9</f>
+        <f t="shared" ref="C16:R16" si="14">C8+C9</f>
         <v>12056</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>13834</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>14352</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>15383</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>15714</v>
       </c>
       <c r="H16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>16724</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>17179</v>
       </c>
       <c r="J16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>17747</v>
       </c>
       <c r="K16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>17807</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>18397</v>
       </c>
       <c r="M16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>18779</v>
       </c>
       <c r="N16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>19218</v>
       </c>
       <c r="O16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>18933</v>
       </c>
       <c r="P16" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>19933</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="16"/>
-        <v>19856.34</v>
+        <f t="shared" si="14"/>
+        <v>20557</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" si="16"/>
-        <v>20229.379999999997</v>
+        <f t="shared" si="14"/>
+        <v>20921.580000000002</v>
       </c>
       <c r="V16" s="5">
         <f>V8+V9</f>
@@ -2370,47 +2371,47 @@
       </c>
       <c r="Z16" s="5">
         <f>Z8+Z9</f>
-        <v>78951.72</v>
+        <v>80344.58</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" ref="AA16:AJ16" si="17">AA8+AA9</f>
-        <v>81796.652400000006</v>
+        <f t="shared" ref="AA16:AJ16" si="15">AA8+AA9</f>
+        <v>85194.460800000001</v>
       </c>
       <c r="AB16" s="5">
-        <f t="shared" si="17"/>
-        <v>83856.936621000001</v>
+        <f t="shared" si="15"/>
+        <v>88940.553937000004</v>
       </c>
       <c r="AC16" s="5">
-        <f t="shared" si="17"/>
-        <v>85500.934659510007</v>
+        <f t="shared" si="15"/>
+        <v>91873.332075110011</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" si="17"/>
-        <v>86796.676703683217</v>
+        <f t="shared" si="15"/>
+        <v>93588.116741796111</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="17"/>
-        <v>87994.974833661152</v>
+        <f t="shared" si="15"/>
+        <v>95357.134386144171</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="17"/>
-        <v>89005.234956463115</v>
+        <f t="shared" si="15"/>
+        <v>97182.672897028504</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="17"/>
-        <v>90028.20388798241</v>
+        <f t="shared" si="15"/>
+        <v>99067.125972268943</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="17"/>
-        <v>91064.060840456004</v>
+        <f t="shared" si="15"/>
+        <v>101012.9981493073</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="17"/>
-        <v>92112.987860726193</v>
+        <f t="shared" si="15"/>
+        <v>103022.91007786308</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="17"/>
-        <v>93175.169879436406</v>
+        <f t="shared" si="15"/>
+        <v>105099.60404629406</v>
       </c>
     </row>
     <row r="17" spans="2:153" x14ac:dyDescent="0.3">
@@ -2459,7 +2460,9 @@
       <c r="P17" s="3">
         <v>4618</v>
       </c>
-      <c r="Q17" s="3"/>
+      <c r="Q17" s="3">
+        <v>4608</v>
+      </c>
       <c r="R17" s="3"/>
       <c r="V17" s="3">
         <v>7975</v>
@@ -2473,7 +2476,7 @@
         <v>15367</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" ref="Y17:Y19" si="18">SUM(K17:N17)</f>
+        <f t="shared" ref="Y17:Y19" si="16">SUM(K17:N17)</f>
         <v>16599</v>
       </c>
       <c r="Z17" s="3"/>
@@ -2534,7 +2537,9 @@
       <c r="P18" s="3">
         <v>1589</v>
       </c>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="3">
+        <v>1611</v>
+      </c>
       <c r="R18" s="3"/>
       <c r="V18" s="3">
         <v>2634</v>
@@ -2548,7 +2553,7 @@
         <v>5657</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>5886</v>
       </c>
       <c r="Z18" s="3"/>
@@ -2609,7 +2614,9 @@
       <c r="P19" s="3">
         <v>1301</v>
       </c>
-      <c r="Q19" s="3"/>
+      <c r="Q19" s="3">
+        <v>1477</v>
+      </c>
       <c r="R19" s="3"/>
       <c r="V19" s="3">
         <v>1328</v>
@@ -2623,7 +2630,7 @@
         <v>3968</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>4782</v>
       </c>
       <c r="Z19" s="3"/>
@@ -2643,68 +2650,68 @@
         <v>27</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:P20" si="19">SUM(C17:C19)+C15+C10</f>
+        <f t="shared" ref="C20:Q20" si="17">SUM(C17:C19)+C15+C10</f>
         <v>5068</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>6522</v>
       </c>
       <c r="E20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>7113</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>8146</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>8630</v>
       </c>
       <c r="H20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>9161</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>9191</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>9782</v>
       </c>
       <c r="K20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>9612</v>
       </c>
       <c r="L20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>10140</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>10276</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>10676</v>
       </c>
       <c r="O20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>10351</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>10990</v>
       </c>
       <c r="Q20" s="3">
-        <f>Q16*0.55</f>
-        <v>10920.987000000001</v>
+        <f t="shared" si="17"/>
+        <v>11114</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" ref="R20" si="20">R16*0.56</f>
-        <v>11328.452799999999</v>
+        <f t="shared" ref="R20" si="18">R16*0.56</f>
+        <v>11716.084800000002</v>
       </c>
       <c r="V20" s="3">
         <f>SUM(V17:V19)+V15+V10</f>
@@ -2724,47 +2731,47 @@
       </c>
       <c r="Z20" s="3">
         <f>SUM(O20:R20)</f>
-        <v>43590.4398</v>
+        <v>44171.084800000004</v>
       </c>
       <c r="AA20" s="3">
-        <f t="shared" ref="AA20:AJ20" si="21">AA16-AA21</f>
-        <v>44988.158820000004</v>
+        <f t="shared" ref="AA20:AJ20" si="19">AA16-AA21</f>
+        <v>46856.953439999997</v>
       </c>
       <c r="AB20" s="3">
-        <f t="shared" si="21"/>
-        <v>46121.315141549996</v>
+        <f t="shared" si="19"/>
+        <v>48917.304665349999</v>
       </c>
       <c r="AC20" s="3">
-        <f t="shared" si="21"/>
-        <v>47025.514062730501</v>
+        <f t="shared" si="19"/>
+        <v>50530.332641310502</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="21"/>
-        <v>47738.172187025768</v>
+        <f t="shared" si="19"/>
+        <v>51473.464207987861</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" si="21"/>
-        <v>48397.236158513631</v>
+        <f t="shared" si="19"/>
+        <v>52446.423912379294</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="21"/>
-        <v>48952.879226054712</v>
+        <f t="shared" si="19"/>
+        <v>53450.470093365679</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="21"/>
-        <v>49515.512138390324</v>
+        <f t="shared" si="19"/>
+        <v>54486.919284747921</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="21"/>
-        <v>50085.233462250799</v>
+        <f t="shared" si="19"/>
+        <v>55557.148982119012</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="21"/>
-        <v>50662.143323399403</v>
+        <f t="shared" si="19"/>
+        <v>56662.600542824694</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="21"/>
-        <v>51246.343433690025</v>
+        <f t="shared" si="19"/>
+        <v>57804.782225461728</v>
       </c>
     </row>
     <row r="21" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2772,68 +2779,68 @@
         <v>28</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" ref="C21:R21" si="22">C16-C20</f>
+        <f t="shared" ref="C21:R21" si="20">C16-C20</f>
         <v>6988</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7312</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7239</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7237</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7084</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7563</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7988</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>7965</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8195</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8257</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8503</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8542</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8582</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>8943</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="22"/>
-        <v>8935.3529999999992</v>
+        <f t="shared" si="20"/>
+        <v>9443</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="22"/>
-        <v>8900.9271999999983</v>
+        <f t="shared" si="20"/>
+        <v>9205.4951999999994</v>
       </c>
       <c r="V21" s="5">
         <f>V16-V20</f>
@@ -2853,47 +2860,47 @@
       </c>
       <c r="Z21" s="5">
         <f>Z16-Z20</f>
-        <v>35361.280200000001</v>
+        <v>36173.495199999998</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" ref="AA21:AJ21" si="23">AA16*0.45</f>
-        <v>36808.493580000002</v>
+        <f t="shared" ref="AA21:AJ21" si="21">AA16*0.45</f>
+        <v>38337.507360000003</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" si="23"/>
-        <v>37735.621479450005</v>
+        <f t="shared" si="21"/>
+        <v>40023.249271650006</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" si="23"/>
-        <v>38475.420596779506</v>
+        <f t="shared" si="21"/>
+        <v>41342.999433799509</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" si="23"/>
-        <v>39058.504516657449</v>
+        <f t="shared" si="21"/>
+        <v>42114.65253380825</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" si="23"/>
-        <v>39597.738675147521</v>
+        <f t="shared" si="21"/>
+        <v>42910.710473764877</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" si="23"/>
-        <v>40052.355730408402</v>
+        <f t="shared" si="21"/>
+        <v>43732.202803662825</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" si="23"/>
-        <v>40512.691749592086</v>
+        <f t="shared" si="21"/>
+        <v>44580.206687521022</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" si="23"/>
-        <v>40978.827378205206</v>
+        <f t="shared" si="21"/>
+        <v>45455.849167188288</v>
       </c>
       <c r="AI21" s="5">
-        <f t="shared" si="23"/>
-        <v>41450.84453732679</v>
+        <f t="shared" si="21"/>
+        <v>46360.309535038388</v>
       </c>
       <c r="AJ21" s="5">
-        <f t="shared" si="23"/>
-        <v>41928.826445746381</v>
+        <f t="shared" si="21"/>
+        <v>47294.821820832331</v>
       </c>
     </row>
     <row r="22" spans="2:153" x14ac:dyDescent="0.3">
@@ -2943,12 +2950,11 @@
         <v>1555</v>
       </c>
       <c r="Q22" s="3">
-        <f t="shared" ref="Q22:R22" si="24">Q16*0.08</f>
-        <v>1588.5072</v>
+        <v>1599</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="24"/>
-        <v>1618.3503999999998</v>
+        <f t="shared" ref="Q22:R22" si="22">R16*0.08</f>
+        <v>1673.7264000000002</v>
       </c>
       <c r="V22" s="3">
         <v>3706</v>
@@ -2967,47 +2973,47 @@
       </c>
       <c r="Z22" s="3">
         <f>SUM(O22:R22)</f>
-        <v>6247.8575999999994</v>
+        <v>6313.7264000000005</v>
       </c>
       <c r="AA22" s="3">
-        <f t="shared" ref="AA22:AJ22" si="25">AA16*0.08</f>
-        <v>6543.7321920000004</v>
+        <f t="shared" ref="AA22:AJ22" si="23">AA16*0.08</f>
+        <v>6815.5568640000001</v>
       </c>
       <c r="AB22" s="3">
-        <f t="shared" si="25"/>
-        <v>6708.55492968</v>
+        <f t="shared" si="23"/>
+        <v>7115.2443149600003</v>
       </c>
       <c r="AC22" s="3">
-        <f t="shared" si="25"/>
-        <v>6840.0747727608004</v>
+        <f t="shared" si="23"/>
+        <v>7349.8665660088009</v>
       </c>
       <c r="AD22" s="3">
-        <f t="shared" si="25"/>
-        <v>6943.7341362946572</v>
+        <f t="shared" si="23"/>
+        <v>7487.0493393436891</v>
       </c>
       <c r="AE22" s="3">
-        <f t="shared" si="25"/>
-        <v>7039.5979866928919</v>
+        <f t="shared" si="23"/>
+        <v>7628.5707508915339</v>
       </c>
       <c r="AF22" s="3">
-        <f t="shared" si="25"/>
-        <v>7120.4187965170495</v>
+        <f t="shared" si="23"/>
+        <v>7774.6138317622808</v>
       </c>
       <c r="AG22" s="3">
-        <f t="shared" si="25"/>
-        <v>7202.2563110385927</v>
+        <f t="shared" si="23"/>
+        <v>7925.3700777815156</v>
       </c>
       <c r="AH22" s="3">
-        <f t="shared" si="25"/>
-        <v>7285.1248672364809</v>
+        <f t="shared" si="23"/>
+        <v>8081.0398519445844</v>
       </c>
       <c r="AI22" s="3">
-        <f t="shared" si="25"/>
-        <v>7369.0390288580957</v>
+        <f t="shared" si="23"/>
+        <v>8241.8328062290475</v>
       </c>
       <c r="AJ22" s="3">
-        <f t="shared" si="25"/>
-        <v>7454.0135903549126</v>
+        <f t="shared" si="23"/>
+        <v>8407.9683237035242</v>
       </c>
     </row>
     <row r="23" spans="2:153" x14ac:dyDescent="0.3">
@@ -3057,12 +3063,11 @@
         <v>2152</v>
       </c>
       <c r="Q23" s="3">
-        <f>M23*1.07</f>
-        <v>2192.4300000000003</v>
+        <v>2239</v>
       </c>
       <c r="R23" s="3">
-        <f>N23*1.05</f>
-        <v>2207.1</v>
+        <f>N23*1.07</f>
+        <v>2249.1400000000003</v>
       </c>
       <c r="V23" s="3">
         <v>4586</v>
@@ -3081,47 +3086,47 @@
       </c>
       <c r="Z23" s="3">
         <f>SUM(O23:R23)</f>
-        <v>8671.5300000000007</v>
+        <v>8760.14</v>
       </c>
       <c r="AA23" s="3">
-        <f>Z23*1.04</f>
-        <v>9018.3912000000018</v>
+        <f>Z23*1.05</f>
+        <v>9198.146999999999</v>
       </c>
       <c r="AB23" s="3">
         <f>AA23*1.03</f>
-        <v>9288.9429360000013</v>
+        <v>9474.0914099999991</v>
       </c>
       <c r="AC23" s="3">
         <f>AB23*1.02</f>
-        <v>9474.7217947200006</v>
+        <v>9663.5732381999987</v>
       </c>
       <c r="AD23" s="3">
-        <f t="shared" ref="AD23:AJ23" si="26">AC23*1.01</f>
-        <v>9569.4690126672012</v>
+        <f>AC23*1.02</f>
+        <v>9856.8447029639992</v>
       </c>
       <c r="AE23" s="3">
-        <f t="shared" si="26"/>
-        <v>9665.1637027938741</v>
+        <f>AD23*1.02</f>
+        <v>10053.981597023279</v>
       </c>
       <c r="AF23" s="3">
-        <f t="shared" si="26"/>
-        <v>9761.8153398218128</v>
+        <f t="shared" ref="AD23:AJ23" si="24">AE23*1.01</f>
+        <v>10154.521412993512</v>
       </c>
       <c r="AG23" s="3">
-        <f t="shared" si="26"/>
-        <v>9859.4334932200309</v>
+        <f t="shared" si="24"/>
+        <v>10256.066627123448</v>
       </c>
       <c r="AH23" s="3">
-        <f t="shared" si="26"/>
-        <v>9958.0278281522315</v>
+        <f t="shared" si="24"/>
+        <v>10358.627293394682</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" si="26"/>
-        <v>10057.608106433754</v>
+        <f t="shared" si="24"/>
+        <v>10462.213566328628</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="26"/>
-        <v>10158.184187498091</v>
+        <f t="shared" si="24"/>
+        <v>10566.835701991915</v>
       </c>
     </row>
     <row r="24" spans="2:153" x14ac:dyDescent="0.3">
@@ -3178,12 +3183,11 @@
         <v>1686</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" ref="Q24" si="27">Q16*0.08</f>
-        <v>1588.5072</v>
+        <v>1780</v>
       </c>
       <c r="R24" s="3">
         <f>R16*0.11</f>
-        <v>2225.2317999999996</v>
+        <v>2301.3738000000003</v>
       </c>
       <c r="V24" s="3">
         <f>1351+1772-28</f>
@@ -3203,47 +3207,47 @@
       </c>
       <c r="Z24" s="3">
         <f>SUM(O24:R24)</f>
-        <v>7145.7389999999996</v>
+        <v>7413.3738000000003</v>
       </c>
       <c r="AA24" s="3">
-        <f t="shared" ref="AA24:AJ24" si="28">AA16*0.08</f>
-        <v>6543.7321920000004</v>
+        <f t="shared" ref="AA24:AJ24" si="25">AA16*0.08</f>
+        <v>6815.5568640000001</v>
       </c>
       <c r="AB24" s="3">
-        <f t="shared" si="28"/>
-        <v>6708.55492968</v>
+        <f t="shared" si="25"/>
+        <v>7115.2443149600003</v>
       </c>
       <c r="AC24" s="3">
-        <f t="shared" si="28"/>
-        <v>6840.0747727608004</v>
+        <f t="shared" si="25"/>
+        <v>7349.8665660088009</v>
       </c>
       <c r="AD24" s="3">
-        <f t="shared" si="28"/>
-        <v>6943.7341362946572</v>
+        <f t="shared" si="25"/>
+        <v>7487.0493393436891</v>
       </c>
       <c r="AE24" s="3">
-        <f t="shared" si="28"/>
-        <v>7039.5979866928919</v>
+        <f t="shared" si="25"/>
+        <v>7628.5707508915339</v>
       </c>
       <c r="AF24" s="3">
-        <f t="shared" si="28"/>
-        <v>7120.4187965170495</v>
+        <f t="shared" si="25"/>
+        <v>7774.6138317622808</v>
       </c>
       <c r="AG24" s="3">
-        <f t="shared" si="28"/>
-        <v>7202.2563110385927</v>
+        <f t="shared" si="25"/>
+        <v>7925.3700777815156</v>
       </c>
       <c r="AH24" s="3">
-        <f t="shared" si="28"/>
-        <v>7285.1248672364809</v>
+        <f t="shared" si="25"/>
+        <v>8081.0398519445844</v>
       </c>
       <c r="AI24" s="3">
-        <f t="shared" si="28"/>
-        <v>7369.0390288580957</v>
+        <f t="shared" si="25"/>
+        <v>8241.8328062290475</v>
       </c>
       <c r="AJ24" s="3">
-        <f t="shared" si="28"/>
-        <v>7454.0135903549126</v>
+        <f t="shared" si="25"/>
+        <v>8407.9683237035242</v>
       </c>
     </row>
     <row r="25" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3251,68 +3255,68 @@
         <v>32</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:L25" si="29">C21-SUM(C22:C24)</f>
+        <f t="shared" ref="C25:L25" si="26">C21-SUM(C22:C24)</f>
         <v>2712</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2543</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2459</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>1871</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2167</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2734</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>3100</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>2512</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>3145</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>3790</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" ref="M25:R25" si="30">M21-SUM(M22:M24)</f>
+        <f t="shared" ref="M25:R25" si="27">M21-SUM(M22:M24)</f>
         <v>3204</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>2756</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>3330</v>
       </c>
       <c r="P25" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="27"/>
         <v>3550</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="30"/>
-        <v>3565.9085999999988</v>
+        <f t="shared" si="27"/>
+        <v>3825</v>
       </c>
       <c r="R25" s="5">
-        <f t="shared" si="30"/>
-        <v>2850.244999999999</v>
+        <f t="shared" si="27"/>
+        <v>2981.2549999999983</v>
       </c>
       <c r="V25" s="5">
         <f>V21-SUM(V22:V24)</f>
@@ -3331,48 +3335,48 @@
         <v>12895</v>
       </c>
       <c r="Z25" s="5">
-        <f t="shared" ref="Z25:AJ25" si="31">Z21-SUM(Z22:Z24)</f>
-        <v>13296.153600000001</v>
+        <f t="shared" ref="Z25:AJ25" si="28">Z21-SUM(Z22:Z24)</f>
+        <v>13686.254999999997</v>
       </c>
       <c r="AA25" s="5">
-        <f t="shared" si="31"/>
-        <v>14702.637996000001</v>
+        <f t="shared" si="28"/>
+        <v>15508.246632000002</v>
       </c>
       <c r="AB25" s="5">
-        <f t="shared" si="31"/>
-        <v>15029.568684090002</v>
+        <f t="shared" si="28"/>
+        <v>16318.669231730004</v>
       </c>
       <c r="AC25" s="5">
-        <f t="shared" si="31"/>
-        <v>15320.549256537906</v>
+        <f t="shared" si="28"/>
+        <v>16979.693063581908</v>
       </c>
       <c r="AD25" s="5">
-        <f t="shared" si="31"/>
-        <v>15601.567231400932</v>
+        <f t="shared" si="28"/>
+        <v>17283.709152156873</v>
       </c>
       <c r="AE25" s="5">
-        <f t="shared" si="31"/>
-        <v>15853.378998967863</v>
+        <f t="shared" si="28"/>
+        <v>17599.58737495853</v>
       </c>
       <c r="AF25" s="5">
-        <f t="shared" si="31"/>
-        <v>16049.702797552491</v>
+        <f t="shared" si="28"/>
+        <v>18028.453727144748</v>
       </c>
       <c r="AG25" s="5">
-        <f t="shared" si="31"/>
-        <v>16248.745634294868</v>
+        <f t="shared" si="28"/>
+        <v>18473.399904834543</v>
       </c>
       <c r="AH25" s="5">
-        <f t="shared" si="31"/>
-        <v>16450.549815580012</v>
+        <f t="shared" si="28"/>
+        <v>18935.142169904437</v>
       </c>
       <c r="AI25" s="5">
-        <f t="shared" si="31"/>
-        <v>16655.158373176844</v>
+        <f t="shared" si="28"/>
+        <v>19414.430356251665</v>
       </c>
       <c r="AJ25" s="5">
-        <f t="shared" si="31"/>
-        <v>16862.615077538463</v>
+        <f t="shared" si="28"/>
+        <v>19912.049471433365</v>
       </c>
     </row>
     <row r="26" spans="2:153" x14ac:dyDescent="0.3">
@@ -3422,12 +3426,11 @@
         <v>665</v>
       </c>
       <c r="Q26" s="3">
-        <f t="shared" ref="Q26:R26" si="32">Q25*0.21</f>
-        <v>748.8408059999997</v>
+        <v>923</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="32"/>
-        <v>598.55144999999982</v>
+        <f t="shared" ref="Q26:R26" si="29">R25*0.21</f>
+        <v>626.06354999999962</v>
       </c>
       <c r="V26" s="3">
         <v>2042</v>
@@ -3446,47 +3449,47 @@
       </c>
       <c r="Z26" s="3">
         <f>SUM(O26:R26)</f>
-        <v>2758.3922559999996</v>
+        <v>2960.0635499999999</v>
       </c>
       <c r="AA26" s="3">
-        <f t="shared" ref="AA26:AJ26" si="33">AA25*0.2</f>
-        <v>2940.5275992000006</v>
+        <f t="shared" ref="AA26:AJ26" si="30">AA25*0.2</f>
+        <v>3101.6493264000005</v>
       </c>
       <c r="AB26" s="3">
-        <f t="shared" si="33"/>
-        <v>3005.9137368180004</v>
+        <f t="shared" si="30"/>
+        <v>3263.733846346001</v>
       </c>
       <c r="AC26" s="3">
-        <f t="shared" si="33"/>
-        <v>3064.1098513075813</v>
+        <f t="shared" si="30"/>
+        <v>3395.9386127163816</v>
       </c>
       <c r="AD26" s="3">
-        <f t="shared" si="33"/>
-        <v>3120.3134462801863</v>
+        <f t="shared" si="30"/>
+        <v>3456.7418304313746</v>
       </c>
       <c r="AE26" s="3">
-        <f t="shared" si="33"/>
-        <v>3170.6757997935729</v>
+        <f t="shared" si="30"/>
+        <v>3519.9174749917061</v>
       </c>
       <c r="AF26" s="3">
-        <f t="shared" si="33"/>
-        <v>3209.9405595104981</v>
+        <f t="shared" si="30"/>
+        <v>3605.6907454289499</v>
       </c>
       <c r="AG26" s="3">
-        <f t="shared" si="33"/>
-        <v>3249.7491268589738</v>
+        <f t="shared" si="30"/>
+        <v>3694.6799809669087</v>
       </c>
       <c r="AH26" s="3">
-        <f t="shared" si="33"/>
-        <v>3290.1099631160027</v>
+        <f t="shared" si="30"/>
+        <v>3787.0284339808877</v>
       </c>
       <c r="AI26" s="3">
-        <f t="shared" si="33"/>
-        <v>3331.0316746353692</v>
+        <f t="shared" si="30"/>
+        <v>3882.8860712503333</v>
       </c>
       <c r="AJ26" s="3">
-        <f t="shared" si="33"/>
-        <v>3372.5230155076929</v>
+        <f t="shared" si="30"/>
+        <v>3982.4098942866731</v>
       </c>
     </row>
     <row r="27" spans="2:153" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3494,68 +3497,68 @@
         <v>34</v>
       </c>
       <c r="C27" s="5">
-        <f t="shared" ref="C27:L27" si="34">C25-C26</f>
+        <f t="shared" ref="C27:L27" si="31">C25-C26</f>
         <v>2099</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>1964</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>1879</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>1572</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>1816</v>
       </c>
       <c r="H27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>2174</v>
       </c>
       <c r="I27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>2451</v>
       </c>
       <c r="J27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>1933</v>
       </c>
       <c r="K27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>2437</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>3015</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" ref="M27:N27" si="35">M25-M26</f>
+        <f t="shared" ref="M27:N27" si="32">M25-M26</f>
         <v>2507</v>
       </c>
       <c r="N27" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>2170</v>
       </c>
       <c r="O27" s="5">
-        <f t="shared" ref="O27:R27" si="36">O25-O26</f>
+        <f t="shared" ref="O27:R27" si="33">O25-O26</f>
         <v>2584</v>
       </c>
       <c r="P27" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="33"/>
         <v>2885</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="36"/>
-        <v>2817.0677939999991</v>
+        <f t="shared" si="33"/>
+        <v>2902</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="36"/>
-        <v>2251.693549999999</v>
+        <f t="shared" si="33"/>
+        <v>2355.1914499999984</v>
       </c>
       <c r="V27" s="5">
         <f>V25-V26</f>
@@ -3575,515 +3578,515 @@
       </c>
       <c r="Z27" s="5">
         <f>Z25-Z26</f>
-        <v>10537.761344000002</v>
+        <v>10726.191449999998</v>
       </c>
       <c r="AA27" s="5">
-        <f t="shared" ref="AA27:AJ27" si="37">AA25-AA26</f>
-        <v>11762.110396800001</v>
+        <f t="shared" ref="AA27:AJ27" si="34">AA25-AA26</f>
+        <v>12406.597305600002</v>
       </c>
       <c r="AB27" s="5">
-        <f t="shared" si="37"/>
-        <v>12023.654947272002</v>
+        <f t="shared" si="34"/>
+        <v>13054.935385384004</v>
       </c>
       <c r="AC27" s="5">
-        <f t="shared" si="37"/>
-        <v>12256.439405230325</v>
+        <f t="shared" si="34"/>
+        <v>13583.754450865526</v>
       </c>
       <c r="AD27" s="5">
-        <f t="shared" si="37"/>
-        <v>12481.253785120745</v>
+        <f t="shared" si="34"/>
+        <v>13826.967321725499</v>
       </c>
       <c r="AE27" s="5">
-        <f t="shared" si="37"/>
-        <v>12682.70319917429</v>
+        <f t="shared" si="34"/>
+        <v>14079.669899966824</v>
       </c>
       <c r="AF27" s="5">
-        <f t="shared" si="37"/>
-        <v>12839.762238041993</v>
+        <f t="shared" si="34"/>
+        <v>14422.762981715798</v>
       </c>
       <c r="AG27" s="5">
-        <f t="shared" si="37"/>
-        <v>12998.996507435895</v>
+        <f t="shared" si="34"/>
+        <v>14778.719923867635</v>
       </c>
       <c r="AH27" s="5">
-        <f t="shared" si="37"/>
-        <v>13160.439852464009</v>
+        <f t="shared" si="34"/>
+        <v>15148.113735923549</v>
       </c>
       <c r="AI27" s="5">
-        <f t="shared" si="37"/>
-        <v>13324.126698541475</v>
+        <f t="shared" si="34"/>
+        <v>15531.544285001331</v>
       </c>
       <c r="AJ27" s="5">
-        <f t="shared" si="37"/>
-        <v>13490.09206203077</v>
+        <f t="shared" si="34"/>
+        <v>15929.639577146692</v>
       </c>
       <c r="AK27" s="4">
         <f>AJ27*(1+$AN$39)</f>
-        <v>13355.191141410462</v>
+        <v>15770.343181375225</v>
       </c>
       <c r="AL27" s="4">
-        <f t="shared" ref="AL27:CW27" si="38">AK27*(1+$AN$39)</f>
-        <v>13221.639229996357</v>
+        <f t="shared" ref="AL27:CW27" si="35">AK27*(1+$AN$39)</f>
+        <v>15612.639749561473</v>
       </c>
       <c r="AM27" s="4">
-        <f t="shared" si="38"/>
-        <v>13089.422837696393</v>
+        <f t="shared" si="35"/>
+        <v>15456.513352065858</v>
       </c>
       <c r="AN27" s="4">
-        <f t="shared" si="38"/>
-        <v>12958.528609319428</v>
+        <f t="shared" si="35"/>
+        <v>15301.9482185452</v>
       </c>
       <c r="AO27" s="4">
-        <f t="shared" si="38"/>
-        <v>12828.943323226234</v>
+        <f t="shared" si="35"/>
+        <v>15148.928736359747</v>
       </c>
       <c r="AP27" s="4">
-        <f t="shared" si="38"/>
-        <v>12700.653889993971</v>
+        <f t="shared" si="35"/>
+        <v>14997.439448996149</v>
       </c>
       <c r="AQ27" s="4">
-        <f t="shared" si="38"/>
-        <v>12573.647351094032</v>
+        <f t="shared" si="35"/>
+        <v>14847.465054506187</v>
       </c>
       <c r="AR27" s="4">
-        <f t="shared" si="38"/>
-        <v>12447.910877583092</v>
+        <f t="shared" si="35"/>
+        <v>14698.990403961125</v>
       </c>
       <c r="AS27" s="4">
-        <f t="shared" si="38"/>
-        <v>12323.431768807261</v>
+        <f t="shared" si="35"/>
+        <v>14552.000499921513</v>
       </c>
       <c r="AT27" s="4">
-        <f t="shared" si="38"/>
-        <v>12200.197451119187</v>
+        <f t="shared" si="35"/>
+        <v>14406.480494922298</v>
       </c>
       <c r="AU27" s="4">
-        <f t="shared" si="38"/>
-        <v>12078.195476607996</v>
+        <f t="shared" si="35"/>
+        <v>14262.415689973075</v>
       </c>
       <c r="AV27" s="4">
-        <f t="shared" si="38"/>
-        <v>11957.413521841916</v>
+        <f t="shared" si="35"/>
+        <v>14119.791533073345</v>
       </c>
       <c r="AW27" s="4">
-        <f t="shared" si="38"/>
-        <v>11837.839386623496</v>
+        <f t="shared" si="35"/>
+        <v>13978.593617742612</v>
       </c>
       <c r="AX27" s="4">
-        <f t="shared" si="38"/>
-        <v>11719.460992757262</v>
+        <f t="shared" si="35"/>
+        <v>13838.807681565186</v>
       </c>
       <c r="AY27" s="4">
-        <f t="shared" si="38"/>
-        <v>11602.26638282969</v>
+        <f t="shared" si="35"/>
+        <v>13700.419604749533</v>
       </c>
       <c r="AZ27" s="4">
-        <f t="shared" si="38"/>
-        <v>11486.243719001393</v>
+        <f t="shared" si="35"/>
+        <v>13563.415408702038</v>
       </c>
       <c r="BA27" s="4">
-        <f t="shared" si="38"/>
-        <v>11371.38128181138</v>
+        <f t="shared" si="35"/>
+        <v>13427.781254615018</v>
       </c>
       <c r="BB27" s="4">
-        <f t="shared" si="38"/>
-        <v>11257.667468993266</v>
+        <f t="shared" si="35"/>
+        <v>13293.503442068868</v>
       </c>
       <c r="BC27" s="4">
-        <f t="shared" si="38"/>
-        <v>11145.090794303333</v>
+        <f t="shared" si="35"/>
+        <v>13160.568407648179</v>
       </c>
       <c r="BD27" s="4">
-        <f t="shared" si="38"/>
-        <v>11033.639886360299</v>
+        <f t="shared" si="35"/>
+        <v>13028.962723571698</v>
       </c>
       <c r="BE27" s="4">
-        <f t="shared" si="38"/>
-        <v>10923.303487496696</v>
+        <f t="shared" si="35"/>
+        <v>12898.673096335981</v>
       </c>
       <c r="BF27" s="4">
-        <f t="shared" si="38"/>
-        <v>10814.070452621729</v>
+        <f t="shared" si="35"/>
+        <v>12769.686365372621</v>
       </c>
       <c r="BG27" s="4">
-        <f t="shared" si="38"/>
-        <v>10705.929748095512</v>
+        <f t="shared" si="35"/>
+        <v>12641.989501718896</v>
       </c>
       <c r="BH27" s="4">
-        <f t="shared" si="38"/>
-        <v>10598.870450614557</v>
+        <f t="shared" si="35"/>
+        <v>12515.569606701707</v>
       </c>
       <c r="BI27" s="4">
-        <f t="shared" si="38"/>
-        <v>10492.881746108411</v>
+        <f t="shared" si="35"/>
+        <v>12390.41391063469</v>
       </c>
       <c r="BJ27" s="4">
-        <f t="shared" si="38"/>
-        <v>10387.952928647326</v>
+        <f t="shared" si="35"/>
+        <v>12266.509771528343</v>
       </c>
       <c r="BK27" s="4">
-        <f t="shared" si="38"/>
-        <v>10284.073399360854</v>
+        <f t="shared" si="35"/>
+        <v>12143.844673813059</v>
       </c>
       <c r="BL27" s="4">
-        <f t="shared" si="38"/>
-        <v>10181.232665367244</v>
+        <f t="shared" si="35"/>
+        <v>12022.406227074927</v>
       </c>
       <c r="BM27" s="4">
-        <f t="shared" si="38"/>
-        <v>10079.420338713571</v>
+        <f t="shared" si="35"/>
+        <v>11902.182164804179</v>
       </c>
       <c r="BN27" s="4">
-        <f t="shared" si="38"/>
-        <v>9978.6261353264363</v>
+        <f t="shared" si="35"/>
+        <v>11783.160343156136</v>
       </c>
       <c r="BO27" s="4">
-        <f t="shared" si="38"/>
-        <v>9878.8398739731711</v>
+        <f t="shared" si="35"/>
+        <v>11665.328739724575</v>
       </c>
       <c r="BP27" s="4">
-        <f t="shared" si="38"/>
-        <v>9780.0514752334384</v>
+        <f t="shared" si="35"/>
+        <v>11548.675452327328</v>
       </c>
       <c r="BQ27" s="4">
-        <f t="shared" si="38"/>
-        <v>9682.2509604811039</v>
+        <f t="shared" si="35"/>
+        <v>11433.188697804055</v>
       </c>
       <c r="BR27" s="4">
-        <f t="shared" si="38"/>
-        <v>9585.4284508762921</v>
+        <f t="shared" si="35"/>
+        <v>11318.856810826013</v>
       </c>
       <c r="BS27" s="4">
-        <f t="shared" si="38"/>
-        <v>9489.574166367529</v>
+        <f t="shared" si="35"/>
+        <v>11205.668242717753</v>
       </c>
       <c r="BT27" s="4">
-        <f t="shared" si="38"/>
-        <v>9394.678424703854</v>
+        <f t="shared" si="35"/>
+        <v>11093.611560290576</v>
       </c>
       <c r="BU27" s="4">
-        <f t="shared" si="38"/>
-        <v>9300.7316404568155</v>
+        <f t="shared" si="35"/>
+        <v>10982.675444687669</v>
       </c>
       <c r="BV27" s="4">
-        <f t="shared" si="38"/>
-        <v>9207.7243240522475</v>
+        <f t="shared" si="35"/>
+        <v>10872.848690240793</v>
       </c>
       <c r="BW27" s="4">
-        <f t="shared" si="38"/>
-        <v>9115.6470808117247</v>
+        <f t="shared" si="35"/>
+        <v>10764.120203338385</v>
       </c>
       <c r="BX27" s="4">
-        <f t="shared" si="38"/>
-        <v>9024.4906100036078</v>
+        <f t="shared" si="35"/>
+        <v>10656.479001305001</v>
       </c>
       <c r="BY27" s="4">
-        <f t="shared" si="38"/>
-        <v>8934.2457039035708</v>
+        <f t="shared" si="35"/>
+        <v>10549.914211291951</v>
       </c>
       <c r="BZ27" s="4">
-        <f t="shared" si="38"/>
-        <v>8844.9032468645346</v>
+        <f t="shared" si="35"/>
+        <v>10444.415069179031</v>
       </c>
       <c r="CA27" s="4">
-        <f t="shared" si="38"/>
-        <v>8756.4542143958897</v>
+        <f t="shared" si="35"/>
+        <v>10339.970918487241</v>
       </c>
       <c r="CB27" s="4">
-        <f t="shared" si="38"/>
-        <v>8668.8896722519312</v>
+        <f t="shared" si="35"/>
+        <v>10236.571209302369</v>
       </c>
       <c r="CC27" s="4">
-        <f t="shared" si="38"/>
-        <v>8582.2007755294126</v>
+        <f t="shared" si="35"/>
+        <v>10134.205497209345</v>
       </c>
       <c r="CD27" s="4">
-        <f t="shared" si="38"/>
-        <v>8496.3787677741184</v>
+        <f t="shared" si="35"/>
+        <v>10032.863442237251</v>
       </c>
       <c r="CE27" s="4">
-        <f t="shared" si="38"/>
-        <v>8411.4149800963769</v>
+        <f t="shared" si="35"/>
+        <v>9932.5348078148781</v>
       </c>
       <c r="CF27" s="4">
-        <f t="shared" si="38"/>
-        <v>8327.3008302954131</v>
+        <f t="shared" si="35"/>
+        <v>9833.2094597367286</v>
       </c>
       <c r="CG27" s="4">
-        <f t="shared" si="38"/>
-        <v>8244.0278219924585</v>
+        <f t="shared" si="35"/>
+        <v>9734.8773651393603</v>
       </c>
       <c r="CH27" s="4">
-        <f t="shared" si="38"/>
-        <v>8161.5875437725335</v>
+        <f t="shared" si="35"/>
+        <v>9637.528591487966</v>
       </c>
       <c r="CI27" s="4">
-        <f t="shared" si="38"/>
-        <v>8079.9716683348079</v>
+        <f t="shared" si="35"/>
+        <v>9541.153305573087</v>
       </c>
       <c r="CJ27" s="4">
-        <f t="shared" si="38"/>
-        <v>7999.1719516514595</v>
+        <f t="shared" si="35"/>
+        <v>9445.7417725173564</v>
       </c>
       <c r="CK27" s="4">
-        <f t="shared" si="38"/>
-        <v>7919.1802321349451</v>
+        <f t="shared" si="35"/>
+        <v>9351.2843547921821</v>
       </c>
       <c r="CL27" s="4">
-        <f t="shared" si="38"/>
-        <v>7839.9884298135958</v>
+        <f t="shared" si="35"/>
+        <v>9257.7715112442602</v>
       </c>
       <c r="CM27" s="4">
-        <f t="shared" si="38"/>
-        <v>7761.5885455154594</v>
+        <f t="shared" si="35"/>
+        <v>9165.1937961318181</v>
       </c>
       <c r="CN27" s="4">
-        <f t="shared" si="38"/>
-        <v>7683.9726600603044</v>
+        <f t="shared" si="35"/>
+        <v>9073.5418581704998</v>
       </c>
       <c r="CO27" s="4">
-        <f t="shared" si="38"/>
-        <v>7607.1329334597012</v>
+        <f t="shared" si="35"/>
+        <v>8982.8064395887941</v>
       </c>
       <c r="CP27" s="4">
-        <f t="shared" si="38"/>
-        <v>7531.0616041251042</v>
+        <f t="shared" si="35"/>
+        <v>8892.9783751929062</v>
       </c>
       <c r="CQ27" s="4">
-        <f t="shared" si="38"/>
-        <v>7455.7509880838534</v>
+        <f t="shared" si="35"/>
+        <v>8804.0485914409765</v>
       </c>
       <c r="CR27" s="4">
-        <f t="shared" si="38"/>
-        <v>7381.1934782030148</v>
+        <f t="shared" si="35"/>
+        <v>8716.0081055265673</v>
       </c>
       <c r="CS27" s="4">
-        <f t="shared" si="38"/>
-        <v>7307.3815434209846</v>
+        <f t="shared" si="35"/>
+        <v>8628.848024471301</v>
       </c>
       <c r="CT27" s="4">
-        <f t="shared" si="38"/>
-        <v>7234.3077279867748</v>
+        <f t="shared" si="35"/>
+        <v>8542.5595442265876</v>
       </c>
       <c r="CU27" s="4">
-        <f t="shared" si="38"/>
-        <v>7161.9646507069074</v>
+        <f t="shared" si="35"/>
+        <v>8457.1339487843215</v>
       </c>
       <c r="CV27" s="4">
-        <f t="shared" si="38"/>
-        <v>7090.3450041998385</v>
+        <f t="shared" si="35"/>
+        <v>8372.5626092964776</v>
       </c>
       <c r="CW27" s="4">
-        <f t="shared" si="38"/>
-        <v>7019.4415541578401</v>
+        <f t="shared" si="35"/>
+        <v>8288.8369832035132</v>
       </c>
       <c r="CX27" s="4">
-        <f t="shared" ref="CX27:EW27" si="39">CW27*(1+$AN$39)</f>
-        <v>6949.2471386162615</v>
+        <f t="shared" ref="CX27:EW27" si="36">CW27*(1+$AN$39)</f>
+        <v>8205.9486133714781</v>
       </c>
       <c r="CY27" s="4">
-        <f t="shared" si="39"/>
-        <v>6879.7546672300987</v>
+        <f t="shared" si="36"/>
+        <v>8123.8891272377632</v>
       </c>
       <c r="CZ27" s="4">
-        <f t="shared" si="39"/>
-        <v>6810.9571205577977</v>
+        <f t="shared" si="36"/>
+        <v>8042.6502359653859</v>
       </c>
       <c r="DA27" s="4">
-        <f t="shared" si="39"/>
-        <v>6742.8475493522201</v>
+        <f t="shared" si="36"/>
+        <v>7962.2237336057324</v>
       </c>
       <c r="DB27" s="4">
-        <f t="shared" si="39"/>
-        <v>6675.4190738586976</v>
+        <f t="shared" si="36"/>
+        <v>7882.6014962696754</v>
       </c>
       <c r="DC27" s="4">
-        <f t="shared" si="39"/>
-        <v>6608.664883120111</v>
+        <f t="shared" si="36"/>
+        <v>7803.7754813069787</v>
       </c>
       <c r="DD27" s="4">
-        <f t="shared" si="39"/>
-        <v>6542.5782342889097</v>
+        <f t="shared" si="36"/>
+        <v>7725.7377264939087</v>
       </c>
       <c r="DE27" s="4">
-        <f t="shared" si="39"/>
-        <v>6477.1524519460208</v>
+        <f t="shared" si="36"/>
+        <v>7648.4803492289693</v>
       </c>
       <c r="DF27" s="4">
-        <f t="shared" si="39"/>
-        <v>6412.3809274265604</v>
+        <f t="shared" si="36"/>
+        <v>7571.9955457366796</v>
       </c>
       <c r="DG27" s="4">
-        <f t="shared" si="39"/>
-        <v>6348.2571181522944</v>
+        <f t="shared" si="36"/>
+        <v>7496.2755902793124</v>
       </c>
       <c r="DH27" s="4">
-        <f t="shared" si="39"/>
-        <v>6284.7745469707716</v>
+        <f t="shared" si="36"/>
+        <v>7421.3128343765193</v>
       </c>
       <c r="DI27" s="4">
-        <f t="shared" si="39"/>
-        <v>6221.9268015010639</v>
+        <f t="shared" si="36"/>
+        <v>7347.0997060327536</v>
       </c>
       <c r="DJ27" s="4">
-        <f t="shared" si="39"/>
-        <v>6159.7075334860529</v>
+        <f t="shared" si="36"/>
+        <v>7273.6287089724256</v>
       </c>
       <c r="DK27" s="4">
-        <f t="shared" si="39"/>
-        <v>6098.1104581511927</v>
+        <f t="shared" si="36"/>
+        <v>7200.8924218827015</v>
       </c>
       <c r="DL27" s="4">
-        <f t="shared" si="39"/>
-        <v>6037.1293535696805</v>
+        <f t="shared" si="36"/>
+        <v>7128.8834976638746</v>
       </c>
       <c r="DM27" s="4">
-        <f t="shared" si="39"/>
-        <v>5976.7580600339834</v>
+        <f t="shared" si="36"/>
+        <v>7057.5946626872355</v>
       </c>
       <c r="DN27" s="4">
-        <f t="shared" si="39"/>
-        <v>5916.9904794336435</v>
+        <f t="shared" si="36"/>
+        <v>6987.0187160603627</v>
       </c>
       <c r="DO27" s="4">
-        <f t="shared" si="39"/>
-        <v>5857.8205746393069</v>
+        <f t="shared" si="36"/>
+        <v>6917.1485288997592</v>
       </c>
       <c r="DP27" s="4">
-        <f t="shared" si="39"/>
-        <v>5799.2423688929139</v>
+        <f t="shared" si="36"/>
+        <v>6847.9770436107619</v>
       </c>
       <c r="DQ27" s="4">
-        <f t="shared" si="39"/>
-        <v>5741.2499452039847</v>
+        <f t="shared" si="36"/>
+        <v>6779.4972731746539</v>
       </c>
       <c r="DR27" s="4">
-        <f t="shared" si="39"/>
-        <v>5683.8374457519449</v>
+        <f t="shared" si="36"/>
+        <v>6711.7023004429075</v>
       </c>
       <c r="DS27" s="4">
-        <f t="shared" si="39"/>
-        <v>5626.9990712944254</v>
+        <f t="shared" si="36"/>
+        <v>6644.5852774384784</v>
       </c>
       <c r="DT27" s="4">
-        <f t="shared" si="39"/>
-        <v>5570.729080581481</v>
+        <f t="shared" si="36"/>
+        <v>6578.1394246640939</v>
       </c>
       <c r="DU27" s="4">
-        <f t="shared" si="39"/>
-        <v>5515.0217897756665</v>
+        <f t="shared" si="36"/>
+        <v>6512.3580304174529</v>
       </c>
       <c r="DV27" s="4">
-        <f t="shared" si="39"/>
-        <v>5459.8715718779094</v>
+        <f t="shared" si="36"/>
+        <v>6447.2344501132784</v>
       </c>
       <c r="DW27" s="4">
-        <f t="shared" si="39"/>
-        <v>5405.2728561591302</v>
+        <f t="shared" si="36"/>
+        <v>6382.7621056121452</v>
       </c>
       <c r="DX27" s="4">
-        <f t="shared" si="39"/>
-        <v>5351.2201275975385</v>
+        <f t="shared" si="36"/>
+        <v>6318.9344845560236</v>
       </c>
       <c r="DY27" s="4">
-        <f t="shared" si="39"/>
-        <v>5297.7079263215628</v>
+        <f t="shared" si="36"/>
+        <v>6255.7451397104633</v>
       </c>
       <c r="DZ27" s="4">
-        <f t="shared" si="39"/>
-        <v>5244.7308470583475</v>
+        <f t="shared" si="36"/>
+        <v>6193.1876883133582</v>
       </c>
       <c r="EA27" s="4">
-        <f t="shared" si="39"/>
-        <v>5192.2835385877643</v>
+        <f t="shared" si="36"/>
+        <v>6131.2558114302246</v>
       </c>
       <c r="EB27" s="4">
-        <f t="shared" si="39"/>
-        <v>5140.3607032018863</v>
+        <f t="shared" si="36"/>
+        <v>6069.9432533159224</v>
       </c>
       <c r="EC27" s="4">
-        <f t="shared" si="39"/>
-        <v>5088.9570961698673</v>
+        <f t="shared" si="36"/>
+        <v>6009.2438207827636</v>
       </c>
       <c r="ED27" s="4">
-        <f t="shared" si="39"/>
-        <v>5038.0675252081683</v>
+        <f t="shared" si="36"/>
+        <v>5949.1513825749362</v>
       </c>
       <c r="EE27" s="4">
-        <f t="shared" si="39"/>
-        <v>4987.6868499560869</v>
+        <f t="shared" si="36"/>
+        <v>5889.6598687491869</v>
       </c>
       <c r="EF27" s="4">
-        <f t="shared" si="39"/>
-        <v>4937.8099814565257</v>
+        <f t="shared" si="36"/>
+        <v>5830.763270061695</v>
       </c>
       <c r="EG27" s="4">
-        <f t="shared" si="39"/>
-        <v>4888.4318816419609</v>
+        <f t="shared" si="36"/>
+        <v>5772.4556373610776</v>
       </c>
       <c r="EH27" s="4">
-        <f t="shared" si="39"/>
-        <v>4839.5475628255408</v>
+        <f t="shared" si="36"/>
+        <v>5714.7310809874671</v>
       </c>
       <c r="EI27" s="4">
-        <f t="shared" si="39"/>
-        <v>4791.1520871972853</v>
+        <f t="shared" si="36"/>
+        <v>5657.5837701775927</v>
       </c>
       <c r="EJ27" s="4">
-        <f t="shared" si="39"/>
-        <v>4743.2405663253121</v>
+        <f t="shared" si="36"/>
+        <v>5601.0079324758171</v>
       </c>
       <c r="EK27" s="4">
-        <f t="shared" si="39"/>
-        <v>4695.808160662059</v>
+        <f t="shared" si="36"/>
+        <v>5544.9978531510587</v>
       </c>
       <c r="EL27" s="4">
-        <f t="shared" si="39"/>
-        <v>4648.8500790554381</v>
+        <f t="shared" si="36"/>
+        <v>5489.5478746195477</v>
       </c>
       <c r="EM27" s="4">
-        <f t="shared" si="39"/>
-        <v>4602.361578264884</v>
+        <f t="shared" si="36"/>
+        <v>5434.6523958733524</v>
       </c>
       <c r="EN27" s="4">
-        <f t="shared" si="39"/>
-        <v>4556.3379624822355</v>
+        <f t="shared" si="36"/>
+        <v>5380.3058719146184</v>
       </c>
       <c r="EO27" s="4">
-        <f t="shared" si="39"/>
-        <v>4510.7745828574134</v>
+        <f t="shared" si="36"/>
+        <v>5326.5028131954723</v>
       </c>
       <c r="EP27" s="4">
-        <f t="shared" si="39"/>
-        <v>4465.6668370288389</v>
+        <f t="shared" si="36"/>
+        <v>5273.2377850635175</v>
       </c>
       <c r="EQ27" s="4">
-        <f t="shared" si="39"/>
-        <v>4421.0101686585504</v>
+        <f t="shared" si="36"/>
+        <v>5220.5054072128823</v>
       </c>
       <c r="ER27" s="4">
-        <f t="shared" si="39"/>
-        <v>4376.800066971965</v>
+        <f t="shared" si="36"/>
+        <v>5168.300353140753</v>
       </c>
       <c r="ES27" s="4">
-        <f t="shared" si="39"/>
-        <v>4333.0320663022449</v>
+        <f t="shared" si="36"/>
+        <v>5116.6173496093452</v>
       </c>
       <c r="ET27" s="4">
-        <f t="shared" si="39"/>
-        <v>4289.7017456392223</v>
+        <f t="shared" si="36"/>
+        <v>5065.4511761132517</v>
       </c>
       <c r="EU27" s="4">
-        <f t="shared" si="39"/>
-        <v>4246.8047281828303</v>
+        <f t="shared" si="36"/>
+        <v>5014.7966643521195</v>
       </c>
       <c r="EV27" s="4">
-        <f t="shared" si="39"/>
-        <v>4204.3366809010022</v>
+        <f t="shared" si="36"/>
+        <v>4964.6486977085979</v>
       </c>
       <c r="EW27" s="4">
-        <f t="shared" si="39"/>
-        <v>4162.2933140919922</v>
+        <f t="shared" si="36"/>
+        <v>4915.0022107315117</v>
       </c>
     </row>
     <row r="28" spans="2:153" x14ac:dyDescent="0.3">
@@ -4136,12 +4139,12 @@
         <v>695.9</v>
       </c>
       <c r="Q28" s="3">
-        <f>695.9</f>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="R28" s="3">
-        <f>695.9</f>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="V28" s="3">
         <v>710.9</v>
@@ -4153,52 +4156,52 @@
         <v>710.9</v>
       </c>
       <c r="Y28" s="3">
-        <f t="shared" ref="Y28" si="40">702.5</f>
+        <f t="shared" ref="Y28" si="37">702.5</f>
         <v>702.5</v>
       </c>
       <c r="Z28" s="3">
-        <f t="shared" ref="Z28:AJ28" si="41">695.9</f>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AA28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AB28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AC28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AD28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AE28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AF28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AG28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AH28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AI28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
       <c r="AJ28" s="3">
-        <f t="shared" si="41"/>
-        <v>695.9</v>
+        <f>688.9</f>
+        <v>688.9</v>
       </c>
     </row>
     <row r="29" spans="2:153" x14ac:dyDescent="0.3">
@@ -4206,68 +4209,68 @@
         <v>35</v>
       </c>
       <c r="C29" s="6">
-        <f t="shared" ref="C29:L29" si="42">C27/C28</f>
+        <f t="shared" ref="C29:L29" si="38">C27/C28</f>
         <v>2.9525953017302013</v>
       </c>
       <c r="D29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>2.762695175130117</v>
       </c>
       <c r="E29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>2.643128428752286</v>
       </c>
       <c r="F29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>2.2112814741876496</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>2.5545083696722464</v>
       </c>
       <c r="H29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>3.0580953720635815</v>
       </c>
       <c r="I29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>3.4477422984948656</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>2.7190884793923198</v>
       </c>
       <c r="K29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>3.4280489520326349</v>
       </c>
       <c r="L29" s="6">
-        <f t="shared" si="42"/>
+        <f t="shared" si="38"/>
         <v>4.2411028274018854</v>
       </c>
       <c r="M29" s="6">
-        <f t="shared" ref="M29:N29" si="43">M27/M28</f>
+        <f t="shared" ref="M29:N29" si="39">M27/M28</f>
         <v>3.5590573537762635</v>
       </c>
       <c r="N29" s="6">
-        <f t="shared" si="43"/>
+        <f t="shared" si="39"/>
         <v>3.0889679715302489</v>
       </c>
       <c r="O29" s="6">
-        <f t="shared" ref="O29:R29" si="44">O27/O28</f>
+        <f t="shared" ref="O29:R29" si="40">O27/O28</f>
         <v>3.6882671995432483</v>
       </c>
       <c r="P29" s="6">
-        <f t="shared" si="44"/>
+        <f t="shared" si="40"/>
         <v>4.1457105906020981</v>
       </c>
       <c r="Q29" s="6">
-        <f t="shared" si="44"/>
-        <v>4.0480928208075859</v>
+        <f t="shared" si="40"/>
+        <v>4.2125127014080421</v>
       </c>
       <c r="R29" s="6">
-        <f t="shared" si="44"/>
-        <v>3.2356567753987631</v>
+        <f t="shared" si="40"/>
+        <v>3.4187711569168218</v>
       </c>
       <c r="V29" s="6">
         <f>V27/V28</f>
@@ -4287,47 +4290,47 @@
       </c>
       <c r="Z29" s="6">
         <f>Z27/Z28</f>
-        <v>15.142637367437853</v>
+        <v>15.570026781826098</v>
       </c>
       <c r="AA29" s="6">
-        <f t="shared" ref="AA29:AJ29" si="45">AA27/AA28</f>
-        <v>16.902012353499067</v>
+        <f t="shared" ref="AA29:AJ29" si="41">AA27/AA28</f>
+        <v>18.009286261576431</v>
       </c>
       <c r="AB29" s="6">
-        <f t="shared" si="45"/>
-        <v>17.277848753085216</v>
+        <f t="shared" si="41"/>
+        <v>18.950407004476709</v>
       </c>
       <c r="AC29" s="6">
-        <f t="shared" si="45"/>
-        <v>17.612357242750864</v>
+        <f t="shared" si="41"/>
+        <v>19.718035202301536</v>
       </c>
       <c r="AD29" s="6">
-        <f t="shared" si="45"/>
-        <v>17.935412825292062</v>
+        <f t="shared" si="41"/>
+        <v>20.07108044959428</v>
       </c>
       <c r="AE29" s="6">
-        <f t="shared" si="45"/>
-        <v>18.224893230599641</v>
+        <f t="shared" si="41"/>
+        <v>20.437900856389643</v>
       </c>
       <c r="AF29" s="6">
-        <f t="shared" si="45"/>
-        <v>18.450585196209214</v>
+        <f t="shared" si="41"/>
+        <v>20.935931168116994</v>
       </c>
       <c r="AG29" s="6">
-        <f t="shared" si="45"/>
-        <v>18.679402942140964</v>
+        <f t="shared" si="41"/>
+        <v>21.452634524412304</v>
       </c>
       <c r="AH29" s="6">
-        <f t="shared" si="45"/>
-        <v>18.911395103411422</v>
+        <f t="shared" si="41"/>
+        <v>21.988842699845478</v>
       </c>
       <c r="AI29" s="6">
-        <f t="shared" si="45"/>
-        <v>19.146611148931566</v>
+        <f t="shared" si="41"/>
+        <v>22.545426455220397</v>
       </c>
       <c r="AJ29" s="6">
-        <f t="shared" si="45"/>
-        <v>19.385101396796625</v>
+        <f t="shared" si="41"/>
+        <v>23.123297397512982</v>
       </c>
     </row>
     <row r="31" spans="2:153" x14ac:dyDescent="0.3">
@@ -4335,107 +4338,107 @@
         <v>67</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" ref="G31:K31" si="46">G3/C3-1</f>
+        <f t="shared" ref="G31:K31" si="42">G3/C3-1</f>
         <v>0.16269202633504021</v>
       </c>
       <c r="H31" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>7.7225962149117144E-2</v>
       </c>
       <c r="I31" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>7.1355759429153842E-2</v>
       </c>
       <c r="J31" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>4.8515214469021073E-2</v>
       </c>
       <c r="K31" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="42"/>
         <v>5.4485969548257129E-2</v>
       </c>
       <c r="L31" s="7">
-        <f t="shared" ref="L31:R31" si="47">L3/H3-1</f>
+        <f t="shared" ref="L31:R31" si="43">L3/H3-1</f>
         <v>4.4098573281452724E-2</v>
       </c>
       <c r="M31" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>4.4243577545195034E-2</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>6.9580419580419495E-2</v>
       </c>
       <c r="O31" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>4.3317422434367536E-2</v>
       </c>
       <c r="P31" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="Q31" s="7">
-        <f t="shared" si="47"/>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" si="43"/>
+        <v>7.2095671981776688E-2</v>
       </c>
       <c r="R31" s="7">
-        <f t="shared" si="47"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="43"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="W31" s="7">
         <f>W3/V3-1</f>
         <v>0.76518892844837483</v>
       </c>
       <c r="X31" s="7">
-        <f t="shared" ref="X31:AJ31" si="48">X3/W3-1</f>
+        <f t="shared" ref="X31:AJ31" si="44">X3/W3-1</f>
         <v>8.7088064022902589E-2</v>
       </c>
       <c r="Y31" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>5.3148192482643131E-2</v>
       </c>
       <c r="Z31" s="7">
-        <f t="shared" si="48"/>
-        <v>5.0093203000682207E-2</v>
+        <f t="shared" si="44"/>
+        <v>5.5718629233916683E-2</v>
       </c>
       <c r="AA31" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB31" s="7">
+        <f t="shared" si="44"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC31" s="7">
+        <f t="shared" si="44"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AB31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AD31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AC31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AE31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AF31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AG31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AH31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG31" s="7">
-        <f t="shared" si="48"/>
+      <c r="AI31" s="7">
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH31" s="7">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AI31" s="7">
-        <f t="shared" si="48"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AJ31" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4444,31 +4447,31 @@
         <v>68</v>
       </c>
       <c r="G32" s="7">
-        <f t="shared" ref="G32:M32" si="49">G4/C4-1</f>
+        <f t="shared" ref="G32:M32" si="45">G4/C4-1</f>
         <v>0.2037947997189038</v>
       </c>
       <c r="H32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.20796758946657667</v>
       </c>
       <c r="I32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.19792342634652815</v>
       </c>
       <c r="J32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.17353846153846164</v>
       </c>
       <c r="K32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.15236427320490376</v>
       </c>
       <c r="L32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.1514812744550027</v>
       </c>
       <c r="M32" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="45"/>
         <v>0.17551462621885161</v>
       </c>
       <c r="N32" s="7">
@@ -4485,7 +4488,7 @@
       </c>
       <c r="Q32" s="7">
         <f>Q4/M4-1</f>
-        <v>0.16999999999999993</v>
+        <v>0.17557603686635948</v>
       </c>
       <c r="R32" s="7">
         <f>R4/N4-1</f>
@@ -4496,56 +4499,56 @@
         <v>0.57621397039729949</v>
       </c>
       <c r="X32" s="7">
-        <f t="shared" ref="X32:AJ32" si="50">X4/W4-1</f>
+        <f t="shared" ref="X32:AJ32" si="46">X4/W4-1</f>
         <v>0.19522240527182877</v>
       </c>
       <c r="Y32" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0.16457615437629225</v>
       </c>
       <c r="Z32" s="7">
-        <f t="shared" si="50"/>
-        <v>0.17571902000236705</v>
+        <f t="shared" si="46"/>
+        <v>0.17715114214699956</v>
       </c>
       <c r="AA32" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
+        <v>0.12999999999999989</v>
+      </c>
+      <c r="AB32" s="7">
+        <f t="shared" si="46"/>
         <v>9.000000000000008E-2</v>
       </c>
-      <c r="AB32" s="7">
-        <f t="shared" si="50"/>
+      <c r="AC32" s="7">
+        <f t="shared" si="46"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AC32" s="7">
-        <f t="shared" si="50"/>
+      <c r="AD32" s="7">
+        <f t="shared" si="46"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AD32" s="7">
-        <f t="shared" si="50"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="AE32" s="7">
-        <f t="shared" si="50"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF32" s="7">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG32" s="7">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH32" s="7">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI32" s="7">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ32" s="7">
-        <f t="shared" si="50"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="46"/>
+        <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="33" spans="2:40" x14ac:dyDescent="0.3">
@@ -4553,31 +4556,31 @@
         <v>69</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" ref="G33:M33" si="51">G5/C5-1</f>
+        <f t="shared" ref="G33:M33" si="47">G5/C5-1</f>
         <v>0.3443708609271523</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>-2.6086956521739091E-2</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>7.8699743370401976E-2</v>
       </c>
       <c r="J33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>9.5681625740897447E-2</v>
       </c>
       <c r="K33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>6.075533661740562E-2</v>
       </c>
       <c r="L33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>3.8961038961038863E-2</v>
       </c>
       <c r="M33" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="47"/>
         <v>4.7581284694686587E-3</v>
       </c>
       <c r="N33" s="7">
@@ -4593,12 +4596,12 @@
         <v>8.293838862559233E-2</v>
       </c>
       <c r="Q33" s="7">
-        <f t="shared" ref="Q33:R34" si="52">Q5/M5-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f>Q7/M7-1</f>
+        <v>0.17619047619047623</v>
       </c>
       <c r="R33" s="7">
-        <f t="shared" si="52"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="Q33:R34" si="48">R5/N5-1</f>
+        <v>0.22999999999999998</v>
       </c>
       <c r="W33" s="7">
         <f>W5/V5-1</f>
@@ -4614,47 +4617,47 @@
       </c>
       <c r="Z33" s="7">
         <f>Z7/Y7-1</f>
-        <v>4.5399852180340039E-2</v>
+        <v>0.12432372505543232</v>
       </c>
       <c r="AA33" s="7">
-        <f t="shared" ref="AA33:AJ33" si="53">AA7/Z7-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AA33:AJ33" si="49">AA7/Z7-1</f>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AB33" s="7">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="49"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AC33" s="7">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="49"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD33" s="7">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE33" s="7">
-        <f t="shared" si="53"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF33" s="7">
-        <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG33" s="7">
-        <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AH33" s="7">
-        <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI33" s="7">
-        <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AJ33" s="7">
-        <f t="shared" si="53"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="49"/>
+        <v>4.0000000000000036E-2</v>
       </c>
     </row>
     <row r="34" spans="2:40" x14ac:dyDescent="0.3">
@@ -4662,31 +4665,31 @@
         <v>70</v>
       </c>
       <c r="G34" s="7">
-        <f t="shared" ref="G34:M34" si="54">G6/C6-1</f>
+        <f t="shared" ref="G34:M34" si="50">G6/C6-1</f>
         <v>0.12903225806451624</v>
       </c>
       <c r="H34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>7.4519230769230838E-2</v>
       </c>
       <c r="I34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>9.52380952380949E-3</v>
       </c>
       <c r="J34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-3.4965034965035002E-2</v>
       </c>
       <c r="K34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-8.0952380952380998E-2</v>
       </c>
       <c r="L34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-8.7248322147650992E-2</v>
       </c>
       <c r="M34" s="7">
-        <f t="shared" si="54"/>
+        <f t="shared" si="50"/>
         <v>-2.5943396226415061E-2</v>
       </c>
       <c r="N34" s="7">
@@ -4695,13 +4698,10 @@
       </c>
       <c r="O34" s="7"/>
       <c r="P34" s="7"/>
-      <c r="Q34" s="7">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
+      <c r="Q34" s="7"/>
       <c r="R34" s="7">
-        <f t="shared" si="52"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="48"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="W34" s="7">
         <f>W6/V6-1</f>
@@ -4732,107 +4732,107 @@
         <v>65</v>
       </c>
       <c r="G35" s="7">
-        <f t="shared" ref="G35:K37" si="55">G9/C9-1</f>
+        <f t="shared" ref="G35:K37" si="51">G9/C9-1</f>
         <v>0.75238095238095237</v>
       </c>
       <c r="H35" s="7">
-        <f t="shared" ref="H35:H36" si="56">H9/D9-1</f>
+        <f t="shared" ref="H35:H36" si="52">H9/D9-1</f>
         <v>0.70596641657734915</v>
       </c>
       <c r="I35" s="7">
-        <f t="shared" ref="I35:I36" si="57">I9/E9-1</f>
+        <f t="shared" ref="I35:I36" si="53">I9/E9-1</f>
         <v>0.55305275637225848</v>
       </c>
       <c r="J35" s="7">
-        <f t="shared" ref="J35:J36" si="58">J9/F9-1</f>
+        <f t="shared" ref="J35:J36" si="54">J9/F9-1</f>
         <v>0.40025220680958395</v>
       </c>
       <c r="K35" s="7">
-        <f t="shared" ref="K35:K36" si="59">K9/G9-1</f>
+        <f t="shared" ref="K35:K36" si="55">K9/G9-1</f>
         <v>0.30774456521739135</v>
       </c>
       <c r="L35" s="7">
-        <f t="shared" ref="L35:L36" si="60">L9/H9-1</f>
+        <f t="shared" ref="L35:L36" si="56">L9/H9-1</f>
         <v>0.21340314136125649</v>
       </c>
       <c r="M35" s="7">
-        <f t="shared" ref="M35:M36" si="61">M9/I9-1</f>
+        <f t="shared" ref="M35:M36" si="57">M9/I9-1</f>
         <v>0.17347328244274807</v>
       </c>
       <c r="N35" s="7">
-        <f t="shared" ref="N35:N36" si="62">N9/J9-1</f>
+        <f t="shared" ref="N35:N36" si="58">N9/J9-1</f>
         <v>9.4560518731988452E-2</v>
       </c>
       <c r="O35" s="7">
-        <f t="shared" ref="O35:O37" si="63">O9/K9-1</f>
+        <f t="shared" ref="O35:O37" si="59">O9/K9-1</f>
         <v>6.2337662337662358E-2</v>
       </c>
       <c r="P35" s="7">
-        <f t="shared" ref="P35:P37" si="64">P9/L9-1</f>
+        <f t="shared" ref="P35:P37" si="60">P9/L9-1</f>
         <v>8.1118398343113629E-2</v>
       </c>
       <c r="Q35" s="7">
-        <f t="shared" ref="Q35:Q37" si="65">Q9/M9-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="Q35:Q37" si="61">Q9/M9-1</f>
+        <v>7.6109936575052828E-2</v>
       </c>
       <c r="R35" s="7">
-        <f t="shared" ref="R35:R37" si="66">R9/N9-1</f>
+        <f t="shared" ref="R35:R37" si="62">R9/N9-1</f>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="W35" s="7">
+        <f t="shared" ref="W35:AJ35" si="63">W9/V9-1</f>
+        <v>0.90833710236695309</v>
+      </c>
+      <c r="X35" s="7">
+        <f t="shared" si="63"/>
+        <v>0.57868541633749415</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="63"/>
+        <v>0.19076214782565182</v>
+      </c>
+      <c r="Z35" s="7">
+        <f t="shared" si="63"/>
+        <v>7.753435595713376E-2</v>
+      </c>
+      <c r="AA35" s="7">
+        <f t="shared" si="63"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AB35" s="7">
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="W35" s="7">
-        <f t="shared" ref="W35:AJ35" si="67">W9/V9-1</f>
-        <v>0.90833710236695309</v>
-      </c>
-      <c r="X35" s="7">
-        <f t="shared" si="67"/>
-        <v>0.57868541633749415</v>
-      </c>
-      <c r="Y35" s="7">
-        <f t="shared" si="67"/>
-        <v>0.19076214782565182</v>
-      </c>
-      <c r="Z35" s="7">
-        <f t="shared" si="67"/>
-        <v>5.0265181760874134E-2</v>
-      </c>
-      <c r="AA35" s="7">
-        <f t="shared" si="67"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AB35" s="7">
-        <f t="shared" si="67"/>
+      <c r="AC35" s="7">
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AC35" s="7">
-        <f t="shared" si="67"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AD35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ35" s="7">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4841,107 +4841,107 @@
         <v>71</v>
       </c>
       <c r="G36" s="7">
+        <f t="shared" si="51"/>
+        <v>3.4641744548286608</v>
+      </c>
+      <c r="H36" s="7">
+        <f t="shared" si="52"/>
+        <v>2.8041002277904328</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="53"/>
+        <v>1.2587939698492461</v>
+      </c>
+      <c r="J36" s="7">
+        <f t="shared" si="54"/>
+        <v>0.61391880695940348</v>
+      </c>
+      <c r="K36" s="7">
         <f t="shared" si="55"/>
-        <v>3.4641744548286608</v>
-      </c>
-      <c r="H36" s="7">
+        <v>0.39986043265875781</v>
+      </c>
+      <c r="L36" s="7">
         <f t="shared" si="56"/>
-        <v>2.8041002277904328</v>
-      </c>
-      <c r="I36" s="7">
+        <v>0.23592814371257487</v>
+      </c>
+      <c r="M36" s="7">
         <f t="shared" si="57"/>
-        <v>1.2587939698492461</v>
-      </c>
-      <c r="J36" s="7">
+        <v>0.19187986651835365</v>
+      </c>
+      <c r="N36" s="7">
         <f t="shared" si="58"/>
-        <v>0.61391880695940348</v>
-      </c>
-      <c r="K36" s="7">
+        <v>4.6714579055441519E-2</v>
+      </c>
+      <c r="O36" s="7">
         <f t="shared" si="59"/>
-        <v>0.39986043265875781</v>
-      </c>
-      <c r="L36" s="7">
+        <v>-1.9940179461615193E-2</v>
+      </c>
+      <c r="P36" s="7">
         <f t="shared" si="60"/>
-        <v>0.23592814371257487</v>
-      </c>
-      <c r="M36" s="7">
+        <v>6.2984496124030009E-3</v>
+      </c>
+      <c r="Q36" s="7">
         <f t="shared" si="61"/>
-        <v>0.19187986651835365</v>
-      </c>
-      <c r="N36" s="7">
+        <v>-5.5996266915538939E-3</v>
+      </c>
+      <c r="R36" s="7">
         <f t="shared" si="62"/>
-        <v>4.6714579055441519E-2</v>
-      </c>
-      <c r="O36" s="7">
-        <f t="shared" si="63"/>
-        <v>-1.9940179461615193E-2</v>
-      </c>
-      <c r="P36" s="7">
+        <v>-1.0000000000000009E-2</v>
+      </c>
+      <c r="W36" s="7">
+        <f t="shared" ref="W36:AJ36" si="64">W10/V10-1</f>
+        <v>1.7880928355196772</v>
+      </c>
+      <c r="X36" s="7">
         <f t="shared" si="64"/>
-        <v>6.2984496124030009E-3</v>
-      </c>
-      <c r="Q36" s="7">
-        <f t="shared" si="65"/>
-        <v>-2.0000000000000018E-2</v>
-      </c>
-      <c r="R36" s="7">
-        <f t="shared" si="66"/>
-        <v>-1.0000000000000009E-2</v>
-      </c>
-      <c r="W36" s="7">
-        <f t="shared" ref="W36:AJ36" si="68">W10/V10-1</f>
-        <v>1.7880928355196772</v>
-      </c>
-      <c r="X36" s="7">
-        <f t="shared" si="68"/>
         <v>1.4788273615635181</v>
       </c>
       <c r="Y36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>0.20484742298145719</v>
       </c>
       <c r="Z36" s="7">
-        <f t="shared" si="68"/>
-        <v>-1.0936742607852712E-2</v>
+        <f t="shared" si="64"/>
+        <v>-7.1970431410566249E-3</v>
       </c>
       <c r="AA36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ36" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4950,23 +4950,23 @@
         <v>66</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.35652569349704422</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.31567796610169485</v>
       </c>
       <c r="I37" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.33514352211016285</v>
       </c>
       <c r="J37" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.30674401740391599</v>
       </c>
       <c r="K37" s="7">
-        <f t="shared" si="55"/>
+        <f t="shared" si="51"/>
         <v>0.26349312772376798</v>
       </c>
       <c r="L37" s="7">
@@ -4978,31 +4978,31 @@
         <v>0.16385822196397437</v>
       </c>
       <c r="N37" s="7">
-        <f t="shared" ref="N37" si="69">N11/J11-1</f>
+        <f t="shared" ref="N37" si="65">N11/J11-1</f>
         <v>0.12042175360710328</v>
       </c>
       <c r="O37" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="59"/>
         <v>0.10612894667020423</v>
       </c>
       <c r="P37" s="7">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>0.12252010723860596</v>
       </c>
       <c r="Q37" s="7">
-        <f t="shared" si="65"/>
-        <v>4.1397903145282022E-2</v>
+        <f t="shared" si="61"/>
+        <v>0.11982026959560654</v>
       </c>
       <c r="R37" s="7">
+        <f t="shared" si="62"/>
+        <v>0.14049529470034683</v>
+      </c>
+      <c r="W37" s="7">
+        <f t="shared" ref="W37:X37" si="66">W11/V11-1</f>
+        <v>0.75381070542360873</v>
+      </c>
+      <c r="X37" s="7">
         <f t="shared" si="66"/>
-        <v>6.5247647350173521E-2</v>
-      </c>
-      <c r="W37" s="7">
-        <f t="shared" ref="W37:X37" si="70">W11/V11-1</f>
-        <v>0.75381070542360873</v>
-      </c>
-      <c r="X37" s="7">
-        <f t="shared" si="70"/>
         <v>0.32733703890853971</v>
       </c>
       <c r="Y37" s="7">
@@ -5010,48 +5010,48 @@
         <v>0.18341708542713575</v>
       </c>
       <c r="Z37" s="7">
-        <f t="shared" ref="Z37:AJ37" si="71">Z11/Y11-1</f>
-        <v>8.2758154796371164E-2</v>
+        <f t="shared" ref="Z37:AJ37" si="67">Z11/Y11-1</f>
+        <v>0.12251946213729648</v>
       </c>
       <c r="AA37" s="7">
-        <f t="shared" si="71"/>
-        <v>3.5150276511633827E-2</v>
+        <f t="shared" si="67"/>
+        <v>6.4695626606263934E-2</v>
       </c>
       <c r="AB37" s="7">
-        <f t="shared" si="71"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="67"/>
+        <v>4.4630814491361193E-2</v>
       </c>
       <c r="AC37" s="7">
-        <f t="shared" si="71"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="67"/>
+        <v>3.4565956565645095E-2</v>
       </c>
       <c r="AD37" s="7">
-        <f t="shared" si="71"/>
+        <f t="shared" si="67"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="AE37" s="7">
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE37" s="7">
-        <f t="shared" si="71"/>
+      <c r="AF37" s="7">
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF37" s="7">
-        <f t="shared" si="71"/>
+      <c r="AG37" s="7">
+        <f t="shared" si="67"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH37" s="7">
+        <f t="shared" si="67"/>
         <v>1.0000000000000231E-2</v>
       </c>
-      <c r="AG37" s="7">
-        <f t="shared" si="71"/>
+      <c r="AI37" s="7">
+        <f t="shared" si="67"/>
         <v>9.9999999999997868E-3</v>
       </c>
-      <c r="AH37" s="7">
-        <f t="shared" si="71"/>
+      <c r="AJ37" s="7">
+        <f t="shared" si="67"/>
         <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AI37" s="7">
-        <f t="shared" si="71"/>
-        <v>1.0000000000000231E-2</v>
-      </c>
-      <c r="AJ37" s="7">
-        <f t="shared" si="71"/>
-        <v>9.9999999999997868E-3</v>
       </c>
     </row>
     <row r="38" spans="2:40" x14ac:dyDescent="0.3">
@@ -5063,23 +5063,23 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7">
-        <f t="shared" ref="G38:K38" si="72">G16/C16-1</f>
+        <f t="shared" ref="G38:K38" si="68">G16/C16-1</f>
         <v>0.30341738553417374</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.20890559491108873</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.19697603121516161</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.15367613599427932</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.13319333078783258</v>
       </c>
       <c r="L38" s="7">
@@ -5087,28 +5087,28 @@
         <v>0.10003587658454904</v>
       </c>
       <c r="M38" s="7">
-        <f t="shared" ref="M38:N38" si="73">M16/I16-1</f>
+        <f t="shared" ref="M38:N38" si="69">M16/I16-1</f>
         <v>9.3136969555853044E-2</v>
       </c>
       <c r="N38" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>8.2887248549050607E-2</v>
       </c>
       <c r="O38" s="7">
-        <f t="shared" ref="O38" si="74">O16/K16-1</f>
+        <f t="shared" ref="O38" si="70">O16/K16-1</f>
         <v>6.3233559836019637E-2</v>
       </c>
       <c r="P38" s="7">
-        <f t="shared" ref="P38" si="75">P16/L16-1</f>
+        <f t="shared" ref="P38" si="71">P16/L16-1</f>
         <v>8.3491873675055617E-2</v>
       </c>
       <c r="Q38" s="7">
-        <f t="shared" ref="Q38" si="76">Q16/M16-1</f>
-        <v>5.7369401991586244E-2</v>
+        <f t="shared" ref="Q38" si="72">Q16/M16-1</f>
+        <v>9.4680227914159421E-2</v>
       </c>
       <c r="R38" s="7">
-        <f t="shared" ref="R38" si="77">R16/N16-1</f>
-        <v>5.2626704131543134E-2</v>
+        <f t="shared" ref="R38" si="73">R16/N16-1</f>
+        <v>8.8645020293474985E-2</v>
       </c>
       <c r="V38" s="7"/>
       <c r="W38" s="7">
@@ -5116,56 +5116,56 @@
         <v>0.78136809069365265</v>
       </c>
       <c r="X38" s="7">
-        <f t="shared" ref="X38:AJ38" si="78">X16/W16-1</f>
+        <f t="shared" ref="X38:AJ38" si="74">X16/W16-1</f>
         <v>0.21103820224719105</v>
       </c>
       <c r="Y38" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="74"/>
         <v>0.10149337925301349</v>
       </c>
       <c r="Z38" s="7">
-        <f t="shared" si="78"/>
-        <v>6.4025013139984654E-2</v>
+        <f t="shared" si="74"/>
+        <v>8.279645826875659E-2</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" si="78"/>
-        <v>3.60338242156093E-2</v>
+        <f t="shared" si="74"/>
+        <v>6.0363509274676597E-2</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" si="78"/>
-        <v>2.5187879461433749E-2</v>
+        <f t="shared" si="74"/>
+        <v>4.3971088047545903E-2</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.9604794841722173E-2</v>
+        <f t="shared" si="74"/>
+        <v>3.2974588174786934E-2</v>
       </c>
       <c r="AD38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.5154712043011331E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.866466174628556E-2</v>
       </c>
       <c r="AE38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.3805806575623025E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.8902160935972967E-2</v>
       </c>
       <c r="AF38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.1480884274490455E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.9144225784846869E-2</v>
       </c>
       <c r="AG38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.1493356902205543E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.9390833973430111E-2</v>
       </c>
       <c r="AH38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.1505916010081219E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.9641956480932476E-2</v>
       </c>
       <c r="AI38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.1518561884780176E-2</v>
+        <f t="shared" si="74"/>
+        <v>1.9897557397365206E-2</v>
       </c>
       <c r="AJ38" s="7">
-        <f t="shared" si="78"/>
-        <v>1.1531294808460935E-2</v>
+        <f t="shared" si="74"/>
+        <v>2.0157593751345626E-2</v>
       </c>
     </row>
     <row r="39" spans="2:40" x14ac:dyDescent="0.3">
@@ -5173,39 +5173,39 @@
         <v>48</v>
       </c>
       <c r="C39" s="7">
-        <f t="shared" ref="C39:K39" si="79">C21/C16</f>
+        <f t="shared" ref="C39:K39" si="75">C21/C16</f>
         <v>0.57962840079628397</v>
       </c>
       <c r="D39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.52855284082694809</v>
       </c>
       <c r="E39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.50438963210702337</v>
       </c>
       <c r="F39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.47045439771175973</v>
       </c>
       <c r="G39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.45080819651266385</v>
       </c>
       <c r="H39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.45222434824204738</v>
       </c>
       <c r="I39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.46498632050759647</v>
       </c>
       <c r="J39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.44880824928156871</v>
       </c>
       <c r="K39" s="7">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.46021227607120796</v>
       </c>
       <c r="L39" s="7">
@@ -5221,80 +5221,80 @@
         <v>0.44447913414507234</v>
       </c>
       <c r="O39" s="7">
-        <f t="shared" ref="O39:R39" si="80">O21/O16</f>
+        <f t="shared" ref="O39:R39" si="76">O21/O16</f>
         <v>0.45328262821528548</v>
       </c>
       <c r="P39" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>0.4486529875081523</v>
       </c>
       <c r="Q39" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
+        <v>0.45935691005496909</v>
+      </c>
+      <c r="R39" s="7">
+        <f t="shared" si="76"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="V39" s="7">
+        <f t="shared" ref="V39:AJ39" si="77">V21/V16</f>
+        <v>0.63312624095305192</v>
+      </c>
+      <c r="W39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.51732134831460674</v>
+      </c>
+      <c r="X39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45424856006175407</v>
+      </c>
+      <c r="Y39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45143596447487233</v>
+      </c>
+      <c r="Z39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.4502294392477999</v>
+      </c>
+      <c r="AA39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45</v>
+      </c>
+      <c r="AB39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45000000000000007</v>
+      </c>
+      <c r="AC39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45000000000000007</v>
+      </c>
+      <c r="AD39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45</v>
+      </c>
+      <c r="AE39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45</v>
+      </c>
+      <c r="AF39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45</v>
+      </c>
+      <c r="AG39" s="7">
+        <f t="shared" si="77"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="R39" s="7">
-        <f t="shared" si="80"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="V39" s="7">
-        <f t="shared" ref="V39:AJ39" si="81">V21/V16</f>
-        <v>0.63312624095305192</v>
-      </c>
-      <c r="W39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.51732134831460674</v>
-      </c>
-      <c r="X39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45424856006175407</v>
-      </c>
-      <c r="Y39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45143596447487233</v>
-      </c>
-      <c r="Z39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.44788486178641834</v>
-      </c>
-      <c r="AA39" s="7">
-        <f t="shared" si="81"/>
+      <c r="AH39" s="7">
+        <f t="shared" si="77"/>
         <v>0.45</v>
       </c>
-      <c r="AB39" s="7">
-        <f t="shared" si="81"/>
+      <c r="AI39" s="7">
+        <f t="shared" si="77"/>
+        <v>0.45</v>
+      </c>
+      <c r="AJ39" s="7">
+        <f t="shared" si="77"/>
         <v>0.45000000000000007</v>
-      </c>
-      <c r="AC39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AD39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AE39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AF39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AG39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AH39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45000000000000007</v>
-      </c>
-      <c r="AI39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
-      </c>
-      <c r="AJ39" s="7">
-        <f t="shared" si="81"/>
-        <v>0.45</v>
       </c>
       <c r="AM39" s="1" t="s">
         <v>54</v>
@@ -5308,39 +5308,39 @@
         <v>49</v>
       </c>
       <c r="C40" s="7">
-        <f t="shared" ref="C40:K40" si="82">C22/C16</f>
+        <f t="shared" ref="C40:K40" si="78">C22/C16</f>
         <v>0.10152621101526212</v>
       </c>
       <c r="D40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.10857308081538239</v>
       </c>
       <c r="E40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>0.10158862876254181</v>
       </c>
       <c r="F40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>8.2818695963076117E-2</v>
       </c>
       <c r="G40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>8.5337915234822453E-2</v>
       </c>
       <c r="H40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>8.4190385075340823E-2</v>
       </c>
       <c r="I40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>7.1948308981896497E-2</v>
       </c>
       <c r="J40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>6.9194793486223025E-2</v>
       </c>
       <c r="K40" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
         <v>8.2888751614533615E-2</v>
       </c>
       <c r="L40" s="7">
@@ -5348,87 +5348,87 @@
         <v>8.0447899113985977E-2</v>
       </c>
       <c r="M40" s="7">
-        <f t="shared" ref="M40:N40" si="83">M22/M16</f>
+        <f t="shared" ref="M40:N40" si="79">M22/M16</f>
         <v>7.8278928590446772E-2</v>
       </c>
       <c r="N40" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>8.3983765220106157E-2</v>
       </c>
       <c r="O40" s="7">
-        <f t="shared" ref="O40:R40" si="84">O22/O16</f>
+        <f t="shared" ref="O40:R40" si="80">O22/O16</f>
         <v>7.848729731157239E-2</v>
       </c>
       <c r="P40" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>7.8011337982240511E-2</v>
       </c>
       <c r="Q40" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
+        <v>7.778372330592985E-2</v>
+      </c>
+      <c r="R40" s="7">
+        <f t="shared" si="80"/>
         <v>0.08</v>
       </c>
-      <c r="R40" s="7">
-        <f t="shared" si="84"/>
+      <c r="V40" s="7">
+        <f t="shared" ref="V40:AJ40" si="81">V22/V16</f>
+        <v>0.11868314865816948</v>
+      </c>
+      <c r="W40" s="7">
+        <f t="shared" si="81"/>
+        <v>9.8121348314606741E-2</v>
+      </c>
+      <c r="X40" s="7">
+        <f t="shared" si="81"/>
+        <v>7.7385547176533453E-2</v>
+      </c>
+      <c r="Y40" s="7">
+        <f t="shared" si="81"/>
+        <v>8.1400520208622526E-2</v>
+      </c>
+      <c r="Z40" s="7">
+        <f t="shared" si="81"/>
+        <v>7.8583102929905169E-2</v>
+      </c>
+      <c r="AA40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="V40" s="7">
-        <f t="shared" ref="V40:AJ40" si="85">V22/V16</f>
-        <v>0.11868314865816948</v>
-      </c>
-      <c r="W40" s="7">
-        <f t="shared" si="85"/>
-        <v>9.8121348314606741E-2</v>
-      </c>
-      <c r="X40" s="7">
-        <f t="shared" si="85"/>
-        <v>7.7385547176533453E-2</v>
-      </c>
-      <c r="Y40" s="7">
-        <f t="shared" si="85"/>
-        <v>8.1400520208622526E-2</v>
-      </c>
-      <c r="Z40" s="7">
-        <f t="shared" si="85"/>
-        <v>7.913516766955804E-2</v>
-      </c>
-      <c r="AA40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AB40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AB40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AC40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AC40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AD40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AD40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AE40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AE40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AF40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AF40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AG40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AG40" s="7">
-        <f t="shared" si="85"/>
+      <c r="AH40" s="7">
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
-      <c r="AH40" s="7">
-        <f t="shared" si="85"/>
-        <v>0.08</v>
-      </c>
       <c r="AI40" s="7">
-        <f t="shared" si="85"/>
-        <v>0.08</v>
+        <f t="shared" si="81"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="AJ40" s="7">
-        <f t="shared" si="85"/>
+        <f t="shared" si="81"/>
         <v>0.08</v>
       </c>
       <c r="AM40" s="1" t="s">
@@ -5447,23 +5447,23 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7">
-        <f t="shared" ref="G41:K41" si="86">G23/C23-1</f>
+        <f t="shared" ref="G41:K41" si="82">G23/C23-1</f>
         <v>0.2176541717049576</v>
       </c>
       <c r="H41" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3.2488986784140916E-2</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>0.17105263157894735</v>
       </c>
       <c r="J41" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>4.7689282202556527E-2</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>4.170804369414105E-2</v>
       </c>
       <c r="L41" s="7">
@@ -5471,28 +5471,28 @@
         <v>3.9466666666666761E-2</v>
       </c>
       <c r="M41" s="7">
-        <f t="shared" ref="M41:N41" si="87">M23/I23-1</f>
+        <f t="shared" ref="M41:N41" si="83">M23/I23-1</f>
         <v>9.7703957010253362E-4</v>
       </c>
       <c r="N41" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>-1.3608634443923018E-2</v>
       </c>
       <c r="O41" s="7">
-        <f t="shared" ref="O41" si="88">O23/K23-1</f>
+        <f t="shared" ref="O41" si="84">O23/K23-1</f>
         <v>1.048617731172552E-2</v>
       </c>
       <c r="P41" s="7">
-        <f t="shared" ref="P41" si="89">P23/L23-1</f>
+        <f t="shared" ref="P41" si="85">P23/L23-1</f>
         <v>0.10415597742432015</v>
       </c>
       <c r="Q41" s="7">
-        <f t="shared" ref="Q41" si="90">Q23/M23-1</f>
+        <f t="shared" ref="Q41" si="86">Q23/M23-1</f>
+        <v>9.272816007808693E-2</v>
+      </c>
+      <c r="R41" s="7">
+        <f t="shared" ref="R41" si="87">R23/N23-1</f>
         <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="R41" s="7">
-        <f t="shared" ref="R41" si="91">R23/N23-1</f>
-        <v>5.0000000000000044E-2</v>
       </c>
       <c r="V41" s="7"/>
       <c r="W41" s="7">
@@ -5500,55 +5500,55 @@
         <v>0.58133449629306577</v>
       </c>
       <c r="X41" s="7">
-        <f t="shared" ref="X41:AJ41" si="92">X23/W23-1</f>
+        <f t="shared" ref="X41:AJ41" si="88">X23/W23-1</f>
         <v>0.11238279095421944</v>
       </c>
       <c r="Y41" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>1.6238998388496295E-2</v>
       </c>
       <c r="Z41" s="7">
-        <f t="shared" si="92"/>
-        <v>5.7761649182727526E-2</v>
+        <f t="shared" si="88"/>
+        <v>6.8570383020248871E-2</v>
       </c>
       <c r="AA41" s="7">
-        <f t="shared" si="92"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="88"/>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AB41" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC41" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD41" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE41" s="7">
+        <f t="shared" si="88"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF41" s="7">
+        <f t="shared" si="88"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE41" s="7">
-        <f t="shared" si="92"/>
+      <c r="AG41" s="7">
+        <f t="shared" si="88"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF41" s="7">
-        <f t="shared" si="92"/>
+      <c r="AH41" s="7">
+        <f t="shared" si="88"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG41" s="7">
-        <f t="shared" si="92"/>
+      <c r="AI41" s="7">
+        <f t="shared" si="88"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH41" s="7">
-        <f t="shared" si="92"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AI41" s="7">
-        <f t="shared" si="92"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AJ41" s="7">
-        <f t="shared" si="92"/>
+        <f t="shared" si="88"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM41" s="1" t="s">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AN41" s="3">
         <f>NPV(AN40,Z27:EW27)</f>
-        <v>197982.70311972545</v>
+        <v>226674.51820242303</v>
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.3">
@@ -5564,39 +5564,39 @@
         <v>51</v>
       </c>
       <c r="C42" s="7">
-        <f t="shared" ref="C42:K42" si="93">C24/C16</f>
+        <f t="shared" ref="C42:K42" si="89">C24/C16</f>
         <v>0.11595885865958859</v>
       </c>
       <c r="D42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.104886511493422</v>
       </c>
       <c r="E42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.10967112597547381</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.13378404732496912</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>9.940180730558737E-2</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>9.2441999521645543E-2</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>9.3428022585715115E-2</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>0.11799177325745197</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="93"/>
+        <f t="shared" si="89"/>
         <v>8.2888751614533615E-2</v>
       </c>
       <c r="L42" s="7">
@@ -5604,87 +5604,87 @@
         <v>5.6422242756971247E-2</v>
       </c>
       <c r="M42" s="7">
-        <f t="shared" ref="M42:N42" si="94">M24/M16</f>
+        <f t="shared" ref="M42:N42" si="90">M24/M16</f>
         <v>9.4786729857819899E-2</v>
       </c>
       <c r="N42" s="7">
-        <f t="shared" si="94"/>
+        <f t="shared" si="90"/>
         <v>0.10771152044957852</v>
       </c>
       <c r="O42" s="7">
-        <f t="shared" ref="O42:R42" si="95">O24/O16</f>
+        <f t="shared" ref="O42:R42" si="91">O24/O16</f>
         <v>8.693815031954788E-2</v>
       </c>
       <c r="P42" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
         <v>8.4583354236692915E-2</v>
       </c>
       <c r="Q42" s="7">
-        <f t="shared" si="95"/>
+        <f t="shared" si="91"/>
+        <v>8.6588509996594828E-2</v>
+      </c>
+      <c r="R42" s="7">
+        <f t="shared" si="91"/>
+        <v>0.11</v>
+      </c>
+      <c r="V42" s="7">
+        <f t="shared" ref="V42:AJ42" si="92">V24/V16</f>
+        <v>9.9116121181067066E-2</v>
+      </c>
+      <c r="W42" s="7">
+        <f t="shared" si="92"/>
+        <v>0.1165123595505618</v>
+      </c>
+      <c r="X42" s="7">
+        <f t="shared" si="92"/>
+        <v>0.10104803752746273</v>
+      </c>
+      <c r="Y42" s="7">
+        <f t="shared" si="92"/>
+        <v>8.5767038180078442E-2</v>
+      </c>
+      <c r="Z42" s="7">
+        <f t="shared" si="92"/>
+        <v>9.2269743646677851E-2</v>
+      </c>
+      <c r="AA42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="R42" s="7">
-        <f t="shared" si="95"/>
-        <v>0.10999999999999999</v>
-      </c>
-      <c r="V42" s="7">
-        <f t="shared" ref="V42:AJ42" si="96">V24/V16</f>
-        <v>9.9116121181067066E-2</v>
-      </c>
-      <c r="W42" s="7">
-        <f t="shared" si="96"/>
-        <v>0.1165123595505618</v>
-      </c>
-      <c r="X42" s="7">
-        <f t="shared" si="96"/>
-        <v>0.10104803752746273</v>
-      </c>
-      <c r="Y42" s="7">
-        <f t="shared" si="96"/>
-        <v>8.5767038180078442E-2</v>
-      </c>
-      <c r="Z42" s="7">
-        <f t="shared" si="96"/>
-        <v>9.0507705215288531E-2</v>
-      </c>
-      <c r="AA42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AB42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AB42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AC42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AC42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AD42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AD42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AE42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AE42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AF42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AF42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AG42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AG42" s="7">
-        <f t="shared" si="96"/>
+      <c r="AH42" s="7">
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
-      <c r="AH42" s="7">
-        <f t="shared" si="96"/>
-        <v>0.08</v>
-      </c>
       <c r="AI42" s="7">
-        <f t="shared" si="96"/>
-        <v>0.08</v>
+        <f t="shared" si="92"/>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="AJ42" s="7">
-        <f t="shared" si="96"/>
+        <f t="shared" si="92"/>
         <v>0.08</v>
       </c>
       <c r="AM42" s="1" t="s">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AN42" s="3">
         <f>Main!D8</f>
-        <v>-1758</v>
+        <v>-3153</v>
       </c>
     </row>
     <row r="43" spans="2:40" x14ac:dyDescent="0.3">
@@ -5700,39 +5700,39 @@
         <v>52</v>
       </c>
       <c r="C43" s="7">
-        <f t="shared" ref="C43:K43" si="97">C25/C16</f>
+        <f t="shared" ref="C43:K43" si="93">C25/C16</f>
         <v>0.22495023224950234</v>
       </c>
       <c r="D43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.18382246638716207</v>
       </c>
       <c r="E43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.171335005574136</v>
       </c>
       <c r="F43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.12162777091594618</v>
       </c>
       <c r="G43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.13790250731831488</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.16347763692896436</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.18045287851446534</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.14154504986758326</v>
       </c>
       <c r="K43" s="7">
-        <f t="shared" si="97"/>
+        <f t="shared" si="93"/>
         <v>0.17661593755264784</v>
       </c>
       <c r="L43" s="7">
@@ -5740,95 +5740,95 @@
         <v>0.20601184975811274</v>
       </c>
       <c r="M43" s="7">
-        <f t="shared" ref="M43:N43" si="98">M25/M16</f>
+        <f t="shared" ref="M43:N43" si="94">M25/M16</f>
         <v>0.17061611374407584</v>
       </c>
       <c r="N43" s="7">
-        <f t="shared" si="98"/>
+        <f t="shared" si="94"/>
         <v>0.14340722239567072</v>
       </c>
       <c r="O43" s="7">
-        <f t="shared" ref="O43:R43" si="99">O25/O16</f>
+        <f t="shared" ref="O43:R43" si="95">O25/O16</f>
         <v>0.17588337822848993</v>
       </c>
       <c r="P43" s="7">
-        <f t="shared" si="99"/>
+        <f t="shared" si="95"/>
         <v>0.17809662368935936</v>
       </c>
       <c r="Q43" s="7">
-        <f t="shared" si="99"/>
-        <v>0.17958539186980071</v>
+        <f t="shared" si="95"/>
+        <v>0.18606800603200857</v>
       </c>
       <c r="R43" s="7">
-        <f t="shared" si="99"/>
-        <v>0.14089631021810847</v>
+        <f t="shared" si="95"/>
+        <v>0.14249664700275974</v>
       </c>
       <c r="V43" s="7">
-        <f t="shared" ref="V43:AJ43" si="100">V25/V16</f>
+        <f t="shared" ref="V43:AJ43" si="96">V25/V16</f>
         <v>0.26846217895343621</v>
       </c>
       <c r="W43" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.17231460674157303</v>
       </c>
       <c r="X43" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.15606258535716405</v>
       </c>
       <c r="Y43" s="7">
-        <f t="shared" si="100"/>
+        <f t="shared" si="96"/>
         <v>0.17378471988248137</v>
       </c>
       <c r="Z43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.16840866291450016</v>
+        <f t="shared" si="96"/>
+        <v>0.170344471276096</v>
       </c>
       <c r="AA43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.17974620677752823</v>
+        <f t="shared" si="96"/>
+        <v>0.18203350882643302</v>
       </c>
       <c r="AB43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.17922868744916923</v>
+        <f t="shared" si="96"/>
+        <v>0.18347838538636876</v>
       </c>
       <c r="AC43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.17918575179965998</v>
+        <f t="shared" si="96"/>
+        <v>0.18481634093449828</v>
       </c>
       <c r="AD43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.17974843996232034</v>
+        <f t="shared" si="96"/>
+        <v>0.18467845869622068</v>
       </c>
       <c r="AE43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.18016232209777724</v>
+        <f t="shared" si="96"/>
+        <v>0.18456497763124718</v>
       </c>
       <c r="AF43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.18032313273936301</v>
+        <f t="shared" si="96"/>
+        <v>0.18551098863320103</v>
       </c>
       <c r="AG43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.1804850583769545</v>
+        <f t="shared" si="96"/>
+        <v>0.18647356248131849</v>
       </c>
       <c r="AH43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.18064810270652581</v>
+        <f t="shared" si="96"/>
+        <v>0.18745253102889201</v>
       </c>
       <c r="AI43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.18081226936595801</v>
+        <f t="shared" si="96"/>
+        <v>0.1884476990756575</v>
       </c>
       <c r="AJ43" s="7">
-        <f t="shared" si="100"/>
-        <v>0.18097756193369724</v>
+        <f t="shared" si="96"/>
+        <v>0.18945884384742825</v>
       </c>
       <c r="AM43" s="1" t="s">
         <v>58</v>
       </c>
       <c r="AN43" s="3">
         <f>AN41+AN42</f>
-        <v>196224.70311972545</v>
+        <v>223521.51820242303</v>
       </c>
     </row>
     <row r="44" spans="2:40" x14ac:dyDescent="0.3">
@@ -5836,39 +5836,39 @@
         <v>33</v>
       </c>
       <c r="C44" s="7">
-        <f t="shared" ref="C44:K44" si="101">C26/C25</f>
+        <f t="shared" ref="C44:K44" si="97">C26/C25</f>
         <v>0.22603244837758113</v>
       </c>
       <c r="D44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.22768383798662997</v>
       </c>
       <c r="E44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.23586823912159413</v>
       </c>
       <c r="F44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.15980758952431853</v>
       </c>
       <c r="G44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.16197508075680664</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.20482809070958302</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.20935483870967742</v>
       </c>
       <c r="J44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.2304936305732484</v>
       </c>
       <c r="K44" s="7">
-        <f t="shared" si="101"/>
+        <f t="shared" si="97"/>
         <v>0.22511923688394275</v>
       </c>
       <c r="L44" s="7">
@@ -5876,87 +5876,87 @@
         <v>0.20448548812664907</v>
       </c>
       <c r="M44" s="7">
-        <f t="shared" ref="M44:N44" si="102">M26/M25</f>
+        <f t="shared" ref="M44:N44" si="98">M26/M25</f>
         <v>0.21754057428214732</v>
       </c>
       <c r="N44" s="7">
-        <f t="shared" si="102"/>
+        <f t="shared" si="98"/>
         <v>0.21262699564586357</v>
       </c>
       <c r="O44" s="7">
-        <f t="shared" ref="O44:R44" si="103">O26/O25</f>
+        <f t="shared" ref="O44:R44" si="99">O26/O25</f>
         <v>0.22402402402402402</v>
       </c>
       <c r="P44" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="99"/>
         <v>0.18732394366197183</v>
       </c>
       <c r="Q44" s="7">
-        <f t="shared" si="103"/>
+        <f t="shared" si="99"/>
+        <v>0.24130718954248365</v>
+      </c>
+      <c r="R44" s="7">
+        <f t="shared" si="99"/>
         <v>0.21</v>
       </c>
-      <c r="R44" s="7">
-        <f t="shared" si="103"/>
-        <v>0.21000000000000002</v>
-      </c>
       <c r="V44" s="7">
-        <f t="shared" ref="V44:AJ44" si="104">V26/V25</f>
+        <f t="shared" ref="V44:AJ44" si="100">V26/V25</f>
         <v>0.24358821424311106</v>
       </c>
       <c r="W44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.21606677099634847</v>
       </c>
       <c r="X44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.20346237991058688</v>
       </c>
       <c r="Y44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.21450174486234974</v>
       </c>
       <c r="Z44" s="7">
-        <f t="shared" si="104"/>
-        <v>0.20745791143688347</v>
+        <f t="shared" si="100"/>
+        <v>0.21628002327882978</v>
       </c>
       <c r="AA44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AB44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AC44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AD44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AE44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AF44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AG44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AH44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AI44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AJ44" s="7">
-        <f t="shared" si="104"/>
+        <f t="shared" si="100"/>
         <v>0.2</v>
       </c>
       <c r="AM44" s="1" t="s">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AN44" s="8">
         <f>AN43/AJ28</f>
-        <v>281.972558010814</v>
+        <v>324.46148672147342</v>
       </c>
     </row>
     <row r="45" spans="2:40" x14ac:dyDescent="0.3">
@@ -5972,39 +5972,39 @@
         <v>53</v>
       </c>
       <c r="C45" s="7">
-        <f t="shared" ref="C45:K45" si="105">C27/C16</f>
+        <f t="shared" ref="C45:K45" si="101">C27/C16</f>
         <v>0.17410418049104182</v>
       </c>
       <c r="D45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.14196906173196472</v>
       </c>
       <c r="E45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.13092251950947603</v>
       </c>
       <c r="F45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.1021907300266528</v>
       </c>
       <c r="G45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.11556573755886471</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.12999282468309017</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.14267419523837244</v>
       </c>
       <c r="J45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.10891981743393249</v>
       </c>
       <c r="K45" s="7">
-        <f t="shared" si="105"/>
+        <f t="shared" si="101"/>
         <v>0.13685629246925365</v>
       </c>
       <c r="L45" s="7">
@@ -6012,95 +6012,95 @@
         <v>0.16388541610045115</v>
       </c>
       <c r="M45" s="7">
-        <f t="shared" ref="M45:N45" si="106">M27/M16</f>
+        <f t="shared" ref="M45:N45" si="102">M27/M16</f>
         <v>0.13350018637840141</v>
       </c>
       <c r="N45" s="7">
-        <f t="shared" si="106"/>
+        <f t="shared" si="102"/>
         <v>0.11291497554376105</v>
       </c>
       <c r="O45" s="7">
-        <f t="shared" ref="O45:R45" si="107">O27/O16</f>
+        <f t="shared" ref="O45:R45" si="103">O27/O16</f>
         <v>0.1364812760788042</v>
       </c>
       <c r="P45" s="7">
-        <f t="shared" si="107"/>
+        <f t="shared" si="103"/>
         <v>0.14473486178698641</v>
       </c>
       <c r="Q45" s="7">
-        <f t="shared" si="107"/>
-        <v>0.14187245957714256</v>
+        <f t="shared" si="103"/>
+        <v>0.14116845843265069</v>
       </c>
       <c r="R45" s="7">
-        <f t="shared" si="107"/>
-        <v>0.11130808507230569</v>
+        <f t="shared" si="103"/>
+        <v>0.11257235113218018</v>
       </c>
       <c r="V45" s="7">
-        <f t="shared" ref="V45:AJ45" si="108">V27/V16</f>
+        <f t="shared" ref="V45:AJ45" si="104">V27/V16</f>
         <v>0.2030679561903542</v>
       </c>
       <c r="W45" s="7">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.13508314606741573</v>
       </c>
       <c r="X45" s="7">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.12430972032539635</v>
       </c>
       <c r="Y45" s="7">
-        <f t="shared" si="108"/>
+        <f t="shared" si="104"/>
         <v>0.13650759423727443</v>
       </c>
       <c r="Z45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.13347095343837984</v>
+        <f t="shared" si="104"/>
+        <v>0.13350236506308202</v>
       </c>
       <c r="AA45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14379696542202258</v>
+        <f t="shared" si="104"/>
+        <v>0.14562680706114642</v>
       </c>
       <c r="AB45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14338294995933537</v>
+        <f t="shared" si="104"/>
+        <v>0.14678270830909501</v>
       </c>
       <c r="AC45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.143348601439728</v>
+        <f t="shared" si="104"/>
+        <v>0.14785307274759862</v>
       </c>
       <c r="AD45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14379875196985628</v>
+        <f t="shared" si="104"/>
+        <v>0.14774276695697655</v>
       </c>
       <c r="AE45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14412985767822178</v>
+        <f t="shared" si="104"/>
+        <v>0.14765198210499775</v>
       </c>
       <c r="AF45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14425850619149042</v>
+        <f t="shared" si="104"/>
+        <v>0.14840879090656081</v>
       </c>
       <c r="AG45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.1443880467015636</v>
+        <f t="shared" si="104"/>
+        <v>0.14917884998505479</v>
       </c>
       <c r="AH45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14451848216522065</v>
+        <f t="shared" si="104"/>
+        <v>0.1499620248231136</v>
       </c>
       <c r="AI45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.1446498154927664</v>
+        <f t="shared" si="104"/>
+        <v>0.15075815926052599</v>
       </c>
       <c r="AJ45" s="7">
-        <f t="shared" si="108"/>
-        <v>0.14478204954695778</v>
+        <f t="shared" si="104"/>
+        <v>0.15156707507794262</v>
       </c>
       <c r="AM45" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AN45" s="8">
         <f>Main!D3</f>
-        <v>337.65</v>
+        <v>357.56</v>
       </c>
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.3">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AN46" s="9">
         <f>AN44/AN45-1</f>
-        <v>-0.16489691097049008</v>
+        <v>-9.2567718085150963E-2</v>
       </c>
     </row>
     <row r="47" spans="2:40" x14ac:dyDescent="0.3">
